--- a/策划/excel/5_Enemy.xlsx
+++ b/策划/excel/5_Enemy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27765" windowHeight="13485"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27315" windowHeight="10815"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="5_Enemy" state="visible" r:id="rId4"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="536">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -34,6 +34,18 @@
     <t>敌人行为树</t>
   </si>
   <si>
+    <t>道具掉落</t>
+  </si>
+  <si>
+    <t>卡牌掉落 （必定掉落,数组长度三意味进入三选一界面 0.4意味着这张牌为1级牌概率是0.4第二个0.4意味这张牌的二级概率为0.4  0.2意味为三级牌概率为0.2）</t>
+  </si>
+  <si>
+    <t>资源掉落 [[资源ID,数量]]：精英敌人掉落100金币和1枝桠，其余敌人固定掉落100金币</t>
+  </si>
+  <si>
+    <t>特殊状态与阶段机制（无召唤）：初始状态、一次性阶段、事件触发</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -52,6 +64,18 @@
     <t>behavior</t>
   </si>
   <si>
+    <t>itemRewad</t>
+  </si>
+  <si>
+    <t>cardRewad</t>
+  </si>
+  <si>
+    <t>resourceReward</t>
+  </si>
+  <si>
+    <t>mechanics</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -61,6 +85,9 @@
     <t>json</t>
   </si>
   <si>
+    <t>array</t>
+  </si>
+  <si>
     <t>server</t>
   </si>
   <si>
@@ -70,37 +97,67 @@
     <t>渡鸦</t>
   </si>
   <si>
+    <t>生命48；行动：。战斗初始：EVASION 1。振翅反扑：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
     <t>{"type":"ACTION","action":"ATTACK","amount":5,"hits":1}</t>
   </si>
   <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.2]]</t>
+  </si>
+  <si>
+    <t>[[180001,100]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"振翅反扑","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"振翅反扑","amount":5,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"振翅反扑·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"振翅反扑·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"渡鸦·追击","amount":3,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
     <t>劫掠者刺客</t>
   </si>
   <si>
     <t>普通敌人</t>
   </si>
   <si>
-    <t>Assassin Ruby Raider。SlaySpireDB v0.107.1，普通难度生命区间取下限。 Killshot 每回合造成 10 点伤害。</t>
-  </si>
-  <si>
-    <t>{"type":"ACTION","action":"ATTACK","moveName":"Killshot","amount":10,"hits":1,"editorId":"sts2-50002-1","editorX":70,"editorY":90}</t>
+    <t>生命54；行动：致命一击。战斗初始：EVASION 1。破绽刺杀：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"ACTION","action":"ATTACK","moveName":"致命一击","amount":10,"hits":1,"editorId":"sts2-50002-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.3]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"破绽刺杀","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"破绽刺杀","amount":10,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"破绽刺杀·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"破绽刺杀·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"劫掠者刺客·追击","amount":7,"hits":1}]}}],"triggers":[]}</t>
   </si>
   <si>
     <t>劫掠者斧手</t>
   </si>
   <si>
-    <t>Axe Ruby Raider。SlaySpireDB v0.107.1，普通难度生命区间取下限。 两次挥砍各造成 5 点伤害并获得 5 点格挡，随后重击 12 点，循环。</t>
-  </si>
-  <si>
-    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"Swing 1","amount":5,"hits":1,"editorId":"sts2-50003-3","editorX":670,"editorY":90},{"type":"ACTION","action":"DEFEND","moveName":"Swing 1·格挡","amount":5,"editorId":"sts2-50003-4","editorX":670,"editorY":245}],"editorId":"sts2-50003-2","editorX":370,"editorY":168},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"Swing 2","amount":5,"hits":1,"editorId":"sts2-50003-6","editorX":670,"editorY":400},{"type":"ACTION","action":"DEFEND","moveName":"Swing 2·格挡","amount":5,"editorId":"sts2-50003-7","editorX":670,"editorY":555}],"editorId":"sts2-50003-5","editorX":370,"editorY":478},{"type":"ACTION","action":"ATTACK","moveName":"Big Swing","amount":12,"hits":1,"editorId":"sts2-50003-8","editorX":370,"editorY":710}],"editorId":"sts2-50003-1","editorX":70,"editorY":439}</t>
+    <t>生命58；行动：挥砍一式、挥砍一式·格挡、挥砍二式、挥砍二式·格挡、重斧横扫。战斗初始：PLATED_ARMOR 2。重斧姿态：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"挥砍一式","amount":5,"hits":1,"editorId":"sts2-50003-3","editorX":670,"editorY":90},{"type":"ACTION","action":"DEFEND","moveName":"挥砍一式·格挡","amount":5,"editorId":"sts2-50003-4","editorX":670,"editorY":245}],"editorId":"sts2-50003-2","editorX":370,"editorY":168},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"挥砍二式","amount":5,"hits":1,"editorId":"sts2-50003-6","editorX":670,"editorY":400},{"type":"ACTION","action":"DEFEND","moveName":"挥砍二式·格挡","amount":5,"editorId":"sts2-50003-7","editorX":670,"editorY":555}],"editorId":"sts2-50003-5","editorX":370,"editorY":478},{"type":"ACTION","action":"ATTACK","moveName":"重斧横扫","amount":12,"hits":1,"editorId":"sts2-50003-8","editorX":370,"editorY":710}],"editorId":"sts2-50003-1","editorX":70,"editorY":439}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.4]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"重斧姿态","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"重斧姿态","amount":12,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"重斧姿态·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"重斧姿态·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"劫掠者斧手·追击","amount":9,"hits":1}]}}],"triggers":[]}</t>
   </si>
   <si>
     <t>盛碗虫（丝）</t>
   </si>
   <si>
-    <t>Bowlbug (Silk)。SlaySpireDB v0.107.1，普通难度生命区间取下限。 毒液施加 1 层虚弱，随后以 4 点伤害攻击两次，交替行动。</t>
-  </si>
-  <si>
-    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"Toxic Spit","status":"WEAK","stacks":1,"editorId":"sts2-50004-2","editorX":370,"editorY":90},{"type":"ACTION","action":"ATTACK","moveName":"Thrash","amount":4,"hits":2,"editorId":"sts2-50004-3","editorX":370,"editorY":245}],"editorId":"sts2-50004-1","editorX":70,"editorY":168}</t>
+    <t>生命56；行动：毒液喷吐、乱击。战斗初始：ARMOR 1。缚丝蜕变：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"毒液喷吐","status":"WEAK","stacks":1,"editorId":"sts2-50004-2","editorX":370,"editorY":90},{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":4,"hits":2,"editorId":"sts2-50004-3","editorX":370,"editorY":245}],"editorId":"sts2-50004-1","editorX":70,"editorY":168}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.5]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"缚丝蜕变","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"缚丝蜕变","amount":4,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"缚丝蜕变·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"缚丝蜕变·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"盛碗虫（丝）·追击","amount":3,"hits":2}]}}],"triggers":[]}</t>
   </si>
   <si>
     <t>旧日雕像</t>
@@ -109,37 +166,64 @@
     <t>精英敌人</t>
   </si>
   <si>
-    <t>Bygone Effigy。SlaySpireDB v0.107.1，普通难度生命区间取下限。 首回合沉睡，次回合苏醒并获得 10 点力量，之后持续斩击 13 点基础伤害。受伤提前苏醒及 Slow 被动尚未实现。</t>
-  </si>
-  <si>
-    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"WAIT","moveName":"Sleep","editorId":"sts2-50005-3","editorX":670,"editorY":90}],"editorId":"sts2-50005-2","editorX":370,"editorY":90},{"type":"CONDITION","field":"TURN","operator":"==","value":2,"children":[{"type":"ACTION","action":"BUFF","moveName":"Wake","status":"STRENGTH","stacks":10,"editorId":"sts2-50005-5","editorX":670,"editorY":245}],"editorId":"sts2-50005-4","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"Slashes","amount":13,"hits":1,"editorId":"sts2-50005-6","editorX":370,"editorY":400}],"editorId":"sts2-50005-1","editorX":70,"editorY":245}</t>
+    <t>生命110；行动：沉睡、苏醒、连环斩击。战斗初始：ARMOR 3。古像复苏：第3回合起进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"WAIT","moveName":"沉睡","editorId":"sts2-50005-3","editorX":670,"editorY":90}],"editorId":"sts2-50005-2","editorX":370,"editorY":90},{"type":"CONDITION","field":"TURN","operator":"==","value":2,"children":[{"type":"ACTION","action":"BUFF","moveName":"苏醒","status":"STRENGTH","stacks":1,"editorId":"sts2-50005-5","editorX":670,"editorY":245}],"editorId":"sts2-50005-4","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"连环斩击","amount":13,"hits":1,"editorId":"sts2-50005-6","editorX":370,"editorY":400}],"editorId":"sts2-50005-1","editorX":70,"editorY":245}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.6]]</t>
+  </si>
+  <si>
+    <t>[[180001,100],[180002,1]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"古像复苏","condition":"TURN_AT_LEAST","value":3,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"REMOVE_STATUS","target":"SELF","params":{"status":"ARMOR","amount":"ALL"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"古像复苏","amount":13,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"古像复苏·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"古像复苏·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"旧日雕像·追击","amount":9,"hits":1}]}}],"triggers":[]}</t>
   </si>
   <si>
     <t>多尼斯异鸟</t>
   </si>
   <si>
-    <t>Byrdonis。SlaySpireDB v0.107.1，普通难度生命区间取下限。 先俯冲造成 17 点伤害，再啄击 3 点伤害三次，交替行动。Territorial 被动尚未实现。</t>
-  </si>
-  <si>
-    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"Swoop","amount":17,"hits":1,"editorId":"sts2-50006-2","editorX":370,"editorY":90},{"type":"ACTION","action":"ATTACK","moveName":"Peck","amount":3,"hits":3,"editorId":"sts2-50006-3","editorX":370,"editorY":245}],"editorId":"sts2-50006-1","editorX":70,"editorY":168}</t>
+    <t>生命100；行动：俯冲、啄击。战斗初始：FLIGHT 3。坠地狂啄：累计受到3段攻击生命损失后进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"俯冲","amount":17,"hits":1,"editorId":"sts2-50006-2","editorX":370,"editorY":90},{"type":"ACTION","action":"ATTACK","moveName":"啄击","amount":3,"hits":3,"editorId":"sts2-50006-3","editorX":370,"editorY":245}],"editorId":"sts2-50006-1","editorX":70,"editorY":168}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.7]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FLIGHT","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"坠地狂啄","condition":"HITS_AT_LEAST","value":3,"effects":[{"type":"REMOVE_STATUS","target":"SELF","params":{"status":"FLIGHT","amount":"ALL"}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"坠地狂啄","amount":17,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"坠地狂啄·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"坠地狂啄·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"多尼斯异鸟·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
   </si>
   <si>
     <t>拳击构装体</t>
   </si>
   <si>
-    <t>Punch Construct。SlaySpireDB v0.107.1，普通难度生命区间取下限。 准备获得 10 格挡，快速拳 5×2 并施加 1 层脆弱，强力拳造成 14 点伤害，循环。初始 Artifact 被动尚未实现。</t>
-  </si>
-  <si>
-    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEFEND","moveName":"Ready","amount":10,"editorId":"sts2-50007-2","editorX":370,"editorY":90},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"Fast Punch","amount":5,"hits":2,"editorId":"sts2-50007-4","editorX":670,"editorY":245},{"type":"ACTION","action":"DEBUFF","moveName":"Fast Punch·脆弱","status":"FRAIL","stacks":1,"editorId":"sts2-50007-5","editorX":670,"editorY":400}],"editorId":"sts2-50007-3","editorX":370,"editorY":323},{"type":"ACTION","action":"ATTACK","moveName":"Strong Punch","amount":14,"hits":1,"editorId":"sts2-50007-6","editorX":370,"editorY":555}],"editorId":"sts2-50007-1","editorX":70,"editorY":323}</t>
+    <t>生命68；行动：准备就绪、快速拳、快速拳·脆弱、重拳。战斗初始：PLATED_ARMOR 3。过载拳击：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEFEND","moveName":"准备就绪","amount":8,"editorId":"sts2-50007-2","editorX":370,"editorY":90},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"快速拳","amount":5,"hits":2,"editorId":"sts2-50007-4","editorX":670,"editorY":245},{"type":"ACTION","action":"DEBUFF","moveName":"快速拳·脆弱","status":"FRAIL","stacks":1,"editorId":"sts2-50007-5","editorX":670,"editorY":400}],"editorId":"sts2-50007-3","editorX":370,"editorY":323},{"type":"ACTION","action":"ATTACK","moveName":"重拳","amount":14,"hits":1,"editorId":"sts2-50007-6","editorX":370,"editorY":555}],"editorId":"sts2-50007-1","editorX":70,"editorY":323}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.8]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"过载拳击","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"过载拳击","amount":14,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"过载拳击·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"过载拳击·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"拳击构装体·追击","amount":10,"hits":1}]}}],"triggers":[]}</t>
   </si>
   <si>
     <t>下水道蚌</t>
   </si>
   <si>
-    <t>Sewer Clam。SlaySpireDB v0.107.1，普通难度生命区间取下限。 先喷射 10 点伤害，再增压获得 4 点力量，交替行动。Plating 初始被动尚未实现。</t>
-  </si>
-  <si>
-    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"Jet","amount":10,"hits":1,"editorId":"sts2-50008-2","editorX":370,"editorY":90},{"type":"ACTION","action":"BUFF","moveName":"Pressurize","status":"STRENGTH","stacks":4,"editorId":"sts2-50008-3","editorX":370,"editorY":245}],"editorId":"sts2-50008-1","editorX":70,"editorY":168}</t>
+    <t>生命64；行动：水流喷射、加压。战斗初始：ARMOR 2。高压喷射：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"水流喷射","amount":10,"hits":1,"editorId":"sts2-50008-2","editorX":370,"editorY":90},{"type":"ACTION","action":"BUFF","moveName":"加压","status":"STRENGTH","stacks":1,"editorId":"sts2-50008-3","editorX":370,"editorY":245}],"editorId":"sts2-50008-1","editorX":70,"editorY":168}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.9]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"高压喷射","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"高压喷射","amount":10,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"高压喷射·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"高压喷射·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"下水道蚌·追击","amount":7,"hits":1}]}}],"triggers":[]}</t>
   </si>
   <si>
     <t>墨影幻灵</t>
@@ -148,28 +232,1396 @@
     <t>首领</t>
   </si>
   <si>
-    <t>Vantom。SlaySpireDB v0.107.1，普通难度生命区间取下限。 墨斑 7 点、墨枪 6×2、肢解 26 点、准备获得 3 点力量，四招循环。Slippery 初始被动尚未实现。</t>
-  </si>
-  <si>
-    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"Ink Blot","amount":7,"hits":1,"editorId":"sts2-50009-2","editorX":370,"editorY":90},{"type":"ACTION","action":"ATTACK","moveName":"Inky Lance","amount":6,"hits":2,"editorId":"sts2-50009-3","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"Dismember","amount":26,"hits":1,"editorId":"sts2-50009-4","editorX":370,"editorY":400},{"type":"ACTION","action":"BUFF","moveName":"Prepare","status":"STRENGTH","stacks":3,"editorId":"sts2-50009-5","editorX":370,"editorY":555}],"editorId":"sts2-50009-1","editorX":70,"editorY":323}</t>
+    <t>生命190；行动：墨迹、墨枪、肢解、蓄势。战斗初始：EVASION 1。墨影实体化：生命≤65%进入，阶段仅触发一次，切换招式。墨影实体化·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"墨迹","amount":7,"hits":1,"editorId":"sts2-50009-2","editorX":370,"editorY":90},{"type":"ACTION","action":"ATTACK","moveName":"墨枪","amount":6,"hits":2,"editorId":"sts2-50009-3","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"肢解","amount":26,"hits":1,"editorId":"sts2-50009-4","editorX":370,"editorY":400},{"type":"ACTION","action":"BUFF","moveName":"蓄势","status":"STRENGTH","stacks":2,"editorId":"sts2-50009-5","editorX":370,"editorY":555}],"editorId":"sts2-50009-1","editorX":70,"editorY":323}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.10]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"墨影实体化","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"墨影实体化","amount":24,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"墨影实体化·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"墨影实体化·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"墨影幻灵·追击","amount":18,"hits":1}]}},{"id":"phase2","name":"墨影实体化·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"墨影实体化·终局","amount":12,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"墨影实体化·终局·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"墨影实体化·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"墨影幻灵·追击","amount":9,"hits":2}]}}],"triggers":[]}</t>
   </si>
   <si>
     <t>巨斧机器人</t>
   </si>
   <si>
-    <t>Axebot。SlaySpireDB v0.107.1，普通难度生命区间取下限。 首回合启动获得 10 格挡和 3 力量；随后上勾拳 12 点并施加 2 虚弱、2 脆弱，与 9×2 连击交替。Stock 复活被动尚未实现。</t>
-  </si>
-  <si>
-    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"Boot Up·力量","status":"STRENGTH","stacks":3,"editorId":"sts2-50010-4","editorX":970,"editorY":90},{"type":"ACTION","action":"DEFEND","moveName":"Boot Up·格挡","amount":10,"editorId":"sts2-50010-5","editorX":970,"editorY":245}],"editorId":"sts2-50010-3","editorX":670,"editorY":168}],"editorId":"sts2-50010-2","editorX":370,"editorY":168},{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"The One-Two","amount":9,"hits":2,"editorId":"sts2-50010-7","editorX":670,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"Hammer Uppercut","amount":12,"hits":1,"editorId":"sts2-50010-9","editorX":970,"editorY":555},{"type":"ACTION","action":"DEBUFF","moveName":"Hammer Uppercut·虚弱","status":"WEAK","stacks":2,"editorId":"sts2-50010-10","editorX":970,"editorY":710},{"type":"ACTION","action":"DEBUFF","moveName":"Hammer Uppercut·脆弱","status":"FRAIL","stacks":2,"editorId":"sts2-50010-11","editorX":970,"editorY":865}],"editorId":"sts2-50010-8","editorX":670,"editorY":710}],"editorId":"sts2-50010-6","editorX":370,"editorY":555}],"editorId":"sts2-50010-1","editorX":70,"editorY":362}</t>
+    <t>生命72；行动：启动·力量、启动·格挡、左右连击、铁锤上勾拳、铁锤上勾拳·虚弱、铁锤上勾拳·脆弱。战斗初始：PLATED_ARMOR 4。重锤启动：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"启动·力量","status":"STRENGTH","stacks":1,"editorId":"sts2-50010-4","editorX":970,"editorY":90},{"type":"ACTION","action":"DEFEND","moveName":"启动·格挡","amount":8,"editorId":"sts2-50010-5","editorX":970,"editorY":245}],"editorId":"sts2-50010-3","editorX":670,"editorY":168}],"editorId":"sts2-50010-2","editorX":370,"editorY":168},{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"左右连击","amount":9,"hits":2,"editorId":"sts2-50010-7","editorX":670,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"铁锤上勾拳","amount":12,"hits":1,"editorId":"sts2-50010-9","editorX":970,"editorY":555},{"type":"ACTION","action":"DEBUFF","moveName":"铁锤上勾拳·虚弱","status":"WEAK","stacks":2,"editorId":"sts2-50010-10","editorX":970,"editorY":710},{"type":"ACTION","action":"DEBUFF","moveName":"铁锤上勾拳·脆弱","status":"FRAIL","stacks":2,"editorId":"sts2-50010-11","editorX":970,"editorY":865}],"editorId":"sts2-50010-8","editorX":670,"editorY":710}],"editorId":"sts2-50010-6","editorX":370,"editorY":555}],"editorId":"sts2-50010-1","editorX":70,"editorY":362}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.11]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":4,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"重锤启动","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"重锤启动","amount":8,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"重锤启动·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"重锤启动·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"巨斧机器人·追击","amount":6,"hits":2}]}}],"triggers":[]}</t>
   </si>
   <si>
     <t>永世沙漏</t>
   </si>
   <si>
-    <t>Aeonglass。SlaySpireDB v0.107.1，普通难度生命区间取下限。 潮落 26 点并获得 33 格挡；眼部激光 11×2；强度增长获得 3+此前使用次数的力量。Wither 卡牌、Withering Presence 与初始 Artifact 尚未实现。</t>
-  </si>
-  <si>
-    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"Ebb","amount":26,"hits":1,"editorId":"sts2-50011-3","editorX":670,"editorY":90},{"type":"ACTION","action":"DEFEND","moveName":"Ebb·格挡","amount":33,"editorId":"sts2-50011-4","editorX":670,"editorY":245}],"editorId":"sts2-50011-2","editorX":370,"editorY":168},{"type":"ACTION","action":"ATTACK","moveName":"Eye Lasers","amount":11,"hits":2,"editorId":"sts2-50011-5","editorX":370,"editorY":400},{"type":"ACTION","action":"EFFECTS","moveName":"Increasing Intensity","effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":"3+@intensity","duration":"COMBAT"}},{"type":"MODIFY_VARIABLE","target":"SELF","params":{"name":"intensity","scope":"COMBAT","operator":"ADD","value":1}}],"editorId":"sts2-50011-6","editorX":370,"editorY":555}],"editorId":"sts2-50011-1","editorX":70,"editorY":362}</t>
+    <t>生命300；行动：退潮、退潮·格挡、眼部激光、强度增长。战斗初始：ARTIFACT 2。逆转沙流：生命≤65%进入，阶段仅触发一次，切换招式。逆转沙流·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"退潮","amount":26,"hits":1,"editorId":"sts2-50011-3","editorX":670,"editorY":90},{"type":"ACTION","action":"DEFEND","moveName":"退潮·格挡","amount":16,"editorId":"sts2-50011-4","editorX":670,"editorY":245}],"editorId":"sts2-50011-2","editorX":370,"editorY":168},{"type":"ACTION","action":"ATTACK","moveName":"眼部激光","amount":11,"hits":2,"editorId":"sts2-50011-5","editorX":370,"editorY":400},{"type":"ACTION","action":"EFFECTS","moveName":"强度增长","effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":"1+min(@intensity,2)","duration":"COMBAT"}},{"type":"MODIFY_VARIABLE","target":"SELF","params":{"name":"intensity","scope":"COMBAT","operator":"ADD","value":1}}],"editorId":"sts2-50011-6","editorX":370,"editorY":555}],"editorId":"sts2-50011-1","editorX":70,"editorY":362}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.12]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"逆转沙流","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"逆转沙流","amount":24,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"逆转沙流·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"逆转沙流·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"永世沙漏·追击","amount":18,"hits":1}]}},{"id":"phase2","name":"逆转沙流·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"逆转沙流·终局","amount":12,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"逆转沙流·终局·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"逆转沙流·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"永世沙漏·追击","amount":9,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>长牙之眼</t>
+  </si>
+  <si>
+    <t>生命48；行动：干扰凝视、长牙撕咬、双牙突刺。战斗初始：EVASION 1。凝视聚焦：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"干扰凝视","status":"WEAK","stacks":1},{"type":"ACTION","action":"ATTACK","moveName":"长牙撕咬","amount":8,"hits":1},{"type":"ACTION","action":"ATTACK","moveName":"双牙突刺","amount":4,"hits":2}]}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.13]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"凝视聚焦","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"凝视聚焦","amount":8,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"凝视聚焦·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"凝视聚焦·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"长牙之眼·追击","amount":6,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>枝条史莱姆（小）</t>
+  </si>
+  <si>
+    <t>生命44；行动：冲撞。战斗初始：ARMOR 1。枝条硬化：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":4,"hits":1,"editorId":"sts2-50013-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.14]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"枝条硬化","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"枝条硬化","amount":4,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"枝条硬化·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"枝条硬化·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"枝条史莱姆（小）·追击","amount":3,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>毒气炸弹</t>
+  </si>
+  <si>
+    <t>生命40；行动：毒气压缩、泄漏毒雾、毒气喷射、引爆毒囊、爆炸自毁。战斗初始：ARMOR 1。毒气泄漏：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"&gt;=","value":3,"children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"引爆毒囊","amount":18,"hits":1},{"type":"ACTION","action":"LOSE_HP","moveName":"爆炸自毁","target":"ENEMY","amount":40}]}]},{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"毒气压缩","amount":4},{"type":"ACTION","action":"DEBUFF","moveName":"泄漏毒雾","status":"POISON","stacks":2}]},{"type":"ACTION","action":"ATTACK","moveName":"毒气喷射","amount":8,"hits":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"引爆毒囊","amount":18,"hits":1},{"type":"ACTION","action":"LOSE_HP","moveName":"爆炸自毁","target":"ENEMY","amount":40}]}]}]}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.15]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"毒气泄漏","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"&gt;=","value":3,"children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"引爆毒囊","amount":18,"hits":1},{"type":"ACTION","action":"LOSE_HP","moveName":"爆炸自毁","target":"ENEMY","amount":40}]}]},{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"毒气压缩","amount":4},{"type":"ACTION","action":"DEBUFF","moveName":"泄漏毒雾","status":"POISON","stacks":2}]},{"type":"ACTION","action":"ATTACK","moveName":"毒气喷射","amount":8,"hits":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"引爆毒囊","amount":18,"hits":1},{"type":"ACTION","action":"LOSE_HP","moveName":"爆炸自毁","target":"ENEMY","amount":40}]}]}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>鬼祟地精</t>
+  </si>
+  <si>
+    <t>生命48；行动：冲撞。战斗初始：EVASION 1。绝境冲撞：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":9,"hits":1,"editorId":"sts2-50015-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.16]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"绝境冲撞","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"绝境冲撞","amount":9,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"绝境冲撞·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"绝境冲撞·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"鬼祟地精·追击","amount":6,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>小墨灵</t>
+  </si>
+  <si>
+    <t>生命48；行动：刺拳、旋风连击、穿透凝视。战斗初始：EVASION 1。墨刺爆发：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"刺拳","amount":3,"hits":1,"editorId":"sts2-50016-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"旋风连击","amount":2,"hits":3,"editorId":"sts2-50016-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"穿透凝视","amount":10,"hits":1,"editorId":"sts2-50016-4","editorX":370,"editorY":555}],"editorId":"sts2-50016-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.17]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"墨刺爆发","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"墨刺爆发","amount":10,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"墨刺爆发·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"墨刺爆发·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"小墨灵·追击","amount":7,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>树叶史莱姆（小）</t>
+  </si>
+  <si>
+    <t>生命46；行动：冲撞、黏浆。战斗初始：REGENERATION 1。黏浆包裹：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":3,"hits":1,"editorId":"sts2-50017-2","editorX":370,"editorY":245},{"type":"ACTION","action":"DEBUFF","moveName":"黏浆","status":"CONSTRICTED","stacks":2}],"editorId":"sts2-50017-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.18]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"黏浆包裹","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":3}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"黏浆包裹","amount":3,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"黏浆包裹·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"黏浆包裹·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"树叶史莱姆（小）·追击","amount":3,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>肥胖地精</t>
+  </si>
+  <si>
+    <t>生命54；行动：护住钱袋、钱袋砸击、蛮横冲撞、闪身戒备。战斗初始：ARMOR 1。护住钱袋：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEFEND","moveName":"护住钱袋","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"钱袋砸击","amount":9,"hits":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蛮横冲撞","amount":6,"hits":1},{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":"EVASION","stacks":1}]}]}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.19]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"护住钱袋","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"护住钱袋","amount":9,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"护住钱袋·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"护住钱袋·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"肥胖地精·追击","amount":6,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>双尾鼠</t>
+  </si>
+  <si>
+    <t>生命56；行动：抓挠、疫病啃咬、尖啸·削弱、集中自身力量、强化自身护甲。战斗初始：EVASION 1。瘟牙激怒：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"抓挠","amount":8,"hits":1,"editorId":"sts2-50019-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"疫病啃咬","amount":6,"hits":1,"editorId":"sts2-50019-3","editorX":370,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"尖啸·削弱","status":"FRAIL","stacks":1,"editorId":"sts2-50019-4","editorX":370,"editorY":555},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"集中自身力量","status":"STRENGTH","stacks":1},{"type":"ACTION","action":"DEFEND","moveName":"强化自身护甲","amount":6}]}],"editorId":"sts2-50019-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.20]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"瘟牙激怒","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"瘟牙激怒","amount":8,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"瘟牙激怒·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"瘟牙激怒·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"双尾鼠·追击","amount":6,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>蠕动虫</t>
+  </si>
+  <si>
+    <t>生命52；行动：恶毒啃咬、蠕动·强化。战斗初始：REGENERATION 2。蠕动蜕皮：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"恶毒啃咬","amount":6,"hits":1,"editorId":"sts2-50020-2","editorX":370,"editorY":245},{"type":"ACTION","action":"BUFF","moveName":"蠕动·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50020-3","editorX":370,"editorY":400}],"editorId":"sts2-50020-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.21]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"蠕动蜕皮","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":3}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蠕动蜕皮","amount":6,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"蠕动蜕皮·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"蠕动蜕皮·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"蠕动虫·追击","amount":4,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>粉碎者</t>
+  </si>
+  <si>
+    <t>生命200；行动：乱击、膨胀打击、虫刺、虫刺·削弱、适应·强化、防御打击、防御打击·格挡。战斗初始：PLATED_ARMOR 4。碎壳适应：生命≤65%进入，阶段仅触发一次，切换招式。碎壳适应·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":12,"hits":1,"editorId":"sts2-50021-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"膨胀打击","amount":4,"hits":1,"editorId":"sts2-50021-3","editorX":370,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"虫刺","amount":6,"hits":2,"editorId":"sts2-50021-5","editorX":670,"editorY":710},{"type":"ACTION","action":"DEBUFF","moveName":"虫刺·削弱","status":"WEAK","stacks":2,"editorId":"sts2-50021-6","editorX":670,"editorY":865},{"type":"ACTION","action":"DEBUFF","moveName":"虫刺·削弱","status":"FRAIL","stacks":2,"editorId":"sts2-50021-7","editorX":670,"editorY":1020}],"editorId":"sts2-50021-4","editorX":370,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"适应·强化","status":"STRENGTH","stacks":2,"editorId":"sts2-50021-8","editorX":370,"editorY":1175},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"防御打击","amount":12,"hits":1,"editorId":"sts2-50021-10","editorX":670,"editorY":1485},{"type":"ACTION","action":"DEFEND","moveName":"防御打击·格挡","amount":16,"editorId":"sts2-50021-11","editorX":670,"editorY":1640}],"editorId":"sts2-50021-9","editorX":370,"editorY":1330}],"editorId":"sts2-50021-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.22]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":4,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"碎壳适应","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":12}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"碎壳适应","amount":12,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"碎壳适应·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"碎壳适应·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"粉碎者·追击","amount":9,"hits":1}]}},{"id":"phase2","name":"碎壳适应·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"碎壳适应·终局","amount":12,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"碎壳适应·终局·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"碎壳适应·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"粉碎者·追击","amount":9,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>红宝石劫掠者（弩手）</t>
+  </si>
+  <si>
+    <t>生命56；行动：装填·格挡、射击。战斗初始：EVASION 1。穿甲弩击：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEFEND","moveName":"装填·格挡","amount":3,"editorId":"sts2-50022-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"射击","amount":14,"hits":1,"editorId":"sts2-50022-3","editorX":370,"editorY":400}],"editorId":"sts2-50022-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.23]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"穿甲弩击","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"穿甲弩击","amount":14,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"穿甲弩击·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"穿甲弩击·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"红宝石劫掠者（弩手）·追击","amount":10,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>幼虫</t>
+  </si>
+  <si>
+    <t>生命48；行动：轻咬。战斗初始：REGENERATION 1。饥饿轻咬：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"ACTION","action":"ATTACK","moveName":"轻咬","amount":4,"hits":1,"editorId":"sts2-50023-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.24]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"饥饿轻咬","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":3}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"饥饿轻咬","amount":4,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"饥饿轻咬·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"饥饿轻咬·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"幼虫·追击","amount":3,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>护卫机器人</t>
+  </si>
+  <si>
+    <t>生命58；行动：护盾展开、盾击反攻、稳住盾面、铁臂重击。战斗初始：PLATED_ARMOR 3。护卫反击：生命≤40%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEFEND","moveName":"护盾展开","amount":8},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"盾击反攻","amount":8,"hits":1},{"type":"ACTION","action":"DEFEND","moveName":"稳住盾面","amount":4}]},{"type":"ACTION","action":"ATTACK","moveName":"铁臂重击","amount":10,"hits":1}]}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.25]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"护卫反击","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"护卫反击","amount":10,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"护卫反击·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"护卫反击·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"护卫机器人·追击","amount":7,"hits":1}]}}],"triggers":[{"event":"ON_SKILL_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":"BLOCK","target":"SELF","params":{"amount":2}}]}]}</t>
+  </si>
+  <si>
+    <t>幻惧灵</t>
+  </si>
+  <si>
+    <t>生命54；行动：猛击。战斗初始：EVASION 1。恐惧具象：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"ACTION","action":"ATTACK","moveName":"猛击","amount":16,"hits":1,"editorId":"sts2-50025-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.26]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"恐惧具象","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"恐惧具象","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"恐惧具象·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"恐惧具象·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"幻惧灵·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>红宝石劫掠者（追踪者）</t>
+  </si>
+  <si>
+    <t>生命56；行动：追踪·削弱、猎犬突袭。战斗初始：EVASION 1。锁定猎物：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"DEBUFF","moveName":"追踪·削弱","status":"FRAIL","stacks":2,"editorId":"sts2-50026-3","editorX":670,"editorY":400}],"editorId":"sts2-50026-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"猎犬突袭","amount":3,"hits":3,"editorId":"sts2-50026-4","editorX":370,"editorY":555}],"editorId":"sts2-50026-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.27]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"锁定猎物","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"锁定猎物","amount":3,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"锁定猎物·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"锁定猎物·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"红宝石劫掠者（追踪者）·追击","amount":3,"hits":3}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>蝌蚪</t>
+  </si>
+  <si>
+    <t>生命52；行动：生长尖刺·强化、尖刺喷吐、旋转。战斗初始：THORNS 1。棘刺成熟：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"BUFF","moveName":"生长尖刺·强化","status":"THORNS","stacks":1,"editorId":"sts2-50027-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"尖刺喷吐","amount":3,"hits":3,"editorId":"sts2-50027-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"旋转","amount":7,"hits":1,"editorId":"sts2-50027-4","editorX":370,"editorY":555}],"editorId":"sts2-50027-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.28]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"THORNS","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"棘刺成熟","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"FRAIL","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"棘刺成熟","amount":3,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"棘刺成熟·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"棘刺成熟·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"蝌蚪·追击","amount":3,"hits":3}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>噪音机器人</t>
+  </si>
+  <si>
+    <t>生命54；行动：干扰噪音、声波冲击、高频震荡、震荡失衡。战斗初始：ARTIFACT 1。噪音过载：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"干扰噪音","status":"WEAK","stacks":1},{"type":"ACTION","action":"ATTACK","moveName":"声波冲击","amount":3,"hits":3},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"高频震荡","amount":7,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"震荡失衡","status":"FRAIL","stacks":1}]}]}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.29]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"噪音过载","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"噪音过载","amount":3,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"噪音过载·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"噪音过载·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"噪音机器人·追击","amount":3,"hits":3}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>刺击机器人</t>
+  </si>
+  <si>
+    <t>生命56；行动：刺击、刺击·脆弱。战斗初始：PLATED_ARMOR 2。针刺加压：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"刺击","amount":11,"hits":1,"editorId":"sts2-50029-2","editorX":370,"editorY":245},{"type":"ACTION","action":"DEBUFF","moveName":"刺击·脆弱","status":"FRAIL","stacks":1,"editorId":"sts2-50029-3","editorX":370,"editorY":400}],"editorId":"sts2-50029-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.30]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"针刺加压","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"针刺加压","amount":11,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"针刺加压·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"针刺加压·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"刺击机器人·追击","amount":8,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>电击机器人</t>
+  </si>
+  <si>
+    <t>生命58；行动：电击、高压电·力量。战斗初始：ARTIFACT 1。高压电流：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"电击","amount":14,"hits":1,"editorId":"sts2-50030-2","editorX":370,"editorY":245},{"type":"ACTION","action":"BUFF","moveName":"高压电·力量","status":"STRENGTH","stacks":1,"editorId":"sts2-50030-3","editorX":370,"editorY":400}],"editorId":"sts2-50030-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.31]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"高压电流","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"高压电流","amount":14,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"高压电流·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"高压电流·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"电击机器人·追击","amount":10,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>灵魂鱼</t>
+  </si>
+  <si>
+    <t>生命210；行动：集中自身力量、强化自身护甲、排气、凝视、隐没·无实体、尖叫、尖叫·削弱。战斗初始：REGENERATION 2。魂潮显形：生命≤65%进入，阶段仅触发一次，切换招式。魂潮显形·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"集中自身力量","status":"STRENGTH","stacks":2},{"type":"ACTION","action":"DEFEND","moveName":"强化自身护甲","amount":6}]},{"type":"ACTION","action":"ATTACK","moveName":"排气","amount":16,"hits":1,"editorId":"sts2-50031-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"凝视","amount":7,"hits":1,"editorId":"sts2-50031-4","editorX":370,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"隐没·无实体","status":"INTANGIBLE","stacks":1,"editorId":"sts2-50031-5","editorX":370,"editorY":710,"duration":"NEXT_TURN"},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"尖叫","amount":11,"hits":1,"editorId":"sts2-50031-7","editorX":670,"editorY":1020},{"type":"ACTION","action":"DEBUFF","moveName":"尖叫·削弱","status":"VULNERABLE","stacks":3,"editorId":"sts2-50031-8","editorX":670,"editorY":1175}],"editorId":"sts2-50031-6","editorX":370,"editorY":865}],"editorId":"sts2-50031-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.32]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"魂潮显形","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":9}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"魂潮显形","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"魂潮显形·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"魂潮显形·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"灵魂鱼·追击","amount":12,"hits":1}]}},{"id":"phase2","name":"魂潮显形·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"魂潮显形·终局","amount":12,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"魂潮显形·终局·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"魂潮显形·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"灵魂鱼·追击","amount":9,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>外骨骼虫</t>
+  </si>
+  <si>
+    <t>生命54；行动：疾行、颚击、狂怒·强化。战斗初始：ARMOR 2。外壳剥落：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"疾行","amount":3,"hits":3,"editorId":"sts2-50032-3","editorX":670,"editorY":400}],"editorId":"sts2-50032-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"疾行","amount":3,"hits":3,"editorId":"sts2-50032-5","editorX":670,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"颚击","amount":8,"hits":1,"editorId":"sts2-50032-6","editorX":670,"editorY":865},{"type":"ACTION","action":"BUFF","moveName":"狂怒·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50032-7","editorX":670,"editorY":1020}],"editorId":"sts2-50032-4","editorX":370,"editorY":555}],"editorId":"sts2-50032-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.33]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"外壳剥落","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"外壳剥落","amount":3,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"外壳剥落·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"外壳剥落·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"外骨骼虫·追击","amount":3,"hits":3}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>尸蛞蝓</t>
+  </si>
+  <si>
+    <t>生命56；行动：鞭打、猛扑、黏液喷吐·削弱。战斗初始：REGENERATION 2。尸液沸腾：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"鞭打","amount":3,"hits":2,"editorId":"sts2-50033-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"猛扑","amount":8,"hits":1,"editorId":"sts2-50033-3","editorX":370,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"黏液喷吐·削弱","status":"FRAIL","stacks":2,"editorId":"sts2-50033-4","editorX":370,"editorY":555}],"editorId":"sts2-50033-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.34]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"尸液沸腾","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":3}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"尸液沸腾","amount":8,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"尸液沸腾·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"尸液沸腾·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"尸蛞蝓·追击","amount":6,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>枝条史莱姆（中）</t>
+  </si>
+  <si>
+    <t>生命60；行动：黏液弹、黏团弹。战斗初始：ARMOR 1。黏液浓缩：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"DEBUFF","moveName":"黏液弹","status":"CONSTRICTED","stacks":2}],"editorId":"sts2-50034-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"黏团弹","amount":11,"hits":1,"editorId":"sts2-50034-5","editorX":670,"editorY":710},{"type":"ACTION","action":"DEBUFF","moveName":"黏液弹","status":"CONSTRICTED","stacks":2}],"editorId":"sts2-50034-4","editorX":370,"editorY":555}],"editorId":"sts2-50034-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.35]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"黏液浓缩","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"黏液浓缩","amount":11,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"黏液浓缩·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"黏液浓缩·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"枝条史莱姆（中）·追击","amount":8,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>幻影园丁</t>
+  </si>
+  <si>
+    <t>生命96；行动：啃咬、鞭击、链锤乱击、膨大·强化。战斗初始：REGENERATION 2。根须暴长：生命≤50%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"啃咬","amount":6,"hits":1,"editorId":"sts2-50035-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"鞭击","amount":7,"hits":1,"editorId":"sts2-50035-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"链锤乱击","amount":3,"hits":3,"editorId":"sts2-50035-4","editorX":370,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"膨大·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50035-5","editorX":370,"editorY":710}],"editorId":"sts2-50035-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.36]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"根须暴长","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":6}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"根须暴长","amount":3,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"根须暴长·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"根须暴长·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"幻影园丁·追击","amount":3,"hits":3}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>红宝石劫掠者（蛮兵）</t>
+  </si>
+  <si>
+    <t>生命62；行动：殴打、咆哮·强化。战斗初始：FURY 1。蛮兵怒吼：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"殴打","amount":7,"hits":1,"editorId":"sts2-50036-2","editorX":370,"editorY":245},{"type":"ACTION","action":"BUFF","moveName":"咆哮·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50036-3","editorX":370,"editorY":400}],"editorId":"sts2-50036-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.37]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FURY","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"蛮兵怒吼","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蛮兵怒吼","amount":7,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"蛮兵怒吼·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"蛮兵怒吼·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"红宝石劫掠者（蛮兵）·追击","amount":5,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>噬咬卷轴</t>
+  </si>
+  <si>
+    <t>生命64；行动：猛咬、咀嚼、增生利齿·强化。战斗初始：FURY 1。利齿增生：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"猛咬","amount":14,"hits":1,"editorId":"sts2-50037-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"咀嚼","amount":5,"hits":2,"editorId":"sts2-50037-3","editorX":370,"editorY":400},{"type":"ACTION","action":"BUFF","moveName":"增生利齿·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50037-4","editorX":370,"editorY":555}],"editorId":"sts2-50037-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.38]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FURY","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"利齿增生","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"利齿增生","amount":14,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"利齿增生·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"利齿增生·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"噬咬卷轴·追击","amount":10,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>咬合杰克果</t>
+  </si>
+  <si>
+    <t>生命60；行动：能量球、能量球·强化。战斗初始：ARTIFACT 1。果核充能：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"能量球","amount":3,"hits":1,"editorId":"sts2-50038-2","editorX":370,"editorY":245},{"type":"ACTION","action":"BUFF","moveName":"能量球·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50038-3","editorX":370,"editorY":400}],"editorId":"sts2-50038-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.39]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"果核充能","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"果核充能","amount":3,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"果核充能·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"果核充能·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"咬合杰克果·追击","amount":3,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>树叶史莱姆（中）</t>
+  </si>
+  <si>
+    <t>生命62；行动：黏液弹、黏团弹。战斗初始：REGENERATION 2。叶片包裹：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"黏液弹","status":"CONSTRICTED","stacks":2},{"type":"ACTION","action":"ATTACK","moveName":"黏团弹","amount":8,"hits":1,"editorId":"sts2-50039-3","editorX":370,"editorY":400}],"editorId":"sts2-50039-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.40]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"叶片包裹","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":3}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"叶片包裹","amount":8,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"叶片包裹·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"叶片包裹·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"树叶史莱姆（中）·追击","amount":6,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>盛碗虫（蜜）</t>
+  </si>
+  <si>
+    <t>生命60；行动：乱击、强化·强化。战斗初始：REGENERATION 2。蜜糖硬化：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":6,"hits":1,"editorId":"sts2-50040-3","editorX":670,"editorY":400}],"editorId":"sts2-50040-2","editorX":370,"editorY":245},{"type":"CONDITION","field":"TURN","operator":"==","value":2,"children":[{"type":"ACTION","action":"BUFF","moveName":"强化·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50040-5","editorX":670,"editorY":710}],"editorId":"sts2-50040-4","editorX":370,"editorY":555},{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":6,"hits":1,"editorId":"sts2-50040-6","editorX":370,"editorY":865}],"editorId":"sts2-50040-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.41]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"蜜糖硬化","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":3}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蜜糖硬化","amount":6,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"蜜糖硬化·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"蜜糖硬化·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"盛碗虫（蜜）·追击","amount":4,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>拉加维林族母</t>
+  </si>
+  <si>
+    <t>生命220；行动：斩击、开膛、斩击二式、斩击二式·格挡、灵魂虹吸·易伤、灵魂虹吸·脆弱、灵魂虹吸·强化。战斗初始：ARMOR 3。虹吸盛宴：生命≤65%进入，阶段仅触发一次，切换招式。虹吸盛宴·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"斩击","amount":19,"hits":1,"editorId":"sts2-50041-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"开膛","amount":9,"hits":2,"editorId":"sts2-50041-3","editorX":370,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"斩击二式","amount":12,"hits":1,"editorId":"sts2-50041-5","editorX":670,"editorY":710},{"type":"ACTION","action":"DEFEND","moveName":"斩击二式·格挡","amount":12,"editorId":"sts2-50041-6","editorX":670,"editorY":865}],"editorId":"sts2-50041-4","editorX":370,"editorY":555},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"灵魂虹吸·易伤","status":"VULNERABLE","stacks":1,"editorId":"sts2-50041-8","editorX":670,"editorY":1175},{"type":"ACTION","action":"DEBUFF","moveName":"灵魂虹吸·脆弱","status":"FRAIL","stacks":1,"editorId":"sts2-50041-9","editorX":670,"editorY":1330},{"type":"ACTION","action":"BUFF","moveName":"灵魂虹吸·强化","status":"STRENGTH","stacks":2,"editorId":"sts2-50041-10","editorX":670,"editorY":1485}],"editorId":"sts2-50041-7","editorX":370,"editorY":1020}],"editorId":"sts2-50041-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.42]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"虹吸盛宴","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":12}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"虹吸盛宴","amount":19,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"虹吸盛宴·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"虹吸盛宴·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"拉加维林族母·追击","amount":14,"hits":1}]}},{"id":"phase2","name":"虹吸盛宴·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"虹吸盛宴·终局","amount":12,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"虹吸盛宴·终局·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"虹吸盛宴·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"拉加维林族母·追击","amount":9,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>淤泥纺织者</t>
+  </si>
+  <si>
+    <t>生命64；行动：喷油、猛击、暴怒、暴怒·强化。战斗初始：ARMOR 1。淤泥凝结：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"喷油","amount":8,"hits":1,"editorId":"sts2-50042-3","editorX":670,"editorY":400}],"editorId":"sts2-50042-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"喷油","amount":8,"hits":1,"editorId":"sts2-50042-5","editorX":670,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"猛击","amount":11,"hits":1,"editorId":"sts2-50042-6","editorX":670,"editorY":865},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"暴怒","amount":6,"hits":1,"editorId":"sts2-50042-8","editorX":970,"editorY":1175},{"type":"ACTION","action":"BUFF","moveName":"暴怒·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50042-9","editorX":970,"editorY":1330}],"editorId":"sts2-50042-7","editorX":670,"editorY":1020}],"editorId":"sts2-50042-4","editorX":370,"editorY":555}],"editorId":"sts2-50042-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.43]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"淤泥凝结","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"淤泥凝结","amount":11,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"淤泥凝结·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"淤泥凝结·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"淤泥纺织者·追击","amount":8,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>钙化教徒</t>
+  </si>
+  <si>
+    <t>生命62；行动：吟唱·仪式、暗影打击。战斗初始：RITUAL 1。骨符共鸣：生命≤40%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"BUFF","moveName":"吟唱·仪式","status":"STRENGTH","stacks":1,"editorId":"sts2-50043-3","editorX":670,"editorY":400}],"editorId":"sts2-50043-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"暗影打击","amount":9,"hits":1,"editorId":"sts2-50043-4","editorX":370,"editorY":555}],"editorId":"sts2-50043-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.44]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"RITUAL","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"骨符共鸣","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"骨符共鸣","amount":9,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"骨符共鸣·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"骨符共鸣·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"钙化教徒·追击","amount":6,"hits":1}]}}],"triggers":[{"event":"ON_POWER_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}}]}]}</t>
+  </si>
+  <si>
+    <t>缩小甲虫</t>
+  </si>
+  <si>
+    <t>生命60；行动：缩小术·脆弱、猛咬、跺击。战斗初始：EVASION 1。缩小遁形：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"缩小术·脆弱","status":"FRAIL","stacks":1,"editorId":"sts2-50044-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"猛咬","amount":7,"hits":1,"editorId":"sts2-50044-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"跺击","amount":13,"hits":1,"editorId":"sts2-50044-4","editorX":370,"editorY":555}],"editorId":"sts2-50044-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.45]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"缩小遁形","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"FRAIL","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"缩小遁形","amount":13,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"缩小遁形·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"缩小遁形·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"缩小甲虫·追击","amount":9,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>炮塔操作员</t>
+  </si>
+  <si>
+    <t>生命64；行动：倾泻火力、装填·强化。战斗初始：PLATED_ARMOR 2。火力倾泻：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"倾泻火力","amount":3,"hits":3,"editorId":"sts2-50045-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"倾泻火力","amount":3,"hits":3,"editorId":"sts2-50045-3","editorX":370,"editorY":400},{"type":"ACTION","action":"BUFF","moveName":"装填·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50045-4","editorX":370,"editorY":555}],"editorId":"sts2-50045-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.46]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"火力倾泻","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"火力倾泻","amount":3,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"火力倾泻·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"火力倾泻·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"炮塔操作员·追击","amount":3,"hits":3}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>千足虫</t>
+  </si>
+  <si>
+    <t>生命105；行动：扭动攻击、壮大、壮大·力量、紧缚、紧缚·虚弱。战斗初始：ARMOR 2。节壳翻涌：生命≤50%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"扭动攻击","amount":5,"hits":2,"editorId":"sts2-50046-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"壮大","amount":6,"hits":1,"editorId":"sts2-50046-4","editorX":670,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"壮大·力量","status":"STRENGTH","stacks":1,"editorId":"sts2-50046-5","editorX":670,"editorY":710}],"editorId":"sts2-50046-3","editorX":370,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"紧缚","amount":8,"hits":1,"editorId":"sts2-50046-7","editorX":670,"editorY":1020},{"type":"ACTION","action":"DEBUFF","moveName":"紧缚·虚弱","status":"WEAK","stacks":1,"editorId":"sts2-50046-8","editorX":670,"editorY":1175}],"editorId":"sts2-50046-6","editorX":370,"editorY":865}],"editorId":"sts2-50046-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.47]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"节壳翻涌","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":8}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"节壳翻涌","amount":5,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"节壳翻涌·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"节壳翻涌·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"千足虫·追击","amount":3,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>啃咬虫</t>
+  </si>
+  <si>
+    <t>生命66；行动：头槌、切割、切割·格挡、嘶鸣·强化。战斗初始：FURY 1。甲颚狂怒：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"头槌","amount":12,"hits":1,"editorId":"sts2-50047-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"切割","amount":6,"hits":1,"editorId":"sts2-50047-4","editorX":670,"editorY":555},{"type":"ACTION","action":"DEFEND","moveName":"切割·格挡","amount":5,"editorId":"sts2-50047-5","editorX":670,"editorY":710}],"editorId":"sts2-50047-3","editorX":370,"editorY":400},{"type":"ACTION","action":"BUFF","moveName":"嘶鸣·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50047-6","editorX":370,"editorY":865}],"editorId":"sts2-50047-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.48]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FURY","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"甲颚狂怒","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"甲颚狂怒","amount":12,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"甲颚狂怒·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"甲颚狂怒·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"啃咬虫·追击","amount":9,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>海朋克</t>
+  </si>
+  <si>
+    <t>生命66；行动：海潮踢、回旋踢、气泡嗝·格挡、气泡嗝·强化。战斗初始：EVASION 1。潮汐回旋：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"海潮踢","amount":11,"hits":1,"editorId":"sts2-50048-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"回旋踢","amount":2,"hits":3,"editorId":"sts2-50048-3","editorX":370,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"气泡嗝·格挡","amount":7,"editorId":"sts2-50048-5","editorX":670,"editorY":710},{"type":"ACTION","action":"BUFF","moveName":"气泡嗝·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50048-6","editorX":670,"editorY":865}],"editorId":"sts2-50048-4","editorX":370,"editorY":555}],"editorId":"sts2-50048-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.49]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"潮汐回旋","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"潮汐回旋","amount":11,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"潮汐回旋·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"潮汐回旋·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"海朋克·追击","amount":8,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>盛碗虫（岩）</t>
+  </si>
+  <si>
+    <t>生命62；行动：头槌、眩晕。战斗初始：ARMOR 3。岩壳碎裂：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"头槌","amount":15,"hits":1,"editorId":"sts2-50049-2","editorX":370,"editorY":245},{"type":"ACTION","action":"WAIT","moveName":"眩晕","editorId":"sts2-50049-3","editorX":370,"editorY":400}],"editorId":"sts2-50049-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.50]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"岩壳碎裂","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"岩壳碎裂","amount":15,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"岩壳碎裂·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"岩壳碎裂·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"盛碗虫（岩）·追击","amount":11,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>飞菇</t>
+  </si>
+  <si>
+    <t>生命68；行动：脆弱孢子、脆弱孢子·削弱、重击、易伤孢子·削弱。战斗初始：REGENERATION 1。孢子成熟：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"脆弱孢子","amount":8,"hits":1,"editorId":"sts2-50050-3","editorX":670,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"脆弱孢子·削弱","status":"FRAIL","stacks":2,"editorId":"sts2-50050-4","editorX":670,"editorY":555}],"editorId":"sts2-50050-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"重击","amount":11,"hits":1,"editorId":"sts2-50050-5","editorX":370,"editorY":710},{"type":"ACTION","action":"DEBUFF","moveName":"易伤孢子·削弱","status":"VULNERABLE","stacks":2,"editorId":"sts2-50050-6","editorX":370,"editorY":865}],"editorId":"sts2-50050-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.51]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"孢子成熟","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":3}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"孢子成熟","amount":11,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"孢子成熟·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"孢子成熟·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"飞菇·追击","amount":8,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>瀑布巨人</t>
+  </si>
+  <si>
+    <t>生命230；行动：蓄势护体、蓄势增压、跺击、跺击·削弱、猛撞、虹吸·治疗、高压水枪、增压。战斗初始：ARMOR 3。洪流增压：生命≤65%进入，阶段仅触发一次，切换招式。洪流增压·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"蓄势护体","amount":8},{"type":"ACTION","action":"BUFF","moveName":"蓄势增压","status":"STRENGTH","stacks":2}]},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"跺击","amount":15,"hits":1,"editorId":"sts2-50051-4","editorX":670,"editorY":555},{"type":"ACTION","action":"DEBUFF","moveName":"跺击·削弱","status":"WEAK","stacks":1,"editorId":"sts2-50051-5","editorX":670,"editorY":710}],"editorId":"sts2-50051-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"猛撞","amount":10,"hits":1,"editorId":"sts2-50051-6","editorX":370,"editorY":865},{"type":"ACTION","action":"HEAL","moveName":"虹吸·治疗","amount":12,"editorId":"sts2-50051-7","editorX":370,"editorY":1020},{"type":"ACTION","action":"ATTACK","moveName":"高压水枪","amount":20,"hits":1,"editorId":"sts2-50051-8","editorX":370,"editorY":1175},{"type":"ACTION","action":"ATTACK","moveName":"增压","amount":13,"hits":1,"editorId":"sts2-50051-9","editorX":370,"editorY":1330}],"editorId":"sts2-50051-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.52]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"洪流增压","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":12}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"洪流增压","amount":20,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"洪流增压·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"洪流增压·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"瀑布巨人·追击","amount":15,"hits":1}]}},{"id":"phase2","name":"洪流增压·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"洪流增压·终局","amount":12,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"洪流增压·终局·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"洪流增压·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"瀑布巨人·追击","amount":9,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>地精佣兵</t>
+  </si>
+  <si>
+    <t>生命72；行动：交出来、双重猛击、双重猛击·削弱、嘿嘿、嘿嘿·强化。战斗初始：EVASION 1。佣兵死斗：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"交出来","amount":7,"hits":2,"editorId":"sts2-50052-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"双重猛击","amount":6,"hits":2,"editorId":"sts2-50052-4","editorX":670,"editorY":555},{"type":"ACTION","action":"DEBUFF","moveName":"双重猛击·削弱","status":"WEAK","stacks":2,"editorId":"sts2-50052-5","editorX":670,"editorY":710}],"editorId":"sts2-50052-3","editorX":370,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"嘿嘿","amount":8,"hits":1,"editorId":"sts2-50052-7","editorX":670,"editorY":1020},{"type":"ACTION","action":"BUFF","moveName":"嘿嘿·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50052-8","editorX":670,"editorY":1175}],"editorId":"sts2-50052-6","editorX":370,"editorY":865}],"editorId":"sts2-50052-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.53]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"佣兵死斗","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"佣兵死斗","amount":7,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"佣兵死斗·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"佣兵死斗·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"地精佣兵·追击","amount":5,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>潮湿教徒</t>
+  </si>
+  <si>
+    <t>生命70；行动：吟唱·仪式、暗影打击。战斗初始：RITUAL 1。潮湿祈祷：生命≤40%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"BUFF","moveName":"吟唱·仪式","status":"STRENGTH","stacks":1,"editorId":"sts2-50053-3","editorX":670,"editorY":400}],"editorId":"sts2-50053-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"暗影打击","amount":6,"hits":1,"editorId":"sts2-50053-4","editorX":370,"editorY":555}],"editorId":"sts2-50053-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.54]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"RITUAL","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"潮湿祈祷","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"FRAIL","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"潮湿祈祷","amount":6,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"潮湿祈祷·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"潮湿祈祷·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"潮湿教徒·追击","amount":4,"hits":1}]}}],"triggers":[{"event":"ON_POWER_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}}]}]}</t>
+  </si>
+  <si>
+    <t>化石潜猎者</t>
+  </si>
+  <si>
+    <t>生命72；行动：咬住、冲撞、冲撞·削弱、鞭击。战斗初始：ARMOR 2。化石开裂：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"咬住","amount":12,"hits":1,"editorId":"sts2-50054-3","editorX":670,"editorY":400}],"editorId":"sts2-50054-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"咬住","amount":12,"hits":1,"editorId":"sts2-50054-5","editorX":670,"editorY":710},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":9,"hits":1,"editorId":"sts2-50054-7","editorX":970,"editorY":1020},{"type":"ACTION","action":"DEBUFF","moveName":"冲撞·削弱","status":"FRAIL","stacks":1,"editorId":"sts2-50054-8","editorX":970,"editorY":1175}],"editorId":"sts2-50054-6","editorX":670,"editorY":865},{"type":"ACTION","action":"ATTACK","moveName":"鞭击","amount":3,"hits":2,"editorId":"sts2-50054-9","editorX":670,"editorY":1330}],"editorId":"sts2-50054-4","editorX":370,"editorY":555}],"editorId":"sts2-50054-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.55]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"化石开裂","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"化石开裂","amount":12,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"化石开裂·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"化石开裂·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"化石潜猎者·追击","amount":9,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>游蛇绞杀者</t>
+  </si>
+  <si>
+    <t>生命70；行动：紧缚·虚弱、抽打、抽打·格挡、鞭击。战斗初始：EVASION 1。绞杀收紧：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"紧缚·虚弱","status":"WEAK","stacks":1,"editorId":"sts2-50055-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"抽打","amount":7,"hits":1,"editorId":"sts2-50055-4","editorX":670,"editorY":555},{"type":"ACTION","action":"DEFEND","moveName":"抽打·格挡","amount":5,"editorId":"sts2-50055-5","editorX":670,"editorY":710}],"editorId":"sts2-50055-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"鞭击","amount":12,"hits":1,"editorId":"sts2-50055-6","editorX":370,"editorY":865}],"editorId":"sts2-50055-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.56]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"绞杀收紧","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"CONSTRICTED","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"绞杀收紧","amount":12,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"绞杀收紧·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"绞杀收紧·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"游蛇绞杀者·追击","amount":9,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>绒毛蠕虫</t>
+  </si>
+  <si>
+    <t>生命74；行动：酸液黏浆、吸气·强化。战斗初始：REGENERATION 2。鼓胀吐酸：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"酸液黏浆","amount":4,"hits":1,"editorId":"sts2-50056-2","editorX":370,"editorY":245},{"type":"ACTION","action":"BUFF","moveName":"吸气·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50056-3","editorX":370,"editorY":400}],"editorId":"sts2-50056-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.57]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"鼓胀吐酸","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":3}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"鼓胀吐酸","amount":4,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"鼓胀吐酸·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"鼓胀吐酸·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"绒毛蠕虫·追击","amount":3,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>活体盾牌</t>
+  </si>
+  <si>
+    <t>生命76；行动：盾击、重击、重击·强化。战斗初始：PLATED_ARMOR 3。盾面反击：生命≤40%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"盾击","amount":6,"hits":1,"editorId":"sts2-50057-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"重击","amount":16,"hits":1,"editorId":"sts2-50057-4","editorX":670,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"重击·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50057-5","editorX":670,"editorY":710}],"editorId":"sts2-50057-3","editorX":370,"editorY":400}],"editorId":"sts2-50057-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.58]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"盾面反击","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"盾面反击","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"盾面反击·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"盾面反击·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"活体盾牌·追击","amount":12,"hits":1}]}}],"triggers":[{"event":"ON_SKILL_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":"BLOCK","target":"SELF","params":{"amount":2}}]}]}</t>
+  </si>
+  <si>
+    <t>眷族追随者</t>
+  </si>
+  <si>
+    <t>生命180；行动：迅捷斩击、回旋斩、力量之舞。战斗初始：ARTIFACT 1。眷族觉醒：生命≤65%进入，阶段仅触发一次，切换招式。眷族觉醒·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"迅捷斩击","amount":6,"hits":1,"editorId":"sts2-50058-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"回旋斩","amount":3,"hits":2,"editorId":"sts2-50058-3","editorX":370,"editorY":400},{"type":"ACTION","action":"BUFF","moveName":"力量之舞","status":"STRENGTH","stacks":2,"editorId":"sts2-50058-4","editorX":370,"editorY":555}],"editorId":"sts2-50058-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.59]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"眷族觉醒","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"眷族觉醒","amount":6,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"眷族觉醒·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"眷族觉醒·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"眷族追随者·追击","amount":4,"hits":1}]}},{"id":"phase2","name":"眷族觉醒·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"眷族觉醒·终局","amount":6,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"眷族觉醒·终局·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"眷族觉醒·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"眷族追随者·追击","amount":4,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>巨口兽</t>
+  </si>
+  <si>
+    <t>生命78；行动：钳击、尖啸。战斗初始：FURY 1。巨口撕扯：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"钳击","amount":8,"hits":2,"editorId":"sts2-50059-2","editorX":370,"editorY":245},{"type":"ACTION","action":"DEBUFF","moveName":"尖啸","status":"WEAK","stacks":2}],"editorId":"sts2-50059-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.60]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FURY","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"巨口撕扯","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"巨口撕扯","amount":8,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"巨口撕扯·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"巨口撕扯·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"巨口兽·追击","amount":6,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>螨虫</t>
+  </si>
+  <si>
+    <t>生命74；行动：毒液、啃咬、吸吮、吸吮·强化。战斗初始：EVASION 1。螨毒扩散：生命≤40%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"毒液","status":"POISON","stacks":2},{"type":"ACTION","action":"ATTACK","moveName":"啃咬","amount":13,"hits":1,"editorId":"sts2-50060-3","editorX":370,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"吸吮","amount":4,"hits":1,"editorId":"sts2-50060-5","editorX":670,"editorY":710},{"type":"ACTION","action":"BUFF","moveName":"吸吮·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50060-6","editorX":670,"editorY":865}],"editorId":"sts2-50060-4","editorX":370,"editorY":555}],"editorId":"sts2-50060-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.61]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"螨毒扩散","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"螨毒扩散","amount":13,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"螨毒扩散·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"螨毒扩散·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"螨虫·追击","amount":9,"hits":1}]}}],"triggers":[{"event":"ON_DAMAGE_DEALT","listenSide":"ENEMY","limit":6,"filter":{"damageKind":"ATTACK"},"effects":[{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":1,"duration":"DEFAULT"}}]}]}</t>
+  </si>
+  <si>
+    <t>仪式巨兽</t>
+  </si>
+  <si>
+    <t>生命240；行动：践踏、震地虚弱、巨兽咆哮·虚弱、跺击、碾压、碾压·强化、犁地、犁地·强化。战斗初始：RITUAL 1。仪式狂热：生命≤65%进入，阶段仅触发一次，切换招式。仪式狂热·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"践踏","amount":12,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"震地虚弱","status":"WEAK","stacks":1}]}],"editorId":"sts2-50061-2","editorX":370,"editorY":245},{"type":"CONDITION","field":"SELF_HP_PERCENT","operator":"&lt;=","value":60,"children":[{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"巨兽咆哮·虚弱","status":"WEAK","stacks":1,"editorId":"sts2-50061-6","editorX":970,"editorY":865},{"type":"ACTION","action":"ATTACK","moveName":"跺击","amount":15,"hits":1,"editorId":"sts2-50061-7","editorX":970,"editorY":1020},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"碾压","amount":17,"hits":1,"editorId":"sts2-50061-9","editorX":1270,"editorY":1330},{"type":"ACTION","action":"BUFF","moveName":"碾压·强化","status":"STRENGTH","stacks":2,"editorId":"sts2-50061-10","editorX":1270,"editorY":1485}],"editorId":"sts2-50061-8","editorX":970,"editorY":1175}],"editorId":"sts2-50061-5","editorX":670,"editorY":710}],"editorId":"sts2-50061-4","editorX":370,"editorY":555},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"犁地","amount":18,"hits":1,"editorId":"sts2-50061-12","editorX":670,"editorY":1795},{"type":"ACTION","action":"BUFF","moveName":"犁地·强化","status":"STRENGTH","stacks":2,"editorId":"sts2-50061-13","editorX":670,"editorY":1950}],"editorId":"sts2-50061-11","editorX":370,"editorY":1640}],"editorId":"sts2-50061-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.62]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"RITUAL","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"仪式狂热","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"FRAIL","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"仪式狂热","amount":18,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"仪式狂热·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"仪式狂热·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"仪式巨兽·追击","amount":13,"hits":1}]}},{"id":"phase2","name":"仪式狂热·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"仪式狂热·终局","amount":12,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"仪式狂热·终局·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"仪式狂热·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"仪式巨兽·追击","amount":9,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>蛙寄生虫</t>
+  </si>
+  <si>
+    <t>生命115；行动：感染、鞭击。战斗初始：REGENERATION 2。寄生蔓延：生命≤50%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"感染","status":"POISON","stacks":2},{"type":"ACTION","action":"ATTACK","moveName":"鞭击","amount":4,"hits":3,"editorId":"sts2-50062-3","editorX":370,"editorY":400}],"editorId":"sts2-50062-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.63]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"寄生蔓延","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":6}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"寄生蔓延","amount":4,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"寄生蔓延·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"寄生蔓延·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"蛙寄生虫·追击","amount":3,"hits":3}]}}],"triggers":[{"event":"ON_DAMAGE_DEALT","listenSide":"ENEMY","limit":6,"filter":{"damageKind":"ATTACK"},"effects":[{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":1,"duration":"DEFAULT"}}]}]}</t>
+  </si>
+  <si>
+    <t>藤蔓蹒跚者</t>
+  </si>
+  <si>
+    <t>生命80；行动：缠绕藤蔓、缠绕藤蔓·脆弱、横扫、猛咬。战斗初始：REGENERATION 2。藤蔓收束：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"缠绕藤蔓","amount":8,"hits":1,"editorId":"sts2-50063-3","editorX":670,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"缠绕藤蔓·脆弱","status":"FRAIL","stacks":1,"editorId":"sts2-50063-4","editorX":670,"editorY":555}],"editorId":"sts2-50063-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"横扫","amount":6,"hits":2,"editorId":"sts2-50063-5","editorX":370,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"猛咬","amount":16,"hits":1,"editorId":"sts2-50063-6","editorX":370,"editorY":865}],"editorId":"sts2-50063-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.64]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"藤蔓收束","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":3}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"藤蔓收束","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"藤蔓收束·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"藤蔓收束·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"藤蔓蹒跚者·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>幽灵船</t>
+  </si>
+  <si>
+    <t>生命78；行动：全速冲撞、缠魂·削弱、横扫、跺击。战斗初始：EVASION 1。亡魂缠绕：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"全速冲撞","amount":10,"hits":1,"editorId":"sts2-50064-3","editorX":670,"editorY":400}],"editorId":"sts2-50064-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"全速冲撞","amount":10,"hits":1,"editorId":"sts2-50064-5","editorX":670,"editorY":710},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"缠魂·削弱","status":"WEAK","stacks":2,"editorId":"sts2-50064-7","editorX":970,"editorY":1020},{"type":"ACTION","action":"DEBUFF","moveName":"缠魂·削弱","status":"FRAIL","stacks":2,"editorId":"sts2-50064-8","editorX":970,"editorY":1175},{"type":"ACTION","action":"DEBUFF","moveName":"缠魂·削弱","status":"VULNERABLE","stacks":2,"editorId":"sts2-50064-9","editorX":970,"editorY":1330}],"editorId":"sts2-50064-6","editorX":670,"editorY":865},{"type":"ACTION","action":"ATTACK","moveName":"横扫","amount":13,"hits":1,"editorId":"sts2-50064-10","editorX":670,"editorY":1485},{"type":"ACTION","action":"ATTACK","moveName":"跺击","amount":4,"hits":3,"editorId":"sts2-50064-11","editorX":670,"editorY":1640}],"editorId":"sts2-50064-4","editorX":370,"editorY":555}],"editorId":"sts2-50064-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.65]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"亡魂缠绕","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"亡魂缠绕","amount":13,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"亡魂缠绕·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"亡魂缠绕·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"幽灵船·追击","amount":9,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>立方构装体</t>
+  </si>
+  <si>
+    <t>生命82；行动：蓄能·强化、连发冲击、连发冲击·强化、喷射冲击、下潜·格挡。战斗初始：PLATED_ARMOR 4。核心暴露：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"BUFF","moveName":"蓄能·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50065-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"连发冲击","amount":7,"hits":1,"editorId":"sts2-50065-4","editorX":670,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"连发冲击·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50065-5","editorX":670,"editorY":710}],"editorId":"sts2-50065-3","editorX":370,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"连发冲击","amount":7,"hits":1,"editorId":"sts2-50065-7","editorX":670,"editorY":1020},{"type":"ACTION","action":"BUFF","moveName":"连发冲击·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50065-8","editorX":670,"editorY":1175}],"editorId":"sts2-50065-6","editorX":370,"editorY":865},{"type":"ACTION","action":"ATTACK","moveName":"喷射冲击","amount":5,"hits":2,"editorId":"sts2-50065-9","editorX":370,"editorY":1330},{"type":"ACTION","action":"DEFEND","moveName":"下潜·格挡","amount":8,"editorId":"sts2-50065-10","editorX":370,"editorY":1485}],"editorId":"sts2-50065-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.66]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":4,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"核心暴露","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"核心暴露","amount":5,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"核心暴露·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"核心暴露·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"立方构装体·追击","amount":3,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>巨颚兽</t>
+  </si>
+  <si>
+    <t>生命84；行动：爪击、咆哮·削弱、撕扯。战斗初始：FURY 1。巨颚咬合：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"爪击","amount":4,"hits":2,"editorId":"sts2-50066-3","editorX":670,"editorY":400}],"editorId":"sts2-50066-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"爪击","amount":4,"hits":2,"editorId":"sts2-50066-5","editorX":670,"editorY":710},{"type":"ACTION","action":"DEBUFF","moveName":"咆哮·削弱","status":"VULNERABLE","stacks":2,"editorId":"sts2-50066-6","editorX":670,"editorY":865},{"type":"ACTION","action":"ATTACK","moveName":"撕扯","amount":14,"hits":1,"editorId":"sts2-50066-7","editorX":670,"editorY":1020}],"editorId":"sts2-50066-4","editorX":370,"editorY":555}],"editorId":"sts2-50066-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.67]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FURY","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"巨颚咬合","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"巨颚咬合","amount":14,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"巨颚咬合·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"巨颚咬合·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"巨颚兽·追击","amount":10,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>雾魔</t>
+  </si>
+  <si>
+    <t>生命80；行动：闪身戒备、横扫、横扫·强化、头槌。战斗初始：EVASION 1。迷雾凝聚：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":"EVASION","stacks":1,"duration":"COMBAT"},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"横扫","amount":8,"hits":1,"editorId":"sts2-50067-4","editorX":670,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"横扫·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50067-5","editorX":670,"editorY":710}],"editorId":"sts2-50067-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"头槌","amount":14,"hits":1,"editorId":"sts2-50067-6","editorX":370,"editorY":865}],"editorId":"sts2-50067-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.68]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"迷雾凝聚","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"迷雾凝聚","amount":14,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"迷雾凝聚·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"迷雾凝聚·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"雾魔·追击","amount":10,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>潜伏群落</t>
+  </si>
+  <si>
+    <t>生命125；行动：重击、疾速冲击、惯性·格挡、惯性·强化、巨蟹冲击。战斗初始：ARMOR 2。群落集中：生命≤50%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"重击","amount":9,"hits":1,"editorId":"sts2-50068-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"疾速冲击","amount":16,"hits":1,"editorId":"sts2-50068-3","editorX":370,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"惯性·格挡","amount":10,"editorId":"sts2-50068-5","editorX":670,"editorY":710},{"type":"ACTION","action":"BUFF","moveName":"惯性·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50068-6","editorX":670,"editorY":865}],"editorId":"sts2-50068-4","editorX":370,"editorY":555},{"type":"ACTION","action":"ATTACK","moveName":"巨蟹冲击","amount":6,"hits":2,"editorId":"sts2-50068-7","editorX":370,"editorY":1020}],"editorId":"sts2-50068-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.69]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"群落集中","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":8}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"群落集中","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"群落集中·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"群落集中·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"潜伏群落·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>窃贼跳虫</t>
+  </si>
+  <si>
+    <t>生命78；行动：偷窃、闪身戒备、帽子戏法、夺取。战斗初始：FLIGHT 2。折翼夺取：累计受到2段攻击生命损失后进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"偷窃","amount":17,"hits":1,"editorId":"sts2-50069-2","editorX":370,"editorY":245},{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":"EVASION","stacks":1,"duration":"COMBAT"},{"type":"ACTION","action":"ATTACK","moveName":"帽子戏法","amount":18,"hits":1,"editorId":"sts2-50069-4","editorX":370,"editorY":555},{"type":"ACTION","action":"ATTACK","moveName":"夺取","amount":14,"hits":1,"editorId":"sts2-50069-5","editorX":370,"editorY":710},{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":"EVASION","stacks":1,"duration":"COMBAT"}],"editorId":"sts2-50069-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.70]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FLIGHT","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"折翼夺取","condition":"HITS_AT_LEAST","value":2,"effects":[{"type":"REMOVE_STATUS","target":"SELF","params":{"status":"FLIGHT","amount":"ALL"}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"FRAIL","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"折翼夺取","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"折翼夺取·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"折翼夺取·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"窃贼跳虫·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>活体迷雾</t>
+  </si>
+  <si>
+    <t>生命82；行动：强化毒雾、强化毒雾·虚弱、膨胀、超级毒雾爆发。战斗初始：EVASION 1。毒雾实体：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"强化毒雾","amount":8,"hits":1,"editorId":"sts2-50070-3","editorX":670,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"强化毒雾·虚弱","status":"WEAK","stacks":1,"editorId":"sts2-50070-4","editorX":670,"editorY":555}],"editorId":"sts2-50070-2","editorX":370,"editorY":245},{"type":"ACTION","action":"DEBUFF","moveName":"膨胀","status":"POISON","stacks":2},{"type":"ACTION","action":"ATTACK","moveName":"超级毒雾爆发","amount":8,"hits":1,"editorId":"sts2-50070-6","editorX":370,"editorY":865}],"editorId":"sts2-50070-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.71]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"毒雾实体","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"毒雾实体","amount":8,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"毒雾实体·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"毒雾实体·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"活体迷雾·追击","amount":6,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>贪得无厌者</t>
+  </si>
+  <si>
+    <t>生命260；行动：液化地面、乱击、突进啃咬、垂涎·强化。战斗初始：FURY 1。吞噬渴求：生命≤65%进入，阶段仅触发一次，切换招式。吞噬渴求·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"液化地面","status":"CONSTRICTED","stacks":2},{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":8,"hits":2,"editorId":"sts2-50071-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"突进啃咬","amount":26,"hits":1,"editorId":"sts2-50071-4","editorX":370,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"垂涎·强化","status":"STRENGTH","stacks":2,"editorId":"sts2-50071-5","editorX":370,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":8,"hits":2,"editorId":"sts2-50071-6","editorX":370,"editorY":865}],"editorId":"sts2-50071-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.72]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FURY","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"吞噬渴求","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"CONSTRICTED","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"吞噬渴求","amount":24,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"吞噬渴求·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"吞噬渴求·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"贪得无厌者·追击","amount":18,"hits":1}]}},{"id":"phase2","name":"吞噬渴求·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"吞噬渴求·终局","amount":12,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"吞噬渴求·终局·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"吞噬渴求·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"贪得无厌者·追击","amount":9,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>魔法骑士</t>
+  </si>
+  <si>
+    <t>生命125；行动：能量盾、能量盾·格挡、压制·脆弱、长枪突刺、准备·格挡、魔法炸弹。战斗初始：ARTIFACT 1。魔盾超载：生命≤50%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"能量盾","amount":6,"hits":1,"editorId":"sts2-50072-3","editorX":670,"editorY":400},{"type":"ACTION","action":"DEFEND","moveName":"能量盾·格挡","amount":5,"editorId":"sts2-50072-4","editorX":670,"editorY":555}],"editorId":"sts2-50072-2","editorX":370,"editorY":245},{"type":"ACTION","action":"DEBUFF","moveName":"压制·脆弱","status":"FRAIL","stacks":1,"editorId":"sts2-50072-5","editorX":370,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"长枪突刺","amount":10,"hits":1,"editorId":"sts2-50072-6","editorX":370,"editorY":865},{"type":"ACTION","action":"DEFEND","moveName":"准备·格挡","amount":5,"editorId":"sts2-50072-7","editorX":370,"editorY":1020},{"type":"ACTION","action":"ATTACK","moveName":"魔法炸弹","amount":22,"hits":1,"editorId":"sts2-50072-8","editorX":370,"editorY":1175}],"editorId":"sts2-50072-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.73]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"魔盾超载","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"魔盾超载","amount":20,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"魔盾超载·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"魔盾超载·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"魔法骑士·追击","amount":15,"hits":1}]}}],"triggers":[{"event":"ON_SKILL_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":"BLOCK","target":"SELF","params":{"amount":2}}]}]}</t>
+  </si>
+  <si>
+    <t>沉睡甲虫</t>
+  </si>
+  <si>
+    <t>生命84；行动：沉睡、滚动突击、滚动突击·强化。战斗初始：ARMOR 3。甲虫惊醒：第3回合起进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"WAIT","moveName":"沉睡","editorId":"sts2-50073-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"滚动突击","amount":16,"hits":1,"editorId":"sts2-50073-4","editorX":670,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"滚动突击·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50073-5","editorX":670,"editorY":710}],"editorId":"sts2-50073-3","editorX":370,"editorY":400}],"editorId":"sts2-50073-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.74]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"甲虫惊醒","condition":"TURN_AT_LEAST","value":3,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"REMOVE_STATUS","target":"SELF","params":{"status":"ARMOR","amount":"ALL"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"甲虫惊醒","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"甲虫惊醒·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"甲虫惊醒·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"沉睡甲虫·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>掘地兽</t>
+  </si>
+  <si>
+    <t>生命88；行动：啃咬、潜地·格挡、地底突袭。战斗初始：PLATED_ARMOR 3。破土强攻：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"啃咬","amount":13,"hits":1,"editorId":"sts2-50074-2","editorX":370,"editorY":245},{"type":"ACTION","action":"DEFEND","moveName":"潜地·格挡","amount":8,"editorId":"sts2-50074-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"地底突袭","amount":18,"hits":1,"editorId":"sts2-50074-4","editorX":370,"editorY":555}],"editorId":"sts2-50074-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.75]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"破土强攻","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"破土强攻","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"破土强攻·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"破土强攻·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"掘地兽·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>幽魂骑士</t>
+  </si>
+  <si>
+    <t>生命130；行动：诅咒·虚弱、灵魂斩击、灵魂烈焰。战斗初始：EVASION 1。幽魂显形：生命≤50%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"DEBUFF","moveName":"诅咒·虚弱","status":"WEAK","stacks":1,"editorId":"sts2-50075-3","editorX":670,"editorY":400}],"editorId":"sts2-50075-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"DEBUFF","moveName":"诅咒·虚弱","status":"WEAK","stacks":1,"editorId":"sts2-50075-5","editorX":670,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"灵魂斩击","amount":15,"hits":1,"editorId":"sts2-50075-6","editorX":670,"editorY":865},{"type":"ACTION","action":"ATTACK","moveName":"灵魂烈焰","amount":3,"hits":3,"editorId":"sts2-50075-7","editorX":670,"editorY":1020}],"editorId":"sts2-50075-4","editorX":370,"editorY":555}],"editorId":"sts2-50075-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.76]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"幽魂显形","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"BURN","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"幽魂显形","amount":15,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"幽魂显形·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"幽魂显形·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"幽魂骑士·追击","amount":11,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>迷失者</t>
+  </si>
+  <si>
+    <t>生命86；行动：虚弱迷雾·易伤、虚弱迷雾·强化、眼部激光。战斗初始：EVASION 1。迷失狂乱：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"虚弱迷雾·易伤","status":"VULNERABLE","stacks":1,"editorId":"sts2-50076-3","editorX":670,"editorY":400},{"type":"ACTION","action":"BUFF","moveName":"虚弱迷雾·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50076-4","editorX":670,"editorY":555}],"editorId":"sts2-50076-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"眼部激光","amount":4,"hits":2,"editorId":"sts2-50076-5","editorX":370,"editorY":710}],"editorId":"sts2-50076-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.77]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"迷失狂乱","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"迷失狂乱","amount":4,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"迷失狂乱·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"迷失狂乱·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"迷失者·追击","amount":3,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>链锤骑士</t>
+  </si>
+  <si>
+    <t>生命135；行动：猛撞、战歌·强化、链锤乱击。战斗初始：PLATED_ARMOR 3。链锤旋舞：生命≤50%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"猛撞","amount":15,"hits":1,"editorId":"sts2-50077-3","editorX":670,"editorY":400}],"editorId":"sts2-50077-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"BUFF","moveName":"战歌·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50077-5","editorX":670,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"链锤乱击","amount":9,"hits":2,"editorId":"sts2-50077-6","editorX":670,"editorY":865},{"type":"ACTION","action":"ATTACK","moveName":"猛撞","amount":15,"hits":1,"editorId":"sts2-50077-7","editorX":670,"editorY":1020}],"editorId":"sts2-50077-4","editorX":370,"editorY":555}],"editorId":"sts2-50077-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.78]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"链锤旋舞","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":8}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"链锤旋舞","amount":9,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"链锤旋舞·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"链锤旋舞·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"链锤骑士·追击","amount":6,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>遗忘者</t>
+  </si>
+  <si>
+    <t>生命88；行动：瘴气·脆弱、瘴气·格挡、瘴气·强化、恐惧。战斗初始：ARTIFACT 1。记忆侵蚀：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"瘴气·脆弱","status":"FRAIL","stacks":1,"editorId":"sts2-50078-3","editorX":670,"editorY":400},{"type":"ACTION","action":"DEFEND","moveName":"瘴气·格挡","amount":8,"editorId":"sts2-50078-4","editorX":670,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"瘴气·强化","status":"DEXTERITY","stacks":2,"editorId":"sts2-50078-5","editorX":670,"editorY":710}],"editorId":"sts2-50078-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"恐惧","amount":15,"hits":1,"editorId":"sts2-50078-6","editorX":370,"editorY":865}],"editorId":"sts2-50078-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.79]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"记忆侵蚀","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"记忆侵蚀","amount":15,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"记忆侵蚀·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"记忆侵蚀·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"遗忘者·追击","amount":11,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>棘刺蟾蜍</t>
+  </si>
+  <si>
+    <t>生命90；行动：凸出尖刺·强化、尖刺爆发、舌鞭。战斗初始：THORNS 3。尖刺绽放：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"BUFF","moveName":"凸出尖刺·强化","status":"THORNS","stacks":1,"editorId":"sts2-50079-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"尖刺爆发","amount":18,"hits":1,"editorId":"sts2-50079-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"舌鞭","amount":17,"hits":1,"editorId":"sts2-50079-4","editorX":370,"editorY":555}],"editorId":"sts2-50079-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.80]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"THORNS","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"尖刺绽放","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"尖刺绽放","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"尖刺绽放·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"尖刺绽放·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"棘刺蟾蜍·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>猎杀者</t>
+  </si>
+  <si>
+    <t>生命94；行动：软化黏液·易伤、啃咬、穿刺。战斗初始：FURY 1。猎杀追击：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"DEBUFF","moveName":"软化黏液·易伤","status":"VULNERABLE","stacks":1,"editorId":"sts2-50080-3","editorX":670,"editorY":400}],"editorId":"sts2-50080-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"DEBUFF","moveName":"软化黏液·易伤","status":"VULNERABLE","stacks":1,"editorId":"sts2-50080-5","editorX":670,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"啃咬","amount":17,"hits":1,"editorId":"sts2-50080-6","editorX":670,"editorY":865},{"type":"ACTION","action":"ATTACK","moveName":"穿刺","amount":6,"hits":3,"editorId":"sts2-50080-7","editorX":670,"editorY":1020}],"editorId":"sts2-50080-4","editorX":370,"editorY":555}],"editorId":"sts2-50080-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.81]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FURY","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"猎杀追击","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"猎杀追击","amount":5,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"猎杀追击·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"猎杀追击·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"猎杀者·追击","amount":3,"hits":3}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>知识恶魔</t>
+  </si>
+  <si>
+    <t>生命270；行动：知识诅咒·虚弱、知识诅咒·脆弱、拍击、知识洪流、沉思、沉思·治疗、沉思·强化。战斗初始：ARTIFACT 2。禁忌知识：生命≤65%进入，阶段仅触发一次，切换招式。禁忌知识·终局：生命≤30%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"知识诅咒·虚弱","status":"WEAK","stacks":2,"editorId":"sts2-50081-3","editorX":670,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"知识诅咒·脆弱","status":"FRAIL","stacks":2,"editorId":"sts2-50081-4","editorX":670,"editorY":555}],"editorId":"sts2-50081-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"拍击","amount":17,"hits":1,"editorId":"sts2-50081-5","editorX":370,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"知识洪流","amount":8,"hits":3,"editorId":"sts2-50081-6","editorX":370,"editorY":865},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"沉思","amount":11,"hits":1,"editorId":"sts2-50081-8","editorX":670,"editorY":1175},{"type":"ACTION","action":"HEAL","moveName":"沉思·治疗","amount":12,"editorId":"sts2-50081-9","editorX":670,"editorY":1330},{"type":"ACTION","action":"BUFF","moveName":"沉思·强化","status":"STRENGTH","stacks":2,"editorId":"sts2-50081-10","editorX":670,"editorY":1485}],"editorId":"sts2-50081-7","editorX":370,"editorY":1020}],"editorId":"sts2-50081-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.82]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"禁忌知识","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"禁忌知识","amount":8,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"禁忌知识·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"禁忌知识·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"知识恶魔·追击","amount":6,"hits":3}]}},{"id":"phase2","name":"禁忌知识·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"禁忌知识·终局","amount":8,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"禁忌知识·终局·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"禁忌知识·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"知识恶魔·追击","amount":6,"hits":3}]}}],"triggers":[{"event":"ON_POWER_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}}]}]}</t>
+  </si>
+  <si>
+    <t>晦影者</t>
+  </si>
+  <si>
+    <t>生命90；行动：闪身戒备、穿透凝视、哀嚎、硬化打击、硬化打击·格挡。战斗初始：EVASION 2。晦影具象：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":"EVASION","stacks":1,"duration":"COMBAT"}],"editorId":"sts2-50082-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":"EVASION","stacks":1,"duration":"COMBAT"},{"type":"ACTION","action":"ATTACK","moveName":"穿透凝视","amount":10,"hits":1,"editorId":"sts2-50082-6","editorX":670,"editorY":865},{"type":"ACTION","action":"DEBUFF","moveName":"哀嚎","status":"WEAK","stacks":2},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"硬化打击","amount":6,"hits":1,"editorId":"sts2-50082-9","editorX":970,"editorY":1330},{"type":"ACTION","action":"DEFEND","moveName":"硬化打击·格挡","amount":6,"editorId":"sts2-50082-10","editorX":970,"editorY":1485}],"editorId":"sts2-50082-8","editorX":670,"editorY":1175}],"editorId":"sts2-50082-4","editorX":370,"editorY":555}],"editorId":"sts2-50082-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.83]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"晦影具象","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"FRAIL","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"晦影具象","amount":10,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"晦影具象·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"晦影具象·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"晦影者·追击","amount":7,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>产卵飞虫</t>
+  </si>
+  <si>
+    <t>生命92；行动：集中自身力量、强化自身护甲、重击、软化打击、软化打击·削弱、营养糊·强化。战斗初始：FLIGHT 3。虫卵吸收：累计受到3段攻击生命损失后进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"集中自身力量","status":"STRENGTH","stacks":1},{"type":"ACTION","action":"DEFEND","moveName":"强化自身护甲","amount":6}]},{"type":"ACTION","action":"ATTACK","moveName":"重击","amount":16,"hits":1,"editorId":"sts2-50083-3","editorX":370,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"软化打击","amount":7,"hits":1,"editorId":"sts2-50083-5","editorX":670,"editorY":710},{"type":"ACTION","action":"DEBUFF","moveName":"软化打击·削弱","status":"VULNERABLE","stacks":2,"editorId":"sts2-50083-6","editorX":670,"editorY":865}],"editorId":"sts2-50083-4","editorX":370,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"营养糊·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50083-7","editorX":370,"editorY":1020}],"editorId":"sts2-50083-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.84]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FLIGHT","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"虫卵吸收","condition":"HITS_AT_LEAST","value":3,"effects":[{"type":"REMOVE_STATUS","target":"SELF","params":{"status":"FLIGHT","amount":"ALL"}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"虫卵吸收","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"虫卵吸收·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"虫卵吸收·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"产卵飞虫·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>虱虫始祖</t>
+  </si>
+  <si>
+    <t>生命96；行动：蛛网炮、蛛网炮·削弱、蜷缩成长·格挡、蜷缩成长·强化、扑击。战斗初始：PLATED_ARMOR 3。始祖蜕壳：生命≤40%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蛛网炮","amount":9,"hits":1,"editorId":"sts2-50084-3","editorX":670,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"蛛网炮·削弱","status":"FRAIL","stacks":2,"editorId":"sts2-50084-4","editorX":670,"editorY":555}],"editorId":"sts2-50084-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"蜷缩成长·格挡","amount":8,"editorId":"sts2-50084-6","editorX":670,"editorY":865},{"type":"ACTION","action":"BUFF","moveName":"蜷缩成长·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50084-7","editorX":670,"editorY":1020}],"editorId":"sts2-50084-5","editorX":370,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"扑击","amount":14,"hits":1,"editorId":"sts2-50084-8","editorX":370,"editorY":1175}],"editorId":"sts2-50084-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.85]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"始祖蜕壳","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"始祖蜕壳","amount":14,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"始祖蜕壳·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"始祖蜕壳·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"虱虫始祖·追击","amount":10,"hits":1}]}}],"triggers":[{"event":"ON_DAMAGE_DEALT","listenSide":"ENEMY","limit":6,"filter":{"damageKind":"ATTACK"},"effects":[{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":1,"duration":"DEFAULT"}}]}]}</t>
+  </si>
+  <si>
+    <t>恐惧鳗鱼</t>
+  </si>
+  <si>
+    <t>生命140；行动：撞击、乱击、恐吓·削弱。战斗初始：EVASION 1。恐惧电流：生命≤50%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"撞击","amount":17,"hits":1,"editorId":"sts2-50085-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":3,"hits":3,"editorId":"sts2-50085-3","editorX":370,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"恐吓·削弱","status":"VULNERABLE","stacks":2,"editorId":"sts2-50085-4","editorX":370,"editorY":555}],"editorId":"sts2-50085-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.86]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"EVASION","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"恐惧电流","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"BURN","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"恐惧电流","amount":17,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"恐惧电流·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"恐惧电流·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"恐惧鳗鱼·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>御虫师</t>
+  </si>
+  <si>
+    <t>生命145；行动：蜂群、长枪突刺、集中自身力量、强化自身护甲。战斗初始：ARTIFACT 1。信息素狂热：生命≤50%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蜂群","amount":3,"hits":3,"editorId":"sts2-50086-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"长枪突刺","amount":18,"hits":1,"editorId":"sts2-50086-3","editorX":370,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"集中自身力量","status":"STRENGTH","stacks":1},{"type":"ACTION","action":"DEFEND","moveName":"强化自身护甲","amount":6}]}],"editorId":"sts2-50086-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.87]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"信息素狂热","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"信息素狂热","amount":18,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"信息素狂热·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"信息素狂热·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"御虫师·追击","amount":13,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>球头怪</t>
+  </si>
+  <si>
+    <t>生命100；行动：电击掌、电击掌·削弱、雷霆打击、电流爆发、电流爆发·强化。战斗初始：ARTIFACT 1。电流回路：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"电击掌","amount":13,"hits":1,"editorId":"sts2-50087-3","editorX":670,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"电击掌·削弱","status":"FRAIL","stacks":2,"editorId":"sts2-50087-4","editorX":670,"editorY":555}],"editorId":"sts2-50087-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"雷霆打击","amount":6,"hits":3,"editorId":"sts2-50087-5","editorX":370,"editorY":710},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"电流爆发","amount":16,"hits":1,"editorId":"sts2-50087-7","editorX":670,"editorY":1020},{"type":"ACTION","action":"BUFF","moveName":"电流爆发·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50087-8","editorX":670,"editorY":1175}],"editorId":"sts2-50087-6","editorX":370,"editorY":865}],"editorId":"sts2-50087-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.88]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"电流回路","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"电流回路","amount":5,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"电流回路·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"电流回路·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"球头怪·追击","amount":3,"hits":3}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>制造者</t>
+  </si>
+  <si>
+    <t>生命100；行动：集中自身力量、强化自身护甲、制造打击、瓦解。战斗初始：PLATED_ARMOR 3。工具改装：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"RANDOM","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"集中自身力量","status":"STRENGTH","stacks":1},{"type":"ACTION","action":"DEFEND","moveName":"强化自身护甲","amount":6}]},{"type":"ACTION","action":"ATTACK","moveName":"制造打击","amount":18,"hits":1,"editorId":"sts2-50088-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"瓦解","amount":11,"hits":1,"editorId":"sts2-50088-4","editorX":370,"editorY":555}],"editorId":"sts2-50088-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.89]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"工具改装","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"工具改装","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"工具改装·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"工具改装·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"制造者·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>虔诚雕塑师</t>
+  </si>
+  <si>
+    <t>生命102；行动：禁忌咒语·仪式、狂野打击。战斗初始：RITUAL 1。禁忌雕像：生命≤40%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"BUFF","moveName":"禁忌咒语·仪式","status":"STRENGTH","stacks":1,"editorId":"sts2-50089-3","editorX":670,"editorY":400}],"editorId":"sts2-50089-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"狂野打击","amount":12,"hits":1,"editorId":"sts2-50089-4","editorX":370,"editorY":555}],"editorId":"sts2-50089-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.90]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"RITUAL","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"禁忌雕像","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"禁忌雕像","amount":12,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"禁忌雕像·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"禁忌雕像·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"虔诚雕塑师·追击","amount":9,"hits":1}]}}],"triggers":[{"event":"ON_POWER_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}}]}]}</t>
+  </si>
+  <si>
+    <t>伪装商人</t>
+  </si>
+  <si>
+    <t>生命104；行动：横扫、喷射硬币、投掷遗物、投掷遗物·削弱、狂怒·强化。战斗初始：FURY 1。贪欲揭面：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"横扫","amount":13,"hits":1,"editorId":"sts2-50090-3","editorX":670,"editorY":400}],"editorId":"sts2-50090-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"横扫","amount":13,"hits":1,"editorId":"sts2-50090-5","editorX":670,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"喷射硬币","amount":2,"hits":3,"editorId":"sts2-50090-6","editorX":670,"editorY":865},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"投掷遗物","amount":9,"hits":1,"editorId":"sts2-50090-8","editorX":970,"editorY":1175},{"type":"ACTION","action":"DEBUFF","moveName":"投掷遗物·削弱","status":"FRAIL","stacks":1,"editorId":"sts2-50090-9","editorX":970,"editorY":1330}],"editorId":"sts2-50090-7","editorX":670,"editorY":1020},{"type":"ACTION","action":"BUFF","moveName":"狂怒·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50090-10","editorX":670,"editorY":1485}],"editorId":"sts2-50090-4","editorX":370,"editorY":555}],"editorId":"sts2-50090-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.91]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FURY","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"贪欲揭面","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"FRAIL","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"贪欲揭面","amount":13,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"贪欲揭面·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"贪欲揭面·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"伪装商人·追击","amount":9,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>女王</t>
+  </si>
+  <si>
+    <t>生命280；行动：傀儡丝线、你属于我·削弱、为我燃烧·格挡、斩下你的头、处决、狂怒·强化。战斗初始：ARTIFACT 2。女王亲征：生命≤65%进入，阶段仅触发一次，切换招式。女王亲征·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"傀儡丝线","status":"CONSTRICTED","stacks":2},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"你属于我·削弱","status":"FRAIL","stacks":3,"editorId":"sts2-50091-4","editorX":670,"editorY":555},{"type":"ACTION","action":"DEBUFF","moveName":"你属于我·削弱","status":"WEAK","stacks":3,"editorId":"sts2-50091-5","editorX":670,"editorY":710},{"type":"ACTION","action":"DEBUFF","moveName":"你属于我·削弱","status":"VULNERABLE","stacks":3,"editorId":"sts2-50091-6","editorX":670,"editorY":865}],"editorId":"sts2-50091-3","editorX":370,"editorY":400},{"type":"ACTION","action":"DEFEND","moveName":"为我燃烧·格挡","amount":16,"editorId":"sts2-50091-7","editorX":370,"editorY":1020},{"type":"ACTION","action":"ATTACK","moveName":"斩下你的头","amount":3,"hits":4,"editorId":"sts2-50091-8","editorX":370,"editorY":1175},{"type":"ACTION","action":"ATTACK","moveName":"处决","amount":15,"hits":1,"editorId":"sts2-50091-9","editorX":370,"editorY":1330},{"type":"ACTION","action":"BUFF","moveName":"狂怒·强化","status":"STRENGTH","stacks":2,"editorId":"sts2-50091-10","editorX":370,"editorY":1485}],"editorId":"sts2-50091-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.92]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"女王亲征","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"女王亲征","amount":15,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"女王亲征·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"女王亲征·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"女王·追击","amount":11,"hits":1}]}},{"id":"phase2","name":"女王亲征·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"女王亲征·终局","amount":12,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"女王亲征·终局·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"女王亲征·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"女王·追击","amount":9,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>火箭</t>
+  </si>
+  <si>
+    <t>生命250；行动：锁定准星、精准光束、蓄能·强化、激光、蓄势护体、蓄势增压。战斗初始：PLATED_ARMOR 3。火箭超载：生命≤65%进入，阶段仅触发一次，切换招式。火箭超载·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"锁定准星","amount":3,"hits":1,"editorId":"sts2-50092-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"精准光束","amount":18,"hits":1,"editorId":"sts2-50092-3","editorX":370,"editorY":400},{"type":"ACTION","action":"BUFF","moveName":"蓄能·强化","status":"STRENGTH","stacks":2,"editorId":"sts2-50092-4","editorX":370,"editorY":555},{"type":"ACTION","action":"ATTACK","moveName":"激光","amount":26,"hits":1,"editorId":"sts2-50092-5","editorX":370,"editorY":710},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"蓄势护体","amount":8},{"type":"ACTION","action":"BUFF","moveName":"蓄势增压","status":"STRENGTH","stacks":2}]}],"editorId":"sts2-50092-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.93]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"火箭超载","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":12}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"火箭超载","amount":24,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"火箭超载·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"火箭超载·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"火箭·追击","amount":18,"hits":1}]}},{"id":"phase2","name":"火箭超载·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"火箭超载·终局","amount":12,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"火箭超载·终局·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"火箭超载·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"火箭·追击","amount":9,"hits":2}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>眷族祭司</t>
+  </si>
+  <si>
+    <t>生命230；行动：脆弱法球、脆弱法球·削弱、虚弱法球、虚弱法球·削弱、光束、仪式·强化。战斗初始：RITUAL 1。祭司法阵：生命≤65%进入，阶段仅触发一次，切换招式。祭司法阵·终局：生命≤30%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"脆弱法球","amount":8,"hits":1,"editorId":"sts2-50093-3","editorX":670,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"脆弱法球·削弱","status":"FRAIL","stacks":1,"editorId":"sts2-50093-4","editorX":670,"editorY":555}],"editorId":"sts2-50093-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"虚弱法球","amount":8,"hits":1,"editorId":"sts2-50093-6","editorX":670,"editorY":865},{"type":"ACTION","action":"DEBUFF","moveName":"虚弱法球·削弱","status":"WEAK","stacks":1,"editorId":"sts2-50093-7","editorX":670,"editorY":1020}],"editorId":"sts2-50093-5","editorX":370,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"光束","amount":3,"hits":3,"editorId":"sts2-50093-8","editorX":370,"editorY":1175},{"type":"ACTION","action":"BUFF","moveName":"仪式·强化","status":"STRENGTH","stacks":2,"editorId":"sts2-50093-9","editorX":370,"editorY":1330}],"editorId":"sts2-50093-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.94]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"RITUAL","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"祭司法阵","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"祭司法阵","amount":3,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"祭司法阵·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"祭司法阵·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"眷族祭司·追击","amount":3,"hits":3}]}},{"id":"phase2","name":"祭司法阵·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"祭司法阵·终局","amount":3,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"祭司法阵·终局·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"祭司法阵·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"眷族祭司·追击","amount":3,"hits":3}]}}],"triggers":[{"event":"ON_POWER_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}}]}]}</t>
+  </si>
+  <si>
+    <t>青蛙骑士</t>
+  </si>
+  <si>
+    <t>生命108；行动：舌鞭、舌鞭·削弱、讨伐邪恶、为了女王·强化、甲虫冲锋。战斗初始：PLATED_ARMOR 3。骑士誓言：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"舌鞭","amount":13,"hits":1,"editorId":"sts2-50094-3","editorX":670,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"舌鞭·削弱","status":"FRAIL","stacks":2,"editorId":"sts2-50094-4","editorX":670,"editorY":555}],"editorId":"sts2-50094-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"讨伐邪恶","amount":18,"hits":1,"editorId":"sts2-50094-5","editorX":370,"editorY":710},{"type":"ACTION","action":"BUFF","moveName":"为了女王·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50094-6","editorX":370,"editorY":865},{"type":"ACTION","action":"ATTACK","moveName":"甲虫冲锋","amount":18,"hits":1,"editorId":"sts2-50094-7","editorX":370,"editorY":1020}],"editorId":"sts2-50094-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.95]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"骑士誓言","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":4}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"骑士誓言","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"骑士誓言·压制","status":"FRAIL","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"骑士誓言·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"青蛙骑士·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>火炬头融合体</t>
+  </si>
+  <si>
+    <t>生命260；行动：冲撞、灵魂光束、虚弱冲撞。战斗初始：ARMOR 3。融合燃烧：生命≤65%进入，阶段仅触发一次，切换招式。融合燃烧·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":18,"hits":1,"editorId":"sts2-50095-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":18,"hits":1,"editorId":"sts2-50095-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"灵魂光束","amount":8,"hits":3,"editorId":"sts2-50095-4","editorX":370,"editorY":555},{"type":"ACTION","action":"ATTACK","moveName":"虚弱冲撞","amount":14,"hits":1,"editorId":"sts2-50095-5","editorX":370,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"虚弱冲撞","amount":14,"hits":1,"editorId":"sts2-50095-6","editorX":370,"editorY":865}],"editorId":"sts2-50095-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.96]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARMOR","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"融合燃烧","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":12}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"融合燃烧","amount":8,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"融合燃烧·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"融合燃烧·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"火炬头融合体·追击","amount":6,"hits":3}]}},{"id":"phase2","name":"融合燃烧·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"融合燃烧·终局","amount":8,"hits":3},{"type":"ACTION","action":"DEBUFF","moveName":"融合燃烧·终局·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"融合燃烧·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"火炬头融合体·追击","amount":6,"hits":3}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>寄生棱晶</t>
+  </si>
+  <si>
+    <t>生命155；行动：刺拳、辐射、辐射·格挡、旋风连击、脉动·格挡、脉动·强化。战斗初始：ARTIFACT 1。棱晶裂解：生命≤50%进入，阶段仅触发一次，切换招式。 另有事件触发机制，详见 mechanics。所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"刺拳","amount":22,"hits":1,"editorId":"sts2-50096-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"辐射","amount":16,"hits":1,"editorId":"sts2-50096-4","editorX":670,"editorY":555},{"type":"ACTION","action":"DEFEND","moveName":"辐射·格挡","amount":12,"editorId":"sts2-50096-5","editorX":670,"editorY":710}],"editorId":"sts2-50096-3","editorX":370,"editorY":400},{"type":"ACTION","action":"ATTACK","moveName":"旋风连击","amount":7,"hits":3,"editorId":"sts2-50096-6","editorX":370,"editorY":865},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"脉动·格挡","amount":12,"editorId":"sts2-50096-8","editorX":670,"editorY":1175},{"type":"ACTION","action":"BUFF","moveName":"脉动·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50096-9","editorX":670,"editorY":1330}],"editorId":"sts2-50096-7","editorX":370,"editorY":1020}],"editorId":"sts2-50096-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.97]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"棱晶裂解","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"棱晶裂解","amount":20,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"棱晶裂解·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"棱晶裂解·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"寄生棱晶·追击","amount":15,"hits":1}]}}],"triggers":[{"event":"ON_DAMAGE_DEALT","listenSide":"ENEMY","limit":6,"filter":{"damageKind":"ATTACK"},"effects":[{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":1,"duration":"DEFAULT"}}]}]}</t>
+  </si>
+  <si>
+    <t>猫头鹰裁判官</t>
+  </si>
+  <si>
+    <t>生命110；行动：裁判审视、连环啄击、审判之翼、判决、判决·削弱。战斗初始：FLIGHT 3。落地审判：累计受到3段攻击生命损失后进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"裁判审视","amount":16,"hits":1,"editorId":"sts2-50097-2","editorX":370,"editorY":245},{"type":"ACTION","action":"ATTACK","moveName":"连环啄击","amount":4,"hits":3,"editorId":"sts2-50097-3","editorX":370,"editorY":400},{"type":"ACTION","action":"DEBUFF","moveName":"审判之翼","status":"WEAK","stacks":2},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"判决","amount":18,"hits":1,"editorId":"sts2-50097-6","editorX":670,"editorY":865},{"type":"ACTION","action":"DEBUFF","moveName":"判决·削弱","status":"VULNERABLE","stacks":2,"editorId":"sts2-50097-7","editorX":670,"editorY":1020}],"editorId":"sts2-50097-5","editorX":370,"editorY":710}],"editorId":"sts2-50097-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.98]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FLIGHT","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"落地审判","condition":"HITS_AT_LEAST","value":3,"effects":[{"type":"REMOVE_STATUS","target":"SELF","params":{"status":"FLIGHT","amount":"ALL"}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"落地审判","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"落地审判·压制","status":"VULNERABLE","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"落地审判·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"猫头鹰裁判官·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>灵魂枢纽</t>
+  </si>
+  <si>
+    <t>生命155；行动：灵魂灼烧、漩涡、汲取生命、汲取生命·削弱。战斗初始：REGENERATION 3。魂核暴露：生命≤50%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"灵魂灼烧","amount":22,"hits":1,"editorId":"sts2-50098-3","editorX":670,"editorY":400}],"editorId":"sts2-50098-2","editorX":370,"editorY":245},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"灵魂灼烧","amount":22,"hits":1,"editorId":"sts2-50098-5","editorX":670,"editorY":710},{"type":"ACTION","action":"ATTACK","moveName":"漩涡","amount":6,"hits":3,"editorId":"sts2-50098-6","editorX":670,"editorY":865},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"汲取生命","amount":18,"hits":1,"editorId":"sts2-50098-8","editorX":970,"editorY":1175},{"type":"ACTION","action":"DEBUFF","moveName":"汲取生命·削弱","status":"VULNERABLE","stacks":2,"editorId":"sts2-50098-9","editorX":970,"editorY":1330},{"type":"ACTION","action":"DEBUFF","moveName":"汲取生命·削弱","status":"WEAK","stacks":2,"editorId":"sts2-50098-10","editorX":970,"editorY":1485}],"editorId":"sts2-50098-7","editorX":670,"editorY":1020}],"editorId":"sts2-50098-4","editorX":370,"editorY":555}],"editorId":"sts2-50098-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.99]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"REGENERATION","stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"魂核暴露","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"HEAL","target":"SELF","params":{"amount":6}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"魂核暴露","amount":20,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"魂核暴露·压制","status":"WEAK","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"魂核暴露·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"灵魂枢纽·追击","amount":15,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>黏液狂战士</t>
+  </si>
+  <si>
+    <t>生命115；行动：喷吐脓液、狂怒连打、吸血拥抱·削弱、吸血拥抱·强化、窒息。战斗初始：FURY 1。黏液沸腾：生命≤40%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"喷吐脓液","status":"POISON","stacks":2},{"type":"ACTION","action":"ATTACK","moveName":"狂怒连打","amount":4,"hits":3,"editorId":"sts2-50099-3","editorX":370,"editorY":400},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"吸血拥抱·削弱","status":"WEAK","stacks":2,"editorId":"sts2-50099-5","editorX":670,"editorY":710},{"type":"ACTION","action":"BUFF","moveName":"吸血拥抱·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50099-6","editorX":670,"editorY":865}],"editorId":"sts2-50099-4","editorX":370,"editorY":555},{"type":"ACTION","action":"ATTACK","moveName":"窒息","amount":18,"hits":1,"editorId":"sts2-50099-7","editorX":370,"editorY":1020}],"editorId":"sts2-50099-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.100]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"FURY","stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"黏液沸腾","condition":"HP_BELOW","value":40,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":1,"duration":"DEFAULT"}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"黏液沸腾","amount":16,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"黏液沸腾·压制","status":"POISON","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"黏液沸腾·重整","amount":3},{"type":"ACTION","action":"ATTACK","moveName":"黏液狂战士·追击","amount":12,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>机甲骑士</t>
+  </si>
+  <si>
+    <t>生命165；行动：冲锋、火焰喷射、持续燃烧、蓄力·格挡、蓄力·强化、沉重劈砍。战斗初始：PLATED_ARMOR 4。机甲破损：生命≤50%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"冲锋","amount":22,"hits":1,"editorId":"sts2-50100-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"火焰喷射","amount":8,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"持续燃烧","status":"BURN","stacks":2}]},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"蓄力·格挡","amount":12,"editorId":"sts2-50100-5","editorX":670,"editorY":710},{"type":"ACTION","action":"BUFF","moveName":"蓄力·强化","status":"STRENGTH","stacks":1,"editorId":"sts2-50100-6","editorX":670,"editorY":865}],"editorId":"sts2-50100-4","editorX":370,"editorY":555},{"type":"ACTION","action":"ATTACK","moveName":"沉重劈砍","amount":22,"hits":1,"editorId":"sts2-50100-7","editorX":370,"editorY":1020}],"editorId":"sts2-50100-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.101]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"PLATED_ARMOR","stacks":4,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"机甲破损","condition":"HP_BELOW","value":50,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":8}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"机甲破损","amount":20,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"机甲破损·压制","status":"BURN","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"机甲破损·重整","amount":6},{"type":"ACTION","action":"ATTACK","moveName":"机甲骑士·追击","amount":15,"hits":1}]}}],"triggers":[]}</t>
+  </si>
+  <si>
+    <t>造门者</t>
+  </si>
+  <si>
+    <t>生命300；行动：光束、退回门内、退回门内·强化。战斗初始：ARTIFACT 2。门扉破裂：生命≤65%进入，阶段仅触发一次，切换招式。门扉破裂·终局：生命≤30%进入，阶段仅触发一次，切换招式。 所有招式均在单敌人战斗中执行，不召唤。</t>
+  </si>
+  <si>
+    <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"光束","amount":26,"hits":1,"editorId":"sts2-50101-2","editorX":370,"editorY":245},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"退回门内","amount":26,"hits":1,"editorId":"sts2-50101-4","editorX":670,"editorY":555},{"type":"ACTION","action":"BUFF","moveName":"退回门内·强化","status":"STRENGTH","stacks":2,"editorId":"sts2-50101-5","editorX":670,"editorY":710}],"editorId":"sts2-50101-3","editorX":370,"editorY":400}],"editorId":"sts2-50101-1","editorX":70,"editorY":90}</t>
+  </si>
+  <si>
+    <t>[[0.4,0.4,0.2],[0.4,0.4,0.2],[0.4,0.4,0.102]]</t>
+  </si>
+  <si>
+    <t>{"initialStatuses":[{"status":"ARTIFACT","stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"门扉破裂","condition":"HP_BELOW","value":65,"effects":[{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"CLEANSE","target":"SELF","params":{}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"门扉破裂","amount":24,"hits":1},{"type":"ACTION","action":"DEBUFF","moveName":"门扉破裂·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"门扉破裂·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"造门者·追击","amount":18,"hits":1}]}},{"id":"phase2","name":"门扉破裂·终局","condition":"HP_BELOW","value":30,"effects":[{"type":"CLEANSE","target":"SELF","params":{}},{"type":"APPLY_STATUS","target":"SELF","params":{"status":"STRENGTH","stacks":1,"duration":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10}}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"门扉破裂·终局","amount":12,"hits":2},{"type":"ACTION","action":"DEBUFF","moveName":"门扉破裂·终局·压制","status":"CONSTRICTED","stacks":1}]},{"type":"ACTION","action":"DEFEND","moveName":"门扉破裂·终局·重整","amount":9},{"type":"ACTION","action":"ATTACK","moveName":"造门者·追击","amount":9,"hits":2}]}}],"triggers":[]}</t>
   </si>
 </sst>
 </file>
@@ -508,16 +1960,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <dimension ref="A1:J106"/>
+  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="28.75" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="4" max="4" width="19.675" customWidth="1"/>
+    <col min="5" max="5" width="14.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="11.0916666666667" customWidth="1"/>
+    <col min="7" max="7" width="22.1666666666667" customWidth="1"/>
+    <col min="8" max="8" width="15.5416666666667" customWidth="1"/>
+    <col min="9" max="9" width="27.1666666666667" customWidth="1"/>
+    <col min="10" max="10" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -536,305 +1993,3377 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>50001</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>170002</v>
+      </c>
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>50002</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="G7">
+        <v>170003</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>50003</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="G8">
+        <v>170004</v>
+      </c>
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>50004</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E9">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="G9">
+        <v>170005</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>50005</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E10">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="G10">
+        <v>170006</v>
+      </c>
+      <c r="H10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>50006</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="E11">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="G11">
+        <v>170007</v>
+      </c>
+      <c r="H11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>50007</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="E12">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="G12">
+        <v>170008</v>
+      </c>
+      <c r="H12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>50008</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E13">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="G13">
+        <v>170009</v>
+      </c>
+      <c r="H13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>50009</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="E14">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="G14">
+        <v>170010</v>
+      </c>
+      <c r="H14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>50010</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E15">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="G15">
+        <v>170011</v>
+      </c>
+      <c r="H15" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>50011</v>
       </c>
       <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16">
+        <v>300</v>
+      </c>
+      <c r="F16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16">
+        <v>170012</v>
+      </c>
+      <c r="H16" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>50012</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17">
+        <v>48</v>
+      </c>
+      <c r="F17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17">
+        <v>170013</v>
+      </c>
+      <c r="H17" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" t="s">
+        <v>30</v>
+      </c>
+      <c r="J17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>50013</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18">
+        <v>44</v>
+      </c>
+      <c r="F18" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18">
+        <v>170014</v>
+      </c>
+      <c r="H18" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>50014</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19">
+        <v>40</v>
+      </c>
+      <c r="F19" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19">
+        <v>170015</v>
+      </c>
+      <c r="H19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I19" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>50015</v>
+      </c>
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20">
+        <v>170016</v>
+      </c>
+      <c r="H20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>50016</v>
+      </c>
+      <c r="B21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21">
+        <v>48</v>
+      </c>
+      <c r="F21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G21">
+        <v>170017</v>
+      </c>
+      <c r="H21" t="s">
+        <v>109</v>
+      </c>
+      <c r="I21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>50017</v>
+      </c>
+      <c r="B22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22">
+        <v>46</v>
+      </c>
+      <c r="F22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22">
+        <v>170018</v>
+      </c>
+      <c r="H22" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>50018</v>
+      </c>
+      <c r="B23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23">
+        <v>54</v>
+      </c>
+      <c r="F23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23">
+        <v>170019</v>
+      </c>
+      <c r="H23" t="s">
+        <v>119</v>
+      </c>
+      <c r="I23" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>50019</v>
+      </c>
+      <c r="B24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24">
+        <v>56</v>
+      </c>
+      <c r="F24" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24">
+        <v>170020</v>
+      </c>
+      <c r="H24" t="s">
+        <v>124</v>
+      </c>
+      <c r="I24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>50020</v>
+      </c>
+      <c r="B25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25">
+        <v>52</v>
+      </c>
+      <c r="F25" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25">
+        <v>170021</v>
+      </c>
+      <c r="H25" t="s">
+        <v>129</v>
+      </c>
+      <c r="I25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>50021</v>
+      </c>
+      <c r="B26" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26">
+        <v>200</v>
+      </c>
+      <c r="F26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26">
+        <v>170022</v>
+      </c>
+      <c r="H26" t="s">
+        <v>134</v>
+      </c>
+      <c r="I26" t="s">
+        <v>30</v>
+      </c>
+      <c r="J26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>50022</v>
+      </c>
+      <c r="B27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27">
+        <v>56</v>
+      </c>
+      <c r="F27" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27">
+        <v>170023</v>
+      </c>
+      <c r="H27" t="s">
+        <v>139</v>
+      </c>
+      <c r="I27" t="s">
+        <v>30</v>
+      </c>
+      <c r="J27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>50023</v>
+      </c>
+      <c r="B28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28">
+        <v>48</v>
+      </c>
+      <c r="F28" t="s">
+        <v>143</v>
+      </c>
+      <c r="G28">
+        <v>170024</v>
+      </c>
+      <c r="H28" t="s">
+        <v>144</v>
+      </c>
+      <c r="I28" t="s">
+        <v>30</v>
+      </c>
+      <c r="J28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>50024</v>
+      </c>
+      <c r="B29" t="s">
+        <v>146</v>
+      </c>
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" t="s">
+        <v>147</v>
+      </c>
+      <c r="E29">
+        <v>58</v>
+      </c>
+      <c r="F29" t="s">
+        <v>148</v>
+      </c>
+      <c r="G29">
+        <v>170025</v>
+      </c>
+      <c r="H29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I29" t="s">
+        <v>30</v>
+      </c>
+      <c r="J29" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>50025</v>
+      </c>
+      <c r="B30" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30">
+        <v>54</v>
+      </c>
+      <c r="F30" t="s">
+        <v>153</v>
+      </c>
+      <c r="G30">
+        <v>170026</v>
+      </c>
+      <c r="H30" t="s">
+        <v>154</v>
+      </c>
+      <c r="I30" t="s">
+        <v>30</v>
+      </c>
+      <c r="J30" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>50026</v>
+      </c>
+      <c r="B31" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" t="s">
+        <v>157</v>
+      </c>
+      <c r="E31">
+        <v>56</v>
+      </c>
+      <c r="F31" t="s">
+        <v>158</v>
+      </c>
+      <c r="G31">
+        <v>170027</v>
+      </c>
+      <c r="H31" t="s">
+        <v>159</v>
+      </c>
+      <c r="I31" t="s">
+        <v>30</v>
+      </c>
+      <c r="J31" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>50027</v>
+      </c>
+      <c r="B32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" t="s">
+        <v>162</v>
+      </c>
+      <c r="E32">
+        <v>52</v>
+      </c>
+      <c r="F32" t="s">
+        <v>163</v>
+      </c>
+      <c r="G32">
+        <v>170028</v>
+      </c>
+      <c r="H32" t="s">
+        <v>164</v>
+      </c>
+      <c r="I32" t="s">
+        <v>30</v>
+      </c>
+      <c r="J32" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>50028</v>
+      </c>
+      <c r="B33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33">
+        <v>54</v>
+      </c>
+      <c r="F33" t="s">
+        <v>168</v>
+      </c>
+      <c r="G33">
+        <v>170029</v>
+      </c>
+      <c r="H33" t="s">
+        <v>169</v>
+      </c>
+      <c r="I33" t="s">
+        <v>30</v>
+      </c>
+      <c r="J33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>50029</v>
+      </c>
+      <c r="B34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34">
+        <v>56</v>
+      </c>
+      <c r="F34" t="s">
+        <v>173</v>
+      </c>
+      <c r="G34">
+        <v>170030</v>
+      </c>
+      <c r="H34" t="s">
+        <v>174</v>
+      </c>
+      <c r="I34" t="s">
+        <v>30</v>
+      </c>
+      <c r="J34" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>50030</v>
+      </c>
+      <c r="B35" t="s">
+        <v>176</v>
+      </c>
+      <c r="C35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" t="s">
+        <v>177</v>
+      </c>
+      <c r="E35">
+        <v>58</v>
+      </c>
+      <c r="F35" t="s">
+        <v>178</v>
+      </c>
+      <c r="G35">
+        <v>170031</v>
+      </c>
+      <c r="H35" t="s">
+        <v>179</v>
+      </c>
+      <c r="I35" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>50031</v>
+      </c>
+      <c r="B36" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36">
+        <v>210</v>
+      </c>
+      <c r="F36" t="s">
+        <v>183</v>
+      </c>
+      <c r="G36">
+        <v>170032</v>
+      </c>
+      <c r="H36" t="s">
+        <v>184</v>
+      </c>
+      <c r="I36" t="s">
+        <v>30</v>
+      </c>
+      <c r="J36" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>50032</v>
+      </c>
+      <c r="B37" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" t="s">
+        <v>187</v>
+      </c>
+      <c r="E37">
+        <v>54</v>
+      </c>
+      <c r="F37" t="s">
+        <v>188</v>
+      </c>
+      <c r="G37">
+        <v>170033</v>
+      </c>
+      <c r="H37" t="s">
+        <v>189</v>
+      </c>
+      <c r="I37" t="s">
+        <v>30</v>
+      </c>
+      <c r="J37" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>50033</v>
+      </c>
+      <c r="B38" t="s">
+        <v>191</v>
+      </c>
+      <c r="C38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" t="s">
+        <v>192</v>
+      </c>
+      <c r="E38">
+        <v>56</v>
+      </c>
+      <c r="F38" t="s">
+        <v>193</v>
+      </c>
+      <c r="G38">
+        <v>170034</v>
+      </c>
+      <c r="H38" t="s">
+        <v>194</v>
+      </c>
+      <c r="I38" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>50034</v>
+      </c>
+      <c r="B39" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" t="s">
+        <v>197</v>
+      </c>
+      <c r="E39">
+        <v>60</v>
+      </c>
+      <c r="F39" t="s">
+        <v>198</v>
+      </c>
+      <c r="G39">
+        <v>170035</v>
+      </c>
+      <c r="H39" t="s">
+        <v>199</v>
+      </c>
+      <c r="I39" t="s">
+        <v>30</v>
+      </c>
+      <c r="J39" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>50035</v>
+      </c>
+      <c r="B40" t="s">
+        <v>201</v>
+      </c>
+      <c r="C40" t="s">
         <v>49</v>
       </c>
-      <c r="C16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16">
+      <c r="D40" t="s">
+        <v>202</v>
+      </c>
+      <c r="E40">
+        <v>96</v>
+      </c>
+      <c r="F40" t="s">
+        <v>203</v>
+      </c>
+      <c r="G40">
+        <v>170036</v>
+      </c>
+      <c r="H40" t="s">
+        <v>204</v>
+      </c>
+      <c r="I40" t="s">
+        <v>53</v>
+      </c>
+      <c r="J40" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>50036</v>
+      </c>
+      <c r="B41" t="s">
+        <v>206</v>
+      </c>
+      <c r="C41" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41">
+        <v>62</v>
+      </c>
+      <c r="F41" t="s">
+        <v>208</v>
+      </c>
+      <c r="G41">
+        <v>170037</v>
+      </c>
+      <c r="H41" t="s">
+        <v>209</v>
+      </c>
+      <c r="I41" t="s">
+        <v>30</v>
+      </c>
+      <c r="J41" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>50037</v>
+      </c>
+      <c r="B42" t="s">
+        <v>211</v>
+      </c>
+      <c r="C42" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" t="s">
+        <v>212</v>
+      </c>
+      <c r="E42">
+        <v>64</v>
+      </c>
+      <c r="F42" t="s">
+        <v>213</v>
+      </c>
+      <c r="G42">
+        <v>170038</v>
+      </c>
+      <c r="H42" t="s">
+        <v>214</v>
+      </c>
+      <c r="I42" t="s">
+        <v>30</v>
+      </c>
+      <c r="J42" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>50038</v>
+      </c>
+      <c r="B43" t="s">
+        <v>216</v>
+      </c>
+      <c r="C43" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" t="s">
+        <v>217</v>
+      </c>
+      <c r="E43">
+        <v>60</v>
+      </c>
+      <c r="F43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G43">
+        <v>170039</v>
+      </c>
+      <c r="H43" t="s">
+        <v>219</v>
+      </c>
+      <c r="I43" t="s">
+        <v>30</v>
+      </c>
+      <c r="J43" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>50039</v>
+      </c>
+      <c r="B44" t="s">
+        <v>221</v>
+      </c>
+      <c r="C44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" t="s">
+        <v>222</v>
+      </c>
+      <c r="E44">
+        <v>62</v>
+      </c>
+      <c r="F44" t="s">
+        <v>223</v>
+      </c>
+      <c r="G44">
+        <v>170040</v>
+      </c>
+      <c r="H44" t="s">
+        <v>224</v>
+      </c>
+      <c r="I44" t="s">
+        <v>30</v>
+      </c>
+      <c r="J44" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>50040</v>
+      </c>
+      <c r="B45" t="s">
+        <v>226</v>
+      </c>
+      <c r="C45" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" t="s">
+        <v>227</v>
+      </c>
+      <c r="E45">
+        <v>60</v>
+      </c>
+      <c r="F45" t="s">
+        <v>228</v>
+      </c>
+      <c r="G45">
+        <v>170041</v>
+      </c>
+      <c r="H45" t="s">
+        <v>229</v>
+      </c>
+      <c r="I45" t="s">
+        <v>30</v>
+      </c>
+      <c r="J45" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>50041</v>
+      </c>
+      <c r="B46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C46" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" t="s">
+        <v>232</v>
+      </c>
+      <c r="E46">
+        <v>220</v>
+      </c>
+      <c r="F46" t="s">
+        <v>233</v>
+      </c>
+      <c r="G46">
+        <v>170042</v>
+      </c>
+      <c r="H46" t="s">
+        <v>234</v>
+      </c>
+      <c r="I46" t="s">
+        <v>30</v>
+      </c>
+      <c r="J46" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>50042</v>
+      </c>
+      <c r="B47" t="s">
+        <v>236</v>
+      </c>
+      <c r="C47" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" t="s">
+        <v>237</v>
+      </c>
+      <c r="E47">
+        <v>64</v>
+      </c>
+      <c r="F47" t="s">
+        <v>238</v>
+      </c>
+      <c r="G47">
+        <v>170043</v>
+      </c>
+      <c r="H47" t="s">
+        <v>239</v>
+      </c>
+      <c r="I47" t="s">
+        <v>30</v>
+      </c>
+      <c r="J47" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>50043</v>
+      </c>
+      <c r="B48" t="s">
+        <v>241</v>
+      </c>
+      <c r="C48" t="s">
+        <v>33</v>
+      </c>
+      <c r="D48" t="s">
+        <v>242</v>
+      </c>
+      <c r="E48">
+        <v>62</v>
+      </c>
+      <c r="F48" t="s">
+        <v>243</v>
+      </c>
+      <c r="G48">
+        <v>170044</v>
+      </c>
+      <c r="H48" t="s">
+        <v>244</v>
+      </c>
+      <c r="I48" t="s">
+        <v>30</v>
+      </c>
+      <c r="J48" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>50044</v>
+      </c>
+      <c r="B49" t="s">
+        <v>246</v>
+      </c>
+      <c r="C49" t="s">
+        <v>33</v>
+      </c>
+      <c r="D49" t="s">
+        <v>247</v>
+      </c>
+      <c r="E49">
+        <v>60</v>
+      </c>
+      <c r="F49" t="s">
+        <v>248</v>
+      </c>
+      <c r="G49">
+        <v>170045</v>
+      </c>
+      <c r="H49" t="s">
+        <v>249</v>
+      </c>
+      <c r="I49" t="s">
+        <v>30</v>
+      </c>
+      <c r="J49" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>50045</v>
+      </c>
+      <c r="B50" t="s">
+        <v>251</v>
+      </c>
+      <c r="C50" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50" t="s">
+        <v>252</v>
+      </c>
+      <c r="E50">
+        <v>64</v>
+      </c>
+      <c r="F50" t="s">
+        <v>253</v>
+      </c>
+      <c r="G50">
+        <v>170046</v>
+      </c>
+      <c r="H50" t="s">
+        <v>254</v>
+      </c>
+      <c r="I50" t="s">
+        <v>30</v>
+      </c>
+      <c r="J50" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50046</v>
+      </c>
+      <c r="B51" t="s">
+        <v>256</v>
+      </c>
+      <c r="C51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" t="s">
+        <v>257</v>
+      </c>
+      <c r="E51">
+        <v>105</v>
+      </c>
+      <c r="F51" t="s">
+        <v>258</v>
+      </c>
+      <c r="G51">
+        <v>170047</v>
+      </c>
+      <c r="H51" t="s">
+        <v>259</v>
+      </c>
+      <c r="I51" t="s">
+        <v>53</v>
+      </c>
+      <c r="J51" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>50047</v>
+      </c>
+      <c r="B52" t="s">
+        <v>261</v>
+      </c>
+      <c r="C52" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" t="s">
+        <v>262</v>
+      </c>
+      <c r="E52">
+        <v>66</v>
+      </c>
+      <c r="F52" t="s">
+        <v>263</v>
+      </c>
+      <c r="G52">
+        <v>170048</v>
+      </c>
+      <c r="H52" t="s">
+        <v>264</v>
+      </c>
+      <c r="I52" t="s">
+        <v>30</v>
+      </c>
+      <c r="J52" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>50048</v>
+      </c>
+      <c r="B53" t="s">
+        <v>266</v>
+      </c>
+      <c r="C53" t="s">
+        <v>33</v>
+      </c>
+      <c r="D53" t="s">
+        <v>267</v>
+      </c>
+      <c r="E53">
+        <v>66</v>
+      </c>
+      <c r="F53" t="s">
+        <v>268</v>
+      </c>
+      <c r="G53">
+        <v>170049</v>
+      </c>
+      <c r="H53" t="s">
+        <v>269</v>
+      </c>
+      <c r="I53" t="s">
+        <v>30</v>
+      </c>
+      <c r="J53" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>50049</v>
+      </c>
+      <c r="B54" t="s">
+        <v>271</v>
+      </c>
+      <c r="C54" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" t="s">
+        <v>272</v>
+      </c>
+      <c r="E54">
+        <v>62</v>
+      </c>
+      <c r="F54" t="s">
+        <v>273</v>
+      </c>
+      <c r="G54">
+        <v>170050</v>
+      </c>
+      <c r="H54" t="s">
+        <v>274</v>
+      </c>
+      <c r="I54" t="s">
+        <v>30</v>
+      </c>
+      <c r="J54" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>50050</v>
+      </c>
+      <c r="B55" t="s">
+        <v>276</v>
+      </c>
+      <c r="C55" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" t="s">
+        <v>277</v>
+      </c>
+      <c r="E55">
+        <v>68</v>
+      </c>
+      <c r="F55" t="s">
+        <v>278</v>
+      </c>
+      <c r="G55">
+        <v>170051</v>
+      </c>
+      <c r="H55" t="s">
+        <v>279</v>
+      </c>
+      <c r="I55" t="s">
+        <v>30</v>
+      </c>
+      <c r="J55" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>50051</v>
+      </c>
+      <c r="B56" t="s">
+        <v>281</v>
+      </c>
+      <c r="C56" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" t="s">
+        <v>282</v>
+      </c>
+      <c r="E56">
+        <v>230</v>
+      </c>
+      <c r="F56" t="s">
+        <v>283</v>
+      </c>
+      <c r="G56">
+        <v>170052</v>
+      </c>
+      <c r="H56" t="s">
+        <v>284</v>
+      </c>
+      <c r="I56" t="s">
+        <v>30</v>
+      </c>
+      <c r="J56" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>50052</v>
+      </c>
+      <c r="B57" t="s">
+        <v>286</v>
+      </c>
+      <c r="C57" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" t="s">
+        <v>287</v>
+      </c>
+      <c r="E57">
+        <v>72</v>
+      </c>
+      <c r="F57" t="s">
+        <v>288</v>
+      </c>
+      <c r="G57">
+        <v>170053</v>
+      </c>
+      <c r="H57" t="s">
+        <v>289</v>
+      </c>
+      <c r="I57" t="s">
+        <v>30</v>
+      </c>
+      <c r="J57" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>50053</v>
+      </c>
+      <c r="B58" t="s">
+        <v>291</v>
+      </c>
+      <c r="C58" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" t="s">
+        <v>292</v>
+      </c>
+      <c r="E58">
+        <v>70</v>
+      </c>
+      <c r="F58" t="s">
+        <v>293</v>
+      </c>
+      <c r="G58">
+        <v>170054</v>
+      </c>
+      <c r="H58" t="s">
+        <v>294</v>
+      </c>
+      <c r="I58" t="s">
+        <v>30</v>
+      </c>
+      <c r="J58" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>50054</v>
+      </c>
+      <c r="B59" t="s">
+        <v>296</v>
+      </c>
+      <c r="C59" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" t="s">
+        <v>297</v>
+      </c>
+      <c r="E59">
+        <v>72</v>
+      </c>
+      <c r="F59" t="s">
+        <v>298</v>
+      </c>
+      <c r="G59">
+        <v>170055</v>
+      </c>
+      <c r="H59" t="s">
+        <v>299</v>
+      </c>
+      <c r="I59" t="s">
+        <v>30</v>
+      </c>
+      <c r="J59" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>50055</v>
+      </c>
+      <c r="B60" t="s">
+        <v>301</v>
+      </c>
+      <c r="C60" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" t="s">
+        <v>302</v>
+      </c>
+      <c r="E60">
+        <v>70</v>
+      </c>
+      <c r="F60" t="s">
+        <v>303</v>
+      </c>
+      <c r="G60">
+        <v>170056</v>
+      </c>
+      <c r="H60" t="s">
+        <v>304</v>
+      </c>
+      <c r="I60" t="s">
+        <v>30</v>
+      </c>
+      <c r="J60" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>50056</v>
+      </c>
+      <c r="B61" t="s">
+        <v>306</v>
+      </c>
+      <c r="C61" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" t="s">
+        <v>307</v>
+      </c>
+      <c r="E61">
+        <v>74</v>
+      </c>
+      <c r="F61" t="s">
+        <v>308</v>
+      </c>
+      <c r="G61">
+        <v>170057</v>
+      </c>
+      <c r="H61" t="s">
+        <v>309</v>
+      </c>
+      <c r="I61" t="s">
+        <v>30</v>
+      </c>
+      <c r="J61" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>50057</v>
+      </c>
+      <c r="B62" t="s">
+        <v>311</v>
+      </c>
+      <c r="C62" t="s">
+        <v>33</v>
+      </c>
+      <c r="D62" t="s">
+        <v>312</v>
+      </c>
+      <c r="E62">
+        <v>76</v>
+      </c>
+      <c r="F62" t="s">
+        <v>313</v>
+      </c>
+      <c r="G62">
+        <v>170058</v>
+      </c>
+      <c r="H62" t="s">
+        <v>314</v>
+      </c>
+      <c r="I62" t="s">
+        <v>30</v>
+      </c>
+      <c r="J62" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>50058</v>
+      </c>
+      <c r="B63" t="s">
+        <v>316</v>
+      </c>
+      <c r="C63" t="s">
+        <v>71</v>
+      </c>
+      <c r="D63" t="s">
+        <v>317</v>
+      </c>
+      <c r="E63">
+        <v>180</v>
+      </c>
+      <c r="F63" t="s">
+        <v>318</v>
+      </c>
+      <c r="G63">
+        <v>170059</v>
+      </c>
+      <c r="H63" t="s">
+        <v>319</v>
+      </c>
+      <c r="I63" t="s">
+        <v>30</v>
+      </c>
+      <c r="J63" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>50059</v>
+      </c>
+      <c r="B64" t="s">
+        <v>321</v>
+      </c>
+      <c r="C64" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" t="s">
+        <v>322</v>
+      </c>
+      <c r="E64">
+        <v>78</v>
+      </c>
+      <c r="F64" t="s">
+        <v>323</v>
+      </c>
+      <c r="G64">
+        <v>170060</v>
+      </c>
+      <c r="H64" t="s">
+        <v>324</v>
+      </c>
+      <c r="I64" t="s">
+        <v>30</v>
+      </c>
+      <c r="J64" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>50060</v>
+      </c>
+      <c r="B65" t="s">
+        <v>326</v>
+      </c>
+      <c r="C65" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" t="s">
+        <v>327</v>
+      </c>
+      <c r="E65">
+        <v>74</v>
+      </c>
+      <c r="F65" t="s">
+        <v>328</v>
+      </c>
+      <c r="G65">
+        <v>170061</v>
+      </c>
+      <c r="H65" t="s">
+        <v>329</v>
+      </c>
+      <c r="I65" t="s">
+        <v>30</v>
+      </c>
+      <c r="J65" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>50061</v>
+      </c>
+      <c r="B66" t="s">
+        <v>331</v>
+      </c>
+      <c r="C66" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" t="s">
+        <v>332</v>
+      </c>
+      <c r="E66">
+        <v>240</v>
+      </c>
+      <c r="F66" t="s">
+        <v>333</v>
+      </c>
+      <c r="G66">
+        <v>170062</v>
+      </c>
+      <c r="H66" t="s">
+        <v>334</v>
+      </c>
+      <c r="I66" t="s">
+        <v>30</v>
+      </c>
+      <c r="J66" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>50062</v>
+      </c>
+      <c r="B67" t="s">
+        <v>336</v>
+      </c>
+      <c r="C67" t="s">
+        <v>49</v>
+      </c>
+      <c r="D67" t="s">
+        <v>337</v>
+      </c>
+      <c r="E67">
+        <v>115</v>
+      </c>
+      <c r="F67" t="s">
+        <v>338</v>
+      </c>
+      <c r="G67">
+        <v>170063</v>
+      </c>
+      <c r="H67" t="s">
+        <v>339</v>
+      </c>
+      <c r="I67" t="s">
+        <v>53</v>
+      </c>
+      <c r="J67" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>50063</v>
+      </c>
+      <c r="B68" t="s">
+        <v>341</v>
+      </c>
+      <c r="C68" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68" t="s">
+        <v>342</v>
+      </c>
+      <c r="E68">
+        <v>80</v>
+      </c>
+      <c r="F68" t="s">
+        <v>343</v>
+      </c>
+      <c r="G68">
+        <v>170064</v>
+      </c>
+      <c r="H68" t="s">
+        <v>344</v>
+      </c>
+      <c r="I68" t="s">
+        <v>30</v>
+      </c>
+      <c r="J68" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>50064</v>
+      </c>
+      <c r="B69" t="s">
+        <v>346</v>
+      </c>
+      <c r="C69" t="s">
+        <v>33</v>
+      </c>
+      <c r="D69" t="s">
+        <v>347</v>
+      </c>
+      <c r="E69">
+        <v>78</v>
+      </c>
+      <c r="F69" t="s">
+        <v>348</v>
+      </c>
+      <c r="G69">
+        <v>170065</v>
+      </c>
+      <c r="H69" t="s">
+        <v>349</v>
+      </c>
+      <c r="I69" t="s">
+        <v>30</v>
+      </c>
+      <c r="J69" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>50065</v>
+      </c>
+      <c r="B70" t="s">
+        <v>351</v>
+      </c>
+      <c r="C70" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" t="s">
+        <v>352</v>
+      </c>
+      <c r="E70">
+        <v>82</v>
+      </c>
+      <c r="F70" t="s">
+        <v>353</v>
+      </c>
+      <c r="G70">
+        <v>170066</v>
+      </c>
+      <c r="H70" t="s">
+        <v>354</v>
+      </c>
+      <c r="I70" t="s">
+        <v>30</v>
+      </c>
+      <c r="J70" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>50066</v>
+      </c>
+      <c r="B71" t="s">
+        <v>356</v>
+      </c>
+      <c r="C71" t="s">
+        <v>33</v>
+      </c>
+      <c r="D71" t="s">
+        <v>357</v>
+      </c>
+      <c r="E71">
+        <v>84</v>
+      </c>
+      <c r="F71" t="s">
+        <v>358</v>
+      </c>
+      <c r="G71">
+        <v>170067</v>
+      </c>
+      <c r="H71" t="s">
+        <v>359</v>
+      </c>
+      <c r="I71" t="s">
+        <v>30</v>
+      </c>
+      <c r="J71" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>50067</v>
+      </c>
+      <c r="B72" t="s">
+        <v>361</v>
+      </c>
+      <c r="C72" t="s">
+        <v>33</v>
+      </c>
+      <c r="D72" t="s">
+        <v>362</v>
+      </c>
+      <c r="E72">
+        <v>80</v>
+      </c>
+      <c r="F72" t="s">
+        <v>363</v>
+      </c>
+      <c r="G72">
+        <v>170068</v>
+      </c>
+      <c r="H72" t="s">
+        <v>364</v>
+      </c>
+      <c r="I72" t="s">
+        <v>30</v>
+      </c>
+      <c r="J72" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>50068</v>
+      </c>
+      <c r="B73" t="s">
+        <v>366</v>
+      </c>
+      <c r="C73" t="s">
+        <v>49</v>
+      </c>
+      <c r="D73" t="s">
+        <v>367</v>
+      </c>
+      <c r="E73">
+        <v>125</v>
+      </c>
+      <c r="F73" t="s">
+        <v>368</v>
+      </c>
+      <c r="G73">
+        <v>170069</v>
+      </c>
+      <c r="H73" t="s">
+        <v>369</v>
+      </c>
+      <c r="I73" t="s">
+        <v>53</v>
+      </c>
+      <c r="J73" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>50069</v>
+      </c>
+      <c r="B74" t="s">
+        <v>371</v>
+      </c>
+      <c r="C74" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" t="s">
+        <v>372</v>
+      </c>
+      <c r="E74">
+        <v>78</v>
+      </c>
+      <c r="F74" t="s">
+        <v>373</v>
+      </c>
+      <c r="G74">
+        <v>170070</v>
+      </c>
+      <c r="H74" t="s">
+        <v>374</v>
+      </c>
+      <c r="I74" t="s">
+        <v>30</v>
+      </c>
+      <c r="J74" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>50070</v>
+      </c>
+      <c r="B75" t="s">
+        <v>376</v>
+      </c>
+      <c r="C75" t="s">
+        <v>33</v>
+      </c>
+      <c r="D75" t="s">
+        <v>377</v>
+      </c>
+      <c r="E75">
+        <v>82</v>
+      </c>
+      <c r="F75" t="s">
+        <v>378</v>
+      </c>
+      <c r="G75">
+        <v>170071</v>
+      </c>
+      <c r="H75" t="s">
+        <v>379</v>
+      </c>
+      <c r="I75" t="s">
+        <v>30</v>
+      </c>
+      <c r="J75" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>50071</v>
+      </c>
+      <c r="B76" t="s">
+        <v>381</v>
+      </c>
+      <c r="C76" t="s">
+        <v>71</v>
+      </c>
+      <c r="D76" t="s">
+        <v>382</v>
+      </c>
+      <c r="E76">
+        <v>260</v>
+      </c>
+      <c r="F76" t="s">
+        <v>383</v>
+      </c>
+      <c r="G76">
+        <v>170072</v>
+      </c>
+      <c r="H76" t="s">
+        <v>384</v>
+      </c>
+      <c r="I76" t="s">
+        <v>30</v>
+      </c>
+      <c r="J76" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>50072</v>
+      </c>
+      <c r="B77" t="s">
+        <v>386</v>
+      </c>
+      <c r="C77" t="s">
+        <v>49</v>
+      </c>
+      <c r="D77" t="s">
+        <v>387</v>
+      </c>
+      <c r="E77">
+        <v>125</v>
+      </c>
+      <c r="F77" t="s">
+        <v>388</v>
+      </c>
+      <c r="G77">
+        <v>170073</v>
+      </c>
+      <c r="H77" t="s">
+        <v>389</v>
+      </c>
+      <c r="I77" t="s">
+        <v>53</v>
+      </c>
+      <c r="J77" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>50073</v>
+      </c>
+      <c r="B78" t="s">
+        <v>391</v>
+      </c>
+      <c r="C78" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" t="s">
+        <v>392</v>
+      </c>
+      <c r="E78">
+        <v>84</v>
+      </c>
+      <c r="F78" t="s">
+        <v>393</v>
+      </c>
+      <c r="G78">
+        <v>170074</v>
+      </c>
+      <c r="H78" t="s">
+        <v>394</v>
+      </c>
+      <c r="I78" t="s">
+        <v>30</v>
+      </c>
+      <c r="J78" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>50074</v>
+      </c>
+      <c r="B79" t="s">
+        <v>396</v>
+      </c>
+      <c r="C79" t="s">
+        <v>33</v>
+      </c>
+      <c r="D79" t="s">
+        <v>397</v>
+      </c>
+      <c r="E79">
+        <v>88</v>
+      </c>
+      <c r="F79" t="s">
+        <v>398</v>
+      </c>
+      <c r="G79">
+        <v>170075</v>
+      </c>
+      <c r="H79" t="s">
+        <v>399</v>
+      </c>
+      <c r="I79" t="s">
+        <v>30</v>
+      </c>
+      <c r="J79" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>50075</v>
+      </c>
+      <c r="B80" t="s">
+        <v>401</v>
+      </c>
+      <c r="C80" t="s">
+        <v>49</v>
+      </c>
+      <c r="D80" t="s">
+        <v>402</v>
+      </c>
+      <c r="E80">
+        <v>130</v>
+      </c>
+      <c r="F80" t="s">
+        <v>403</v>
+      </c>
+      <c r="G80">
+        <v>170076</v>
+      </c>
+      <c r="H80" t="s">
+        <v>404</v>
+      </c>
+      <c r="I80" t="s">
+        <v>53</v>
+      </c>
+      <c r="J80" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>50076</v>
+      </c>
+      <c r="B81" t="s">
+        <v>406</v>
+      </c>
+      <c r="C81" t="s">
+        <v>33</v>
+      </c>
+      <c r="D81" t="s">
+        <v>407</v>
+      </c>
+      <c r="E81">
+        <v>86</v>
+      </c>
+      <c r="F81" t="s">
+        <v>408</v>
+      </c>
+      <c r="G81">
+        <v>170077</v>
+      </c>
+      <c r="H81" t="s">
+        <v>409</v>
+      </c>
+      <c r="I81" t="s">
+        <v>30</v>
+      </c>
+      <c r="J81" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>50077</v>
+      </c>
+      <c r="B82" t="s">
+        <v>411</v>
+      </c>
+      <c r="C82" t="s">
+        <v>49</v>
+      </c>
+      <c r="D82" t="s">
+        <v>412</v>
+      </c>
+      <c r="E82">
+        <v>135</v>
+      </c>
+      <c r="F82" t="s">
+        <v>413</v>
+      </c>
+      <c r="G82">
+        <v>170078</v>
+      </c>
+      <c r="H82" t="s">
+        <v>414</v>
+      </c>
+      <c r="I82" t="s">
+        <v>53</v>
+      </c>
+      <c r="J82" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>50078</v>
+      </c>
+      <c r="B83" t="s">
+        <v>416</v>
+      </c>
+      <c r="C83" t="s">
+        <v>33</v>
+      </c>
+      <c r="D83" t="s">
+        <v>417</v>
+      </c>
+      <c r="E83">
+        <v>88</v>
+      </c>
+      <c r="F83" t="s">
+        <v>418</v>
+      </c>
+      <c r="G83">
+        <v>170079</v>
+      </c>
+      <c r="H83" t="s">
+        <v>419</v>
+      </c>
+      <c r="I83" t="s">
+        <v>30</v>
+      </c>
+      <c r="J83" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>50079</v>
+      </c>
+      <c r="B84" t="s">
+        <v>421</v>
+      </c>
+      <c r="C84" t="s">
+        <v>33</v>
+      </c>
+      <c r="D84" t="s">
+        <v>422</v>
+      </c>
+      <c r="E84">
+        <v>90</v>
+      </c>
+      <c r="F84" t="s">
+        <v>423</v>
+      </c>
+      <c r="G84">
+        <v>170080</v>
+      </c>
+      <c r="H84" t="s">
+        <v>424</v>
+      </c>
+      <c r="I84" t="s">
+        <v>30</v>
+      </c>
+      <c r="J84" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>50080</v>
+      </c>
+      <c r="B85" t="s">
+        <v>426</v>
+      </c>
+      <c r="C85" t="s">
+        <v>33</v>
+      </c>
+      <c r="D85" t="s">
+        <v>427</v>
+      </c>
+      <c r="E85">
+        <v>94</v>
+      </c>
+      <c r="F85" t="s">
+        <v>428</v>
+      </c>
+      <c r="G85">
+        <v>170081</v>
+      </c>
+      <c r="H85" t="s">
+        <v>429</v>
+      </c>
+      <c r="I85" t="s">
+        <v>30</v>
+      </c>
+      <c r="J85" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>50081</v>
+      </c>
+      <c r="B86" t="s">
+        <v>431</v>
+      </c>
+      <c r="C86" t="s">
+        <v>71</v>
+      </c>
+      <c r="D86" t="s">
+        <v>432</v>
+      </c>
+      <c r="E86">
+        <v>270</v>
+      </c>
+      <c r="F86" t="s">
+        <v>433</v>
+      </c>
+      <c r="G86">
+        <v>170082</v>
+      </c>
+      <c r="H86" t="s">
+        <v>434</v>
+      </c>
+      <c r="I86" t="s">
+        <v>30</v>
+      </c>
+      <c r="J86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>50082</v>
+      </c>
+      <c r="B87" t="s">
+        <v>436</v>
+      </c>
+      <c r="C87" t="s">
+        <v>33</v>
+      </c>
+      <c r="D87" t="s">
+        <v>437</v>
+      </c>
+      <c r="E87">
+        <v>90</v>
+      </c>
+      <c r="F87" t="s">
+        <v>438</v>
+      </c>
+      <c r="G87">
+        <v>170083</v>
+      </c>
+      <c r="H87" t="s">
+        <v>439</v>
+      </c>
+      <c r="I87" t="s">
+        <v>30</v>
+      </c>
+      <c r="J87" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>50083</v>
+      </c>
+      <c r="B88" t="s">
+        <v>441</v>
+      </c>
+      <c r="C88" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" t="s">
+        <v>442</v>
+      </c>
+      <c r="E88">
+        <v>92</v>
+      </c>
+      <c r="F88" t="s">
+        <v>443</v>
+      </c>
+      <c r="G88">
+        <v>170084</v>
+      </c>
+      <c r="H88" t="s">
+        <v>444</v>
+      </c>
+      <c r="I88" t="s">
+        <v>30</v>
+      </c>
+      <c r="J88" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>50084</v>
+      </c>
+      <c r="B89" t="s">
+        <v>446</v>
+      </c>
+      <c r="C89" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" t="s">
+        <v>447</v>
+      </c>
+      <c r="E89">
+        <v>96</v>
+      </c>
+      <c r="F89" t="s">
+        <v>448</v>
+      </c>
+      <c r="G89">
+        <v>170085</v>
+      </c>
+      <c r="H89" t="s">
+        <v>449</v>
+      </c>
+      <c r="I89" t="s">
+        <v>30</v>
+      </c>
+      <c r="J89" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>50085</v>
+      </c>
+      <c r="B90" t="s">
+        <v>451</v>
+      </c>
+      <c r="C90" t="s">
+        <v>49</v>
+      </c>
+      <c r="D90" t="s">
+        <v>452</v>
+      </c>
+      <c r="E90">
+        <v>140</v>
+      </c>
+      <c r="F90" t="s">
+        <v>453</v>
+      </c>
+      <c r="G90">
+        <v>170086</v>
+      </c>
+      <c r="H90" t="s">
+        <v>454</v>
+      </c>
+      <c r="I90" t="s">
+        <v>53</v>
+      </c>
+      <c r="J90" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>50086</v>
+      </c>
+      <c r="B91" t="s">
+        <v>456</v>
+      </c>
+      <c r="C91" t="s">
+        <v>49</v>
+      </c>
+      <c r="D91" t="s">
+        <v>457</v>
+      </c>
+      <c r="E91">
+        <v>145</v>
+      </c>
+      <c r="F91" t="s">
+        <v>458</v>
+      </c>
+      <c r="G91">
+        <v>170087</v>
+      </c>
+      <c r="H91" t="s">
+        <v>459</v>
+      </c>
+      <c r="I91" t="s">
+        <v>53</v>
+      </c>
+      <c r="J91" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>50087</v>
+      </c>
+      <c r="B92" t="s">
+        <v>461</v>
+      </c>
+      <c r="C92" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" t="s">
+        <v>462</v>
+      </c>
+      <c r="E92">
+        <v>100</v>
+      </c>
+      <c r="F92" t="s">
+        <v>463</v>
+      </c>
+      <c r="G92">
+        <v>170088</v>
+      </c>
+      <c r="H92" t="s">
+        <v>464</v>
+      </c>
+      <c r="I92" t="s">
+        <v>30</v>
+      </c>
+      <c r="J92" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>50088</v>
+      </c>
+      <c r="B93" t="s">
+        <v>466</v>
+      </c>
+      <c r="C93" t="s">
+        <v>33</v>
+      </c>
+      <c r="D93" t="s">
+        <v>467</v>
+      </c>
+      <c r="E93">
+        <v>100</v>
+      </c>
+      <c r="F93" t="s">
+        <v>468</v>
+      </c>
+      <c r="G93">
+        <v>170089</v>
+      </c>
+      <c r="H93" t="s">
+        <v>469</v>
+      </c>
+      <c r="I93" t="s">
+        <v>30</v>
+      </c>
+      <c r="J93" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>50089</v>
+      </c>
+      <c r="B94" t="s">
+        <v>471</v>
+      </c>
+      <c r="C94" t="s">
+        <v>33</v>
+      </c>
+      <c r="D94" t="s">
+        <v>472</v>
+      </c>
+      <c r="E94">
+        <v>102</v>
+      </c>
+      <c r="F94" t="s">
+        <v>473</v>
+      </c>
+      <c r="G94">
+        <v>170090</v>
+      </c>
+      <c r="H94" t="s">
+        <v>474</v>
+      </c>
+      <c r="I94" t="s">
+        <v>30</v>
+      </c>
+      <c r="J94" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>50090</v>
+      </c>
+      <c r="B95" t="s">
+        <v>476</v>
+      </c>
+      <c r="C95" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" t="s">
+        <v>477</v>
+      </c>
+      <c r="E95">
+        <v>104</v>
+      </c>
+      <c r="F95" t="s">
+        <v>478</v>
+      </c>
+      <c r="G95">
+        <v>170091</v>
+      </c>
+      <c r="H95" t="s">
+        <v>479</v>
+      </c>
+      <c r="I95" t="s">
+        <v>30</v>
+      </c>
+      <c r="J95" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>50091</v>
+      </c>
+      <c r="B96" t="s">
+        <v>481</v>
+      </c>
+      <c r="C96" t="s">
+        <v>71</v>
+      </c>
+      <c r="D96" t="s">
+        <v>482</v>
+      </c>
+      <c r="E96">
+        <v>280</v>
+      </c>
+      <c r="F96" t="s">
+        <v>483</v>
+      </c>
+      <c r="G96">
+        <v>170092</v>
+      </c>
+      <c r="H96" t="s">
+        <v>484</v>
+      </c>
+      <c r="I96" t="s">
+        <v>30</v>
+      </c>
+      <c r="J96" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>50092</v>
+      </c>
+      <c r="B97" t="s">
+        <v>486</v>
+      </c>
+      <c r="C97" t="s">
+        <v>71</v>
+      </c>
+      <c r="D97" t="s">
+        <v>487</v>
+      </c>
+      <c r="E97">
+        <v>250</v>
+      </c>
+      <c r="F97" t="s">
+        <v>488</v>
+      </c>
+      <c r="G97">
+        <v>170093</v>
+      </c>
+      <c r="H97" t="s">
+        <v>489</v>
+      </c>
+      <c r="I97" t="s">
+        <v>30</v>
+      </c>
+      <c r="J97" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>50093</v>
+      </c>
+      <c r="B98" t="s">
+        <v>491</v>
+      </c>
+      <c r="C98" t="s">
+        <v>71</v>
+      </c>
+      <c r="D98" t="s">
+        <v>492</v>
+      </c>
+      <c r="E98">
+        <v>230</v>
+      </c>
+      <c r="F98" t="s">
+        <v>493</v>
+      </c>
+      <c r="G98">
+        <v>170094</v>
+      </c>
+      <c r="H98" t="s">
+        <v>494</v>
+      </c>
+      <c r="I98" t="s">
+        <v>30</v>
+      </c>
+      <c r="J98" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>50094</v>
+      </c>
+      <c r="B99" t="s">
+        <v>496</v>
+      </c>
+      <c r="C99" t="s">
+        <v>33</v>
+      </c>
+      <c r="D99" t="s">
+        <v>497</v>
+      </c>
+      <c r="E99">
+        <v>108</v>
+      </c>
+      <c r="F99" t="s">
+        <v>498</v>
+      </c>
+      <c r="G99">
+        <v>170095</v>
+      </c>
+      <c r="H99" t="s">
+        <v>499</v>
+      </c>
+      <c r="I99" t="s">
+        <v>30</v>
+      </c>
+      <c r="J99" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>50095</v>
+      </c>
+      <c r="B100" t="s">
+        <v>501</v>
+      </c>
+      <c r="C100" t="s">
+        <v>71</v>
+      </c>
+      <c r="D100" t="s">
+        <v>502</v>
+      </c>
+      <c r="E100">
+        <v>260</v>
+      </c>
+      <c r="F100" t="s">
+        <v>503</v>
+      </c>
+      <c r="G100">
+        <v>170096</v>
+      </c>
+      <c r="H100" t="s">
+        <v>504</v>
+      </c>
+      <c r="I100" t="s">
+        <v>30</v>
+      </c>
+      <c r="J100" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>50096</v>
+      </c>
+      <c r="B101" t="s">
+        <v>506</v>
+      </c>
+      <c r="C101" t="s">
+        <v>49</v>
+      </c>
+      <c r="D101" t="s">
+        <v>507</v>
+      </c>
+      <c r="E101">
+        <v>155</v>
+      </c>
+      <c r="F101" t="s">
+        <v>508</v>
+      </c>
+      <c r="G101">
+        <v>170097</v>
+      </c>
+      <c r="H101" t="s">
+        <v>509</v>
+      </c>
+      <c r="I101" t="s">
+        <v>53</v>
+      </c>
+      <c r="J101" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>50097</v>
+      </c>
+      <c r="B102" t="s">
+        <v>511</v>
+      </c>
+      <c r="C102" t="s">
+        <v>33</v>
+      </c>
+      <c r="D102" t="s">
         <v>512</v>
       </c>
-      <c r="F16" t="s">
-        <v>51</v>
+      <c r="E102">
+        <v>110</v>
+      </c>
+      <c r="F102" t="s">
+        <v>513</v>
+      </c>
+      <c r="G102">
+        <v>170098</v>
+      </c>
+      <c r="H102" t="s">
+        <v>514</v>
+      </c>
+      <c r="I102" t="s">
+        <v>30</v>
+      </c>
+      <c r="J102" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>50098</v>
+      </c>
+      <c r="B103" t="s">
+        <v>516</v>
+      </c>
+      <c r="C103" t="s">
+        <v>49</v>
+      </c>
+      <c r="D103" t="s">
+        <v>517</v>
+      </c>
+      <c r="E103">
+        <v>155</v>
+      </c>
+      <c r="F103" t="s">
+        <v>518</v>
+      </c>
+      <c r="G103">
+        <v>170099</v>
+      </c>
+      <c r="H103" t="s">
+        <v>519</v>
+      </c>
+      <c r="I103" t="s">
+        <v>53</v>
+      </c>
+      <c r="J103" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>50099</v>
+      </c>
+      <c r="B104" t="s">
+        <v>521</v>
+      </c>
+      <c r="C104" t="s">
+        <v>33</v>
+      </c>
+      <c r="D104" t="s">
+        <v>522</v>
+      </c>
+      <c r="E104">
+        <v>115</v>
+      </c>
+      <c r="F104" t="s">
+        <v>523</v>
+      </c>
+      <c r="G104">
+        <v>170100</v>
+      </c>
+      <c r="H104" t="s">
+        <v>524</v>
+      </c>
+      <c r="I104" t="s">
+        <v>30</v>
+      </c>
+      <c r="J104" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>50100</v>
+      </c>
+      <c r="B105" t="s">
+        <v>526</v>
+      </c>
+      <c r="C105" t="s">
+        <v>49</v>
+      </c>
+      <c r="D105" t="s">
+        <v>527</v>
+      </c>
+      <c r="E105">
+        <v>165</v>
+      </c>
+      <c r="F105" t="s">
+        <v>528</v>
+      </c>
+      <c r="G105">
+        <v>170101</v>
+      </c>
+      <c r="H105" t="s">
+        <v>529</v>
+      </c>
+      <c r="I105" t="s">
+        <v>53</v>
+      </c>
+      <c r="J105" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>50101</v>
+      </c>
+      <c r="B106" t="s">
+        <v>531</v>
+      </c>
+      <c r="C106" t="s">
+        <v>71</v>
+      </c>
+      <c r="D106" t="s">
+        <v>532</v>
+      </c>
+      <c r="E106">
+        <v>300</v>
+      </c>
+      <c r="F106" t="s">
+        <v>533</v>
+      </c>
+      <c r="G106">
+        <v>170102</v>
+      </c>
+      <c r="H106" t="s">
+        <v>534</v>
+      </c>
+      <c r="I106" t="s">
+        <v>30</v>
+      </c>
+      <c r="J106" t="s">
+        <v>535</v>
       </c>
     </row>
   </sheetData>

--- a/策划/excel/5_Enemy.xlsx
+++ b/策划/excel/5_Enemy.xlsx
@@ -2150,8 +2150,10 @@
       <c r="E6">
         <v>48</v>
       </c>
-      <c r="F6" t="s">
-        <v>28</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>{"type":"ACTION","action":"ATTACK","amount":5,"hits":1,"children":[],"weight":1}</t>
+        </is>
       </c>
       <c r="G6">
         <v>170002</v>
@@ -2162,8 +2164,10 @@
       <c r="I6" t="s">
         <v>30</v>
       </c>
-      <c r="J6" t="s">
-        <v>31</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"振翅反扑","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"振翅反扑","amount":5,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"振翅反扑·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"振翅反扑·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"渡鸦·追击","amount":3,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -2182,8 +2186,10 @@
       <c r="E7">
         <v>54</v>
       </c>
-      <c r="F7" t="s">
-        <v>35</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>{"type":"ACTION","action":"ATTACK","moveName":"致命一击","amount":10,"hits":1,"editorId":"sts2-50002-1","editorX":70,"editorY":90,"children":[],"weight":1}</t>
+        </is>
       </c>
       <c r="G7">
         <v>170003</v>
@@ -2194,8 +2200,10 @@
       <c r="I7" t="s">
         <v>30</v>
       </c>
-      <c r="J7" t="s">
-        <v>37</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"破绽刺杀","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"破绽刺杀","amount":10,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"破绽刺杀·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"破绽刺杀·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"劫掠者刺客·追击","amount":7,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -2214,8 +2222,10 @@
       <c r="E8">
         <v>58</v>
       </c>
-      <c r="F8" t="s">
-        <v>40</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"挥砍一式","amount":5,"hits":1,"editorId":"sts2-50003-3","editorX":670,"editorY":90,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"挥砍一式·格挡","amount":5,"editorId":"sts2-50003-4","editorX":670,"editorY":245,"children":[],"weight":1}],"editorId":"sts2-50003-2","editorX":370,"editorY":168,"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"挥砍二式","amount":5,"hits":1,"editorId":"sts2-50003-6","editorX":670,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"挥砍二式·格挡","amount":5,"editorId":"sts2-50003-7","editorX":670,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50003-5","editorX":370,"editorY":478,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"重斧横扫","amount":12,"hits":1,"editorId":"sts2-50003-8","editorX":370,"editorY":710,"children":[],"weight":1}],"editorId":"sts2-50003-1","editorX":70,"editorY":439,"weight":1}</t>
+        </is>
       </c>
       <c r="G8">
         <v>170004</v>
@@ -2226,8 +2236,10 @@
       <c r="I8" t="s">
         <v>30</v>
       </c>
-      <c r="J8" t="s">
-        <v>42</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"重斧姿态","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"重斧姿态","amount":12,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"重斧姿态·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"重斧姿态·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"劫掠者斧手·追击","amount":9,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2246,8 +2258,10 @@
       <c r="E9">
         <v>56</v>
       </c>
-      <c r="F9" t="s">
-        <v>45</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"毒液喷吐","status":200003,"stacks":1,"editorId":"sts2-50004-2","editorX":370,"editorY":90,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":4,"hits":2,"editorId":"sts2-50004-3","editorX":370,"editorY":245,"children":[],"weight":1}],"editorId":"sts2-50004-1","editorX":70,"editorY":168,"weight":1}</t>
+        </is>
       </c>
       <c r="G9">
         <v>170005</v>
@@ -2258,8 +2272,10 @@
       <c r="I9" t="s">
         <v>30</v>
       </c>
-      <c r="J9" t="s">
-        <v>47</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"缚丝蜕变","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"缚丝蜕变","amount":4,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"缚丝蜕变·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"缚丝蜕变·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"盛碗虫（丝）·追击","amount":3,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2278,8 +2294,10 @@
       <c r="E10">
         <v>110</v>
       </c>
-      <c r="F10" t="s">
-        <v>51</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"WAIT","moveName":"沉睡","editorId":"sts2-50005-3","editorX":670,"editorY":90,"children":[],"weight":1}],"editorId":"sts2-50005-2","editorX":370,"editorY":90,"weight":1},{"type":"CONDITION","field":"TURN","operator":"==","value":2,"children":[{"type":"ACTION","action":"BUFF","moveName":"苏醒","status":200001,"stacks":1,"editorId":"sts2-50005-5","editorX":670,"editorY":245,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50005-4","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"连环斩击","amount":13,"hits":1,"editorId":"sts2-50005-6","editorX":370,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50005-1","editorX":70,"editorY":245,"weight":1}</t>
+        </is>
       </c>
       <c r="G10">
         <v>170006</v>
@@ -2290,8 +2308,10 @@
       <c r="I10" t="s">
         <v>53</v>
       </c>
-      <c r="J10" t="s">
-        <v>54</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"古像复苏","condition":"TURN_AT_LEAST","value":3,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210011,"target":"SELF","params":{"status":200013,"stacks":"ALL","amount":"ALL"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"古像复苏","amount":13,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"古像复苏·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"古像复苏·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"旧日雕像·追击","amount":9,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -2310,8 +2330,10 @@
       <c r="E11">
         <v>100</v>
       </c>
-      <c r="F11" t="s">
-        <v>57</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"俯冲","amount":17,"hits":1,"editorId":"sts2-50006-2","editorX":370,"editorY":90,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"啄击","amount":3,"hits":3,"editorId":"sts2-50006-3","editorX":370,"editorY":245,"children":[],"weight":1}],"editorId":"sts2-50006-1","editorX":70,"editorY":168,"weight":1}</t>
+        </is>
       </c>
       <c r="G11">
         <v>170007</v>
@@ -2322,8 +2344,10 @@
       <c r="I11" t="s">
         <v>53</v>
       </c>
-      <c r="J11" t="s">
-        <v>59</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200015,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"坠地狂啄","condition":"HITS_AT_LEAST","value":3,"effects":[{"type":210011,"target":"SELF","params":{"status":200015,"stacks":"ALL","amount":"ALL"},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"坠地狂啄","amount":17,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"坠地狂啄·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"坠地狂啄·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"多尼斯异鸟·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -2342,8 +2366,10 @@
       <c r="E12">
         <v>68</v>
       </c>
-      <c r="F12" t="s">
-        <v>62</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEFEND","moveName":"准备就绪","amount":8,"editorId":"sts2-50007-2","editorX":370,"editorY":90,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"快速拳","amount":5,"hits":2,"editorId":"sts2-50007-4","editorX":670,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"快速拳·脆弱","status":200005,"stacks":1,"editorId":"sts2-50007-5","editorX":670,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50007-3","editorX":370,"editorY":323,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"重拳","amount":14,"hits":1,"editorId":"sts2-50007-6","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50007-1","editorX":70,"editorY":323,"weight":1}</t>
+        </is>
       </c>
       <c r="G12">
         <v>170008</v>
@@ -2354,8 +2380,10 @@
       <c r="I12" t="s">
         <v>30</v>
       </c>
-      <c r="J12" t="s">
-        <v>64</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"过载拳击","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"过载拳击","amount":14,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"过载拳击·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"过载拳击·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"拳击构装体·追击","amount":10,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -2374,8 +2402,10 @@
       <c r="E13">
         <v>64</v>
       </c>
-      <c r="F13" t="s">
-        <v>67</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"水流喷射","amount":10,"hits":1,"editorId":"sts2-50008-2","editorX":370,"editorY":90,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"加压","status":200001,"stacks":1,"editorId":"sts2-50008-3","editorX":370,"editorY":245,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50008-1","editorX":70,"editorY":168,"weight":1}</t>
+        </is>
       </c>
       <c r="G13">
         <v>170009</v>
@@ -2386,8 +2416,10 @@
       <c r="I13" t="s">
         <v>30</v>
       </c>
-      <c r="J13" t="s">
-        <v>69</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"高压喷射","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"高压喷射","amount":10,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"高压喷射·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"高压喷射·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"下水道蚌·追击","amount":7,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -2406,8 +2438,10 @@
       <c r="E14">
         <v>190</v>
       </c>
-      <c r="F14" t="s">
-        <v>73</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"墨迹","amount":7,"hits":1,"editorId":"sts2-50009-2","editorX":370,"editorY":90,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"墨枪","amount":6,"hits":2,"editorId":"sts2-50009-3","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"肢解","amount":26,"hits":1,"editorId":"sts2-50009-4","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"蓄势","status":200001,"stacks":2,"editorId":"sts2-50009-5","editorX":370,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50009-1","editorX":70,"editorY":323,"weight":1}</t>
+        </is>
       </c>
       <c r="G14">
         <v>170010</v>
@@ -2418,8 +2452,10 @@
       <c r="I14" t="s">
         <v>30</v>
       </c>
-      <c r="J14" t="s">
-        <v>75</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"墨影实体化","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"墨影实体化","amount":24,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"墨影实体化·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"墨影实体化·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"墨影幻灵·追击","amount":18,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"墨影实体化·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"墨影实体化·终局","amount":12,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"墨影实体化·终局·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"墨影实体化·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"墨影幻灵·追击","amount":9,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2438,8 +2474,10 @@
       <c r="E15">
         <v>72</v>
       </c>
-      <c r="F15" t="s">
-        <v>78</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"启动·力量","status":200001,"stacks":1,"editorId":"sts2-50010-4","editorX":970,"editorY":90,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEFEND","moveName":"启动·格挡","amount":8,"editorId":"sts2-50010-5","editorX":970,"editorY":245,"children":[],"weight":1}],"editorId":"sts2-50010-3","editorX":670,"editorY":168,"weight":1}],"editorId":"sts2-50010-2","editorX":370,"editorY":168,"weight":1},{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"左右连击","amount":9,"hits":2,"editorId":"sts2-50010-7","editorX":670,"editorY":400,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"铁锤上勾拳","amount":12,"hits":1,"editorId":"sts2-50010-9","editorX":970,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"铁锤上勾拳·虚弱","status":200003,"stacks":2,"editorId":"sts2-50010-10","editorX":970,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEBUFF","moveName":"铁锤上勾拳·脆弱","status":200005,"stacks":2,"editorId":"sts2-50010-11","editorX":970,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50010-8","editorX":670,"editorY":710,"weight":1}],"editorId":"sts2-50010-6","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50010-1","editorX":70,"editorY":362,"weight":1}</t>
+        </is>
       </c>
       <c r="G15">
         <v>170011</v>
@@ -2450,8 +2488,10 @@
       <c r="I15" t="s">
         <v>30</v>
       </c>
-      <c r="J15" t="s">
-        <v>80</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":4,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"重锤启动","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"重锤启动","amount":8,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"重锤启动·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"重锤启动·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"巨斧机器人·追击","amount":6,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2470,8 +2510,10 @@
       <c r="E16">
         <v>300</v>
       </c>
-      <c r="F16" t="s">
-        <v>83</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"退潮","amount":26,"hits":1,"editorId":"sts2-50011-3","editorX":670,"editorY":90,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"退潮·格挡","amount":16,"editorId":"sts2-50011-4","editorX":670,"editorY":245,"children":[],"weight":1}],"editorId":"sts2-50011-2","editorX":370,"editorY":168,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"眼部激光","amount":11,"hits":2,"editorId":"sts2-50011-5","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"EFFECTS","moveName":"强度增长","effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":"1+min(@intensity,2)","duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210034,"target":"SELF","params":{"name":"intensity","operator":"ADD","value":1,"scope":"COMBAT"},"children":[],"elseEffects":[]}],"editorId":"sts2-50011-6","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50011-1","editorX":70,"editorY":362,"weight":1}</t>
+        </is>
       </c>
       <c r="G16">
         <v>170012</v>
@@ -2482,8 +2524,10 @@
       <c r="I16" t="s">
         <v>30</v>
       </c>
-      <c r="J16" t="s">
-        <v>85</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"逆转沙流","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"逆转沙流","amount":24,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"逆转沙流·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"逆转沙流·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"永世沙漏·追击","amount":18,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"逆转沙流·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"逆转沙流·终局","amount":12,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"逆转沙流·终局·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"逆转沙流·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"永世沙漏·追击","amount":9,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2502,8 +2546,10 @@
       <c r="E17">
         <v>48</v>
       </c>
-      <c r="F17" t="s">
-        <v>88</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"干扰凝视","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"长牙撕咬","amount":8,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"双牙突刺","amount":4,"hits":2,"children":[],"weight":1}],"weight":1}</t>
+        </is>
       </c>
       <c r="G17">
         <v>170013</v>
@@ -2514,8 +2560,10 @@
       <c r="I17" t="s">
         <v>30</v>
       </c>
-      <c r="J17" t="s">
-        <v>90</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"凝视聚焦","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"凝视聚焦","amount":8,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"凝视聚焦·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"凝视聚焦·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"长牙之眼·追击","amount":6,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2534,8 +2582,10 @@
       <c r="E18">
         <v>44</v>
       </c>
-      <c r="F18" t="s">
-        <v>93</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":4,"hits":1,"editorId":"sts2-50013-1","editorX":70,"editorY":90,"children":[],"weight":1}</t>
+        </is>
       </c>
       <c r="G18">
         <v>170014</v>
@@ -2546,8 +2596,10 @@
       <c r="I18" t="s">
         <v>30</v>
       </c>
-      <c r="J18" t="s">
-        <v>95</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"枝条硬化","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"枝条硬化","amount":4,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"枝条硬化·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"枝条硬化·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"枝条史莱姆（小）·追击","amount":3,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2566,8 +2618,10 @@
       <c r="E19">
         <v>40</v>
       </c>
-      <c r="F19" t="s">
-        <v>98</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"&gt;=","value":3,"children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"引爆毒囊","amount":18,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"LOSE_HP","moveName":"爆炸自毁","target":"ENEMY","amount":40,"children":[],"weight":1}],"weight":1}],"weight":1},{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"毒气压缩","amount":4,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"泄漏毒雾","status":200006,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"毒气喷射","amount":8,"hits":1,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"引爆毒囊","amount":18,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"LOSE_HP","moveName":"爆炸自毁","target":"ENEMY","amount":40,"children":[],"weight":1}],"weight":1}],"weight":1}],"weight":1}</t>
+        </is>
       </c>
       <c r="G19">
         <v>170015</v>
@@ -2578,8 +2632,10 @@
       <c r="I19" t="s">
         <v>30</v>
       </c>
-      <c r="J19" t="s">
-        <v>100</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"毒气泄漏","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"&gt;=","value":3,"children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"引爆毒囊","amount":18,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"LOSE_HP","moveName":"爆炸自毁","target":"ENEMY","amount":40,"children":[],"weight":1}],"weight":1}],"weight":1},{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"毒气压缩","amount":4,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"泄漏毒雾","status":200006,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"毒气喷射","amount":8,"hits":1,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"引爆毒囊","amount":18,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"LOSE_HP","moveName":"爆炸自毁","target":"ENEMY","amount":40,"children":[],"weight":1}],"weight":1}],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2598,8 +2654,10 @@
       <c r="E20">
         <v>48</v>
       </c>
-      <c r="F20" t="s">
-        <v>103</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":9,"hits":1,"editorId":"sts2-50015-1","editorX":70,"editorY":90,"children":[],"weight":1}</t>
+        </is>
       </c>
       <c r="G20">
         <v>170016</v>
@@ -2610,8 +2668,10 @@
       <c r="I20" t="s">
         <v>30</v>
       </c>
-      <c r="J20" t="s">
-        <v>105</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"绝境冲撞","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"绝境冲撞","amount":9,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"绝境冲撞·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"绝境冲撞·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"鬼祟地精·追击","amount":6,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2630,8 +2690,10 @@
       <c r="E21">
         <v>48</v>
       </c>
-      <c r="F21" t="s">
-        <v>108</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"刺拳","amount":3,"hits":1,"editorId":"sts2-50016-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"旋风连击","amount":2,"hits":3,"editorId":"sts2-50016-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"穿透凝视","amount":10,"hits":1,"editorId":"sts2-50016-4","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50016-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G21">
         <v>170017</v>
@@ -2642,8 +2704,10 @@
       <c r="I21" t="s">
         <v>30</v>
       </c>
-      <c r="J21" t="s">
-        <v>110</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"墨刺爆发","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"墨刺爆发","amount":10,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"墨刺爆发·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"墨刺爆发·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"小墨灵·追击","amount":7,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2662,8 +2726,10 @@
       <c r="E22">
         <v>46</v>
       </c>
-      <c r="F22" t="s">
-        <v>113</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":3,"hits":1,"editorId":"sts2-50017-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"黏浆","status":200020,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50017-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G22">
         <v>170018</v>
@@ -2674,8 +2740,10 @@
       <c r="I22" t="s">
         <v>30</v>
       </c>
-      <c r="J22" t="s">
-        <v>115</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"黏浆包裹","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"黏浆包裹","amount":3,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"黏浆包裹·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"黏浆包裹·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"树叶史莱姆（小）·追击","amount":3,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2694,8 +2762,10 @@
       <c r="E23">
         <v>54</v>
       </c>
-      <c r="F23" t="s">
-        <v>118</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEFEND","moveName":"护住钱袋","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"钱袋砸击","amount":9,"hits":1,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蛮横冲撞","amount":6,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":200014,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1}],"weight":1}</t>
+        </is>
       </c>
       <c r="G23">
         <v>170019</v>
@@ -2706,8 +2776,10 @@
       <c r="I23" t="s">
         <v>30</v>
       </c>
-      <c r="J23" t="s">
-        <v>120</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"护住钱袋","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"护住钱袋","amount":9,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"护住钱袋·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"护住钱袋·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"肥胖地精·追击","amount":6,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2726,8 +2798,10 @@
       <c r="E24">
         <v>56</v>
       </c>
-      <c r="F24" t="s">
-        <v>123</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"抓挠","amount":8,"hits":1,"editorId":"sts2-50019-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"疫病啃咬","amount":6,"hits":1,"editorId":"sts2-50019-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"尖啸·削弱","status":200005,"stacks":1,"editorId":"sts2-50019-4","editorX":370,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"集中自身力量","status":200001,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEFEND","moveName":"强化自身护甲","amount":6,"children":[],"weight":1}],"weight":1}],"editorId":"sts2-50019-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G24">
         <v>170020</v>
@@ -2738,8 +2812,10 @@
       <c r="I24" t="s">
         <v>30</v>
       </c>
-      <c r="J24" t="s">
-        <v>125</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"瘟牙激怒","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"瘟牙激怒","amount":8,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"瘟牙激怒·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"瘟牙激怒·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"双尾鼠·追击","amount":6,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2758,8 +2834,10 @@
       <c r="E25">
         <v>52</v>
       </c>
-      <c r="F25" t="s">
-        <v>128</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"恶毒啃咬","amount":6,"hits":1,"editorId":"sts2-50020-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"蠕动·强化","status":200001,"stacks":1,"editorId":"sts2-50020-3","editorX":370,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50020-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G25">
         <v>170021</v>
@@ -2770,8 +2848,10 @@
       <c r="I25" t="s">
         <v>30</v>
       </c>
-      <c r="J25" t="s">
-        <v>130</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"蠕动蜕皮","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蠕动蜕皮","amount":6,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"蠕动蜕皮·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"蠕动蜕皮·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"蠕动虫·追击","amount":4,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2790,8 +2870,10 @@
       <c r="E26">
         <v>200</v>
       </c>
-      <c r="F26" t="s">
-        <v>133</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":12,"hits":1,"editorId":"sts2-50021-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"膨胀打击","amount":4,"hits":1,"editorId":"sts2-50021-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"虫刺","amount":6,"hits":2,"editorId":"sts2-50021-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"虫刺·削弱","status":200003,"stacks":2,"editorId":"sts2-50021-6","editorX":670,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEBUFF","moveName":"虫刺·削弱","status":200005,"stacks":2,"editorId":"sts2-50021-7","editorX":670,"editorY":1020,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50021-4","editorX":370,"editorY":555,"weight":1},{"type":"ACTION","action":"BUFF","moveName":"适应·强化","status":200001,"stacks":2,"editorId":"sts2-50021-8","editorX":370,"editorY":1175,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"防御打击","amount":12,"hits":1,"editorId":"sts2-50021-10","editorX":670,"editorY":1485,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"防御打击·格挡","amount":16,"editorId":"sts2-50021-11","editorX":670,"editorY":1640,"children":[],"weight":1}],"editorId":"sts2-50021-9","editorX":370,"editorY":1330,"weight":1}],"editorId":"sts2-50021-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G26">
         <v>170022</v>
@@ -2802,8 +2884,10 @@
       <c r="I26" t="s">
         <v>30</v>
       </c>
-      <c r="J26" t="s">
-        <v>135</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":4,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"碎壳适应","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":12,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"碎壳适应","amount":12,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"碎壳适应·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"碎壳适应·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"粉碎者·追击","amount":9,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"碎壳适应·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"碎壳适应·终局","amount":12,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"碎壳适应·终局·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"碎壳适应·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"粉碎者·追击","amount":9,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2822,8 +2906,10 @@
       <c r="E27">
         <v>56</v>
       </c>
-      <c r="F27" t="s">
-        <v>138</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEFEND","moveName":"装填·格挡","amount":3,"editorId":"sts2-50022-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"射击","amount":14,"hits":1,"editorId":"sts2-50022-3","editorX":370,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50022-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G27">
         <v>170023</v>
@@ -2834,8 +2920,10 @@
       <c r="I27" t="s">
         <v>30</v>
       </c>
-      <c r="J27" t="s">
-        <v>140</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"穿甲弩击","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"穿甲弩击","amount":14,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"穿甲弩击·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"穿甲弩击·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"红宝石劫掠者（弩手）·追击","amount":10,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2854,8 +2942,10 @@
       <c r="E28">
         <v>48</v>
       </c>
-      <c r="F28" t="s">
-        <v>143</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>{"type":"ACTION","action":"ATTACK","moveName":"轻咬","amount":4,"hits":1,"editorId":"sts2-50023-1","editorX":70,"editorY":90,"children":[],"weight":1}</t>
+        </is>
       </c>
       <c r="G28">
         <v>170024</v>
@@ -2866,8 +2956,10 @@
       <c r="I28" t="s">
         <v>30</v>
       </c>
-      <c r="J28" t="s">
-        <v>145</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"饥饿轻咬","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"饥饿轻咬","amount":4,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"饥饿轻咬·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"饥饿轻咬·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"幼虫·追击","amount":3,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2886,8 +2978,10 @@
       <c r="E29">
         <v>58</v>
       </c>
-      <c r="F29" t="s">
-        <v>148</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEFEND","moveName":"护盾展开","amount":8,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"盾击反攻","amount":8,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"稳住盾面","amount":4,"children":[],"weight":1}],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"铁臂重击","amount":10,"hits":1,"children":[],"weight":1}],"weight":1}</t>
+        </is>
       </c>
       <c r="G29">
         <v>170025</v>
@@ -2898,8 +2992,10 @@
       <c r="I29" t="s">
         <v>30</v>
       </c>
-      <c r="J29" t="s">
-        <v>150</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"护卫反击","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"护卫反击","amount":10,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"护卫反击·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"护卫反击·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"护卫机器人·追击","amount":7,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_SKILL_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":210002,"target":"SELF","params":{"amount":2,"scale":true},"children":[],"elseEffects":[]}],"filter":{}}]}</t>
+        </is>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2918,8 +3014,10 @@
       <c r="E30">
         <v>54</v>
       </c>
-      <c r="F30" t="s">
-        <v>153</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>{"type":"ACTION","action":"ATTACK","moveName":"猛击","amount":16,"hits":1,"editorId":"sts2-50025-1","editorX":70,"editorY":90,"children":[],"weight":1}</t>
+        </is>
       </c>
       <c r="G30">
         <v>170026</v>
@@ -2930,8 +3028,10 @@
       <c r="I30" t="s">
         <v>30</v>
       </c>
-      <c r="J30" t="s">
-        <v>155</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"恐惧具象","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"恐惧具象","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"恐惧具象·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"恐惧具象·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"幻惧灵·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2950,8 +3050,10 @@
       <c r="E31">
         <v>56</v>
       </c>
-      <c r="F31" t="s">
-        <v>158</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"DEBUFF","moveName":"追踪·削弱","status":200005,"stacks":2,"editorId":"sts2-50026-3","editorX":670,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50026-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"猎犬突袭","amount":3,"hits":3,"editorId":"sts2-50026-4","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50026-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G31">
         <v>170027</v>
@@ -2962,8 +3064,10 @@
       <c r="I31" t="s">
         <v>30</v>
       </c>
-      <c r="J31" t="s">
-        <v>160</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"锁定猎物","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"锁定猎物","amount":3,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"锁定猎物·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"锁定猎物·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"红宝石劫掠者（追踪者）·追击","amount":3,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -2982,8 +3086,10 @@
       <c r="E32">
         <v>52</v>
       </c>
-      <c r="F32" t="s">
-        <v>163</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"BUFF","moveName":"生长尖刺·强化","status":200009,"stacks":1,"editorId":"sts2-50027-2","editorX":370,"editorY":245,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"尖刺喷吐","amount":3,"hits":3,"editorId":"sts2-50027-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"旋转","amount":7,"hits":1,"editorId":"sts2-50027-4","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50027-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G32">
         <v>170028</v>
@@ -2994,8 +3100,10 @@
       <c r="I32" t="s">
         <v>30</v>
       </c>
-      <c r="J32" t="s">
-        <v>165</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200009,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"棘刺成熟","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200005,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"棘刺成熟","amount":3,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"棘刺成熟·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"棘刺成熟·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"蝌蚪·追击","amount":3,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -3014,8 +3122,10 @@
       <c r="E33">
         <v>54</v>
       </c>
-      <c r="F33" t="s">
-        <v>168</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"干扰噪音","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"声波冲击","amount":3,"hits":3,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"高频震荡","amount":7,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"震荡失衡","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1}],"weight":1}</t>
+        </is>
       </c>
       <c r="G33">
         <v>170029</v>
@@ -3026,8 +3136,10 @@
       <c r="I33" t="s">
         <v>30</v>
       </c>
-      <c r="J33" t="s">
-        <v>170</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"噪音过载","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"噪音过载","amount":3,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"噪音过载·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"噪音过载·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"噪音机器人·追击","amount":3,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -3046,8 +3158,10 @@
       <c r="E34">
         <v>56</v>
       </c>
-      <c r="F34" t="s">
-        <v>173</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"刺击","amount":11,"hits":1,"editorId":"sts2-50029-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"刺击·脆弱","status":200005,"stacks":1,"editorId":"sts2-50029-3","editorX":370,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50029-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G34">
         <v>170030</v>
@@ -3058,8 +3172,10 @@
       <c r="I34" t="s">
         <v>30</v>
       </c>
-      <c r="J34" t="s">
-        <v>175</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"针刺加压","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"针刺加压","amount":11,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"针刺加压·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"针刺加压·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"刺击机器人·追击","amount":8,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -3078,8 +3194,10 @@
       <c r="E35">
         <v>58</v>
       </c>
-      <c r="F35" t="s">
-        <v>178</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"电击","amount":14,"hits":1,"editorId":"sts2-50030-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"高压电·力量","status":200001,"stacks":1,"editorId":"sts2-50030-3","editorX":370,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50030-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G35">
         <v>170031</v>
@@ -3090,8 +3208,10 @@
       <c r="I35" t="s">
         <v>30</v>
       </c>
-      <c r="J35" t="s">
-        <v>180</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"高压电流","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"高压电流","amount":14,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"高压电流·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"高压电流·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"电击机器人·追击","amount":10,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -3110,8 +3230,10 @@
       <c r="E36">
         <v>210</v>
       </c>
-      <c r="F36" t="s">
-        <v>183</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"集中自身力量","status":200001,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEFEND","moveName":"强化自身护甲","amount":6,"children":[],"weight":1}],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"排气","amount":16,"hits":1,"editorId":"sts2-50031-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"凝视","amount":7,"hits":1,"editorId":"sts2-50031-4","editorX":370,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"隐没·无实体","status":200008,"stacks":1,"editorId":"sts2-50031-5","editorX":370,"editorY":710,"duration":"NEXT_TURN","children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"尖叫","amount":11,"hits":1,"editorId":"sts2-50031-7","editorX":670,"editorY":1020,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"尖叫·削弱","status":200004,"stacks":3,"editorId":"sts2-50031-8","editorX":670,"editorY":1175,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50031-6","editorX":370,"editorY":865,"weight":1}],"editorId":"sts2-50031-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G36">
         <v>170032</v>
@@ -3122,8 +3244,10 @@
       <c r="I36" t="s">
         <v>30</v>
       </c>
-      <c r="J36" t="s">
-        <v>185</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"魂潮显形","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":9},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"魂潮显形","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"魂潮显形·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"魂潮显形·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"灵魂鱼·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"魂潮显形·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"魂潮显形·终局","amount":12,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"魂潮显形·终局·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"魂潮显形·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"灵魂鱼·追击","amount":9,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -3142,8 +3266,10 @@
       <c r="E37">
         <v>54</v>
       </c>
-      <c r="F37" t="s">
-        <v>188</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"疾行","amount":3,"hits":3,"editorId":"sts2-50032-3","editorX":670,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50032-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"疾行","amount":3,"hits":3,"editorId":"sts2-50032-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"颚击","amount":8,"hits":1,"editorId":"sts2-50032-6","editorX":670,"editorY":865,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"狂怒·强化","status":200001,"stacks":1,"editorId":"sts2-50032-7","editorX":670,"editorY":1020,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50032-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50032-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G37">
         <v>170033</v>
@@ -3154,8 +3280,10 @@
       <c r="I37" t="s">
         <v>30</v>
       </c>
-      <c r="J37" t="s">
-        <v>190</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"外壳剥落","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"外壳剥落","amount":3,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"外壳剥落·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"外壳剥落·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"外骨骼虫·追击","amount":3,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -3174,8 +3302,10 @@
       <c r="E38">
         <v>56</v>
       </c>
-      <c r="F38" t="s">
-        <v>193</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"鞭打","amount":3,"hits":2,"editorId":"sts2-50033-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"猛扑","amount":8,"hits":1,"editorId":"sts2-50033-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"黏液喷吐·削弱","status":200005,"stacks":2,"editorId":"sts2-50033-4","editorX":370,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50033-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G38">
         <v>170034</v>
@@ -3186,8 +3316,10 @@
       <c r="I38" t="s">
         <v>30</v>
       </c>
-      <c r="J38" t="s">
-        <v>195</v>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"尸液沸腾","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"尸液沸腾","amount":8,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"尸液沸腾·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"尸液沸腾·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"尸蛞蝓·追击","amount":6,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -3206,8 +3338,10 @@
       <c r="E39">
         <v>60</v>
       </c>
-      <c r="F39" t="s">
-        <v>198</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"DEBUFF","moveName":"黏液弹","status":200020,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50034-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"黏团弹","amount":11,"hits":1,"editorId":"sts2-50034-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"黏液弹","status":200020,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50034-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50034-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G39">
         <v>170035</v>
@@ -3218,8 +3352,10 @@
       <c r="I39" t="s">
         <v>30</v>
       </c>
-      <c r="J39" t="s">
-        <v>200</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"黏液浓缩","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"黏液浓缩","amount":11,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"黏液浓缩·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"黏液浓缩·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"枝条史莱姆（中）·追击","amount":8,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -3238,8 +3374,10 @@
       <c r="E40">
         <v>96</v>
       </c>
-      <c r="F40" t="s">
-        <v>203</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"啃咬","amount":6,"hits":1,"editorId":"sts2-50035-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"鞭击","amount":7,"hits":1,"editorId":"sts2-50035-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"链锤乱击","amount":3,"hits":3,"editorId":"sts2-50035-4","editorX":370,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"膨大·强化","status":200001,"stacks":1,"editorId":"sts2-50035-5","editorX":370,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50035-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G40">
         <v>170036</v>
@@ -3250,8 +3388,10 @@
       <c r="I40" t="s">
         <v>53</v>
       </c>
-      <c r="J40" t="s">
-        <v>205</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"根须暴长","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"根须暴长","amount":3,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"根须暴长·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"根须暴长·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"幻影园丁·追击","amount":3,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -3270,8 +3410,10 @@
       <c r="E41">
         <v>62</v>
       </c>
-      <c r="F41" t="s">
-        <v>208</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"殴打","amount":7,"hits":1,"editorId":"sts2-50036-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"咆哮·强化","status":200001,"stacks":1,"editorId":"sts2-50036-3","editorX":370,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50036-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G41">
         <v>170037</v>
@@ -3282,8 +3424,10 @@
       <c r="I41" t="s">
         <v>30</v>
       </c>
-      <c r="J41" t="s">
-        <v>210</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200017,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"蛮兵怒吼","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蛮兵怒吼","amount":7,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"蛮兵怒吼·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"蛮兵怒吼·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"红宝石劫掠者（蛮兵）·追击","amount":5,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -3302,8 +3446,10 @@
       <c r="E42">
         <v>64</v>
       </c>
-      <c r="F42" t="s">
-        <v>213</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"猛咬","amount":14,"hits":1,"editorId":"sts2-50037-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"咀嚼","amount":5,"hits":2,"editorId":"sts2-50037-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"增生利齿·强化","status":200001,"stacks":1,"editorId":"sts2-50037-4","editorX":370,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50037-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G42">
         <v>170038</v>
@@ -3314,8 +3460,10 @@
       <c r="I42" t="s">
         <v>30</v>
       </c>
-      <c r="J42" t="s">
-        <v>215</v>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200017,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"利齿增生","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"利齿增生","amount":14,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"利齿增生·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"利齿增生·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"噬咬卷轴·追击","amount":10,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -3334,8 +3482,10 @@
       <c r="E43">
         <v>60</v>
       </c>
-      <c r="F43" t="s">
-        <v>218</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"能量球","amount":3,"hits":1,"editorId":"sts2-50038-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"能量球·强化","status":200001,"stacks":1,"editorId":"sts2-50038-3","editorX":370,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50038-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G43">
         <v>170039</v>
@@ -3346,8 +3496,10 @@
       <c r="I43" t="s">
         <v>30</v>
       </c>
-      <c r="J43" t="s">
-        <v>220</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"果核充能","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"果核充能","amount":3,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"果核充能·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"果核充能·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"咬合杰克果·追击","amount":3,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -3366,8 +3518,10 @@
       <c r="E44">
         <v>62</v>
       </c>
-      <c r="F44" t="s">
-        <v>223</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"黏液弹","status":200020,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"黏团弹","amount":8,"hits":1,"editorId":"sts2-50039-3","editorX":370,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50039-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G44">
         <v>170040</v>
@@ -3378,8 +3532,10 @@
       <c r="I44" t="s">
         <v>30</v>
       </c>
-      <c r="J44" t="s">
-        <v>225</v>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"叶片包裹","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"叶片包裹","amount":8,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"叶片包裹·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"叶片包裹·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"树叶史莱姆（中）·追击","amount":6,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -3398,8 +3554,10 @@
       <c r="E45">
         <v>60</v>
       </c>
-      <c r="F45" t="s">
-        <v>228</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":6,"hits":1,"editorId":"sts2-50040-3","editorX":670,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50040-2","editorX":370,"editorY":245,"weight":1},{"type":"CONDITION","field":"TURN","operator":"==","value":2,"children":[{"type":"ACTION","action":"BUFF","moveName":"强化·强化","status":200001,"stacks":1,"editorId":"sts2-50040-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50040-4","editorX":370,"editorY":555,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":6,"hits":1,"editorId":"sts2-50040-6","editorX":370,"editorY":865,"children":[],"weight":1}],"editorId":"sts2-50040-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G45">
         <v>170041</v>
@@ -3410,8 +3568,10 @@
       <c r="I45" t="s">
         <v>30</v>
       </c>
-      <c r="J45" t="s">
-        <v>230</v>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"蜜糖硬化","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蜜糖硬化","amount":6,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"蜜糖硬化·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"蜜糖硬化·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"盛碗虫（蜜）·追击","amount":4,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -3430,8 +3590,10 @@
       <c r="E46">
         <v>220</v>
       </c>
-      <c r="F46" t="s">
-        <v>233</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"斩击","amount":19,"hits":1,"editorId":"sts2-50041-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"开膛","amount":9,"hits":2,"editorId":"sts2-50041-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"斩击二式","amount":12,"hits":1,"editorId":"sts2-50041-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"斩击二式·格挡","amount":12,"editorId":"sts2-50041-6","editorX":670,"editorY":865,"children":[],"weight":1}],"editorId":"sts2-50041-4","editorX":370,"editorY":555,"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"灵魂虹吸·易伤","status":200004,"stacks":1,"editorId":"sts2-50041-8","editorX":670,"editorY":1175,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEBUFF","moveName":"灵魂虹吸·脆弱","status":200005,"stacks":1,"editorId":"sts2-50041-9","editorX":670,"editorY":1330,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"BUFF","moveName":"灵魂虹吸·强化","status":200001,"stacks":2,"editorId":"sts2-50041-10","editorX":670,"editorY":1485,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50041-7","editorX":370,"editorY":1020,"weight":1}],"editorId":"sts2-50041-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G46">
         <v>170042</v>
@@ -3442,8 +3604,10 @@
       <c r="I46" t="s">
         <v>30</v>
       </c>
-      <c r="J46" t="s">
-        <v>235</v>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"虹吸盛宴","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":12,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"虹吸盛宴","amount":19,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"虹吸盛宴·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"虹吸盛宴·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"拉加维林族母·追击","amount":14,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"虹吸盛宴·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"虹吸盛宴·终局","amount":12,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"虹吸盛宴·终局·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"虹吸盛宴·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"拉加维林族母·追击","amount":9,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -3462,8 +3626,10 @@
       <c r="E47">
         <v>64</v>
       </c>
-      <c r="F47" t="s">
-        <v>238</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"喷油","amount":8,"hits":1,"editorId":"sts2-50042-3","editorX":670,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50042-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"喷油","amount":8,"hits":1,"editorId":"sts2-50042-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"猛击","amount":11,"hits":1,"editorId":"sts2-50042-6","editorX":670,"editorY":865,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"暴怒","amount":6,"hits":1,"editorId":"sts2-50042-8","editorX":970,"editorY":1175,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"暴怒·强化","status":200001,"stacks":1,"editorId":"sts2-50042-9","editorX":970,"editorY":1330,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50042-7","editorX":670,"editorY":1020,"weight":1}],"editorId":"sts2-50042-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50042-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G47">
         <v>170043</v>
@@ -3474,8 +3640,10 @@
       <c r="I47" t="s">
         <v>30</v>
       </c>
-      <c r="J47" t="s">
-        <v>240</v>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"淤泥凝结","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"淤泥凝结","amount":11,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"淤泥凝结·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"淤泥凝结·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"淤泥纺织者·追击","amount":8,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -3494,8 +3662,10 @@
       <c r="E48">
         <v>62</v>
       </c>
-      <c r="F48" t="s">
-        <v>243</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"BUFF","moveName":"吟唱·仪式","status":200001,"stacks":1,"editorId":"sts2-50043-3","editorX":670,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50043-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"暗影打击","amount":9,"hits":1,"editorId":"sts2-50043-4","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50043-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G48">
         <v>170044</v>
@@ -3506,8 +3676,10 @@
       <c r="I48" t="s">
         <v>30</v>
       </c>
-      <c r="J48" t="s">
-        <v>245</v>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200018,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"骨符共鸣","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"骨符共鸣","amount":9,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"骨符共鸣·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"骨符共鸣·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"钙化教徒·追击","amount":6,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_POWER_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}],"filter":{}}]}</t>
+        </is>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -3526,8 +3698,10 @@
       <c r="E49">
         <v>60</v>
       </c>
-      <c r="F49" t="s">
-        <v>248</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"缩小术·脆弱","status":200005,"stacks":1,"editorId":"sts2-50044-2","editorX":370,"editorY":245,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"猛咬","amount":7,"hits":1,"editorId":"sts2-50044-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"跺击","amount":13,"hits":1,"editorId":"sts2-50044-4","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50044-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G49">
         <v>170045</v>
@@ -3538,8 +3712,10 @@
       <c r="I49" t="s">
         <v>30</v>
       </c>
-      <c r="J49" t="s">
-        <v>250</v>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"缩小遁形","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200005,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"缩小遁形","amount":13,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"缩小遁形·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"缩小遁形·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"缩小甲虫·追击","amount":9,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -3558,8 +3734,10 @@
       <c r="E50">
         <v>64</v>
       </c>
-      <c r="F50" t="s">
-        <v>253</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"倾泻火力","amount":3,"hits":3,"editorId":"sts2-50045-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"倾泻火力","amount":3,"hits":3,"editorId":"sts2-50045-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"装填·强化","status":200001,"stacks":1,"editorId":"sts2-50045-4","editorX":370,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50045-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G50">
         <v>170046</v>
@@ -3570,8 +3748,10 @@
       <c r="I50" t="s">
         <v>30</v>
       </c>
-      <c r="J50" t="s">
-        <v>255</v>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"火力倾泻","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"火力倾泻","amount":3,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"火力倾泻·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"火力倾泻·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"炮塔操作员·追击","amount":3,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -3590,8 +3770,10 @@
       <c r="E51">
         <v>105</v>
       </c>
-      <c r="F51" t="s">
-        <v>258</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"扭动攻击","amount":5,"hits":2,"editorId":"sts2-50046-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"壮大","amount":6,"hits":1,"editorId":"sts2-50046-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"壮大·力量","status":200001,"stacks":1,"editorId":"sts2-50046-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50046-3","editorX":370,"editorY":400,"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"紧缚","amount":8,"hits":1,"editorId":"sts2-50046-7","editorX":670,"editorY":1020,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"紧缚·虚弱","status":200003,"stacks":1,"editorId":"sts2-50046-8","editorX":670,"editorY":1175,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50046-6","editorX":370,"editorY":865,"weight":1}],"editorId":"sts2-50046-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G51">
         <v>170047</v>
@@ -3602,8 +3784,10 @@
       <c r="I51" t="s">
         <v>53</v>
       </c>
-      <c r="J51" t="s">
-        <v>260</v>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"节壳翻涌","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"节壳翻涌","amount":5,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"节壳翻涌·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"节壳翻涌·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"千足虫·追击","amount":3,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -3622,8 +3806,10 @@
       <c r="E52">
         <v>66</v>
       </c>
-      <c r="F52" t="s">
-        <v>263</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"头槌","amount":12,"hits":1,"editorId":"sts2-50047-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"切割","amount":6,"hits":1,"editorId":"sts2-50047-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"切割·格挡","amount":5,"editorId":"sts2-50047-5","editorX":670,"editorY":710,"children":[],"weight":1}],"editorId":"sts2-50047-3","editorX":370,"editorY":400,"weight":1},{"type":"ACTION","action":"BUFF","moveName":"嘶鸣·强化","status":200001,"stacks":1,"editorId":"sts2-50047-6","editorX":370,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50047-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G52">
         <v>170048</v>
@@ -3634,8 +3820,10 @@
       <c r="I52" t="s">
         <v>30</v>
       </c>
-      <c r="J52" t="s">
-        <v>265</v>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200017,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"甲颚狂怒","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"甲颚狂怒","amount":12,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"甲颚狂怒·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"甲颚狂怒·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"啃咬虫·追击","amount":9,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -3654,8 +3842,10 @@
       <c r="E53">
         <v>66</v>
       </c>
-      <c r="F53" t="s">
-        <v>268</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"海潮踢","amount":11,"hits":1,"editorId":"sts2-50048-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"回旋踢","amount":2,"hits":3,"editorId":"sts2-50048-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"气泡嗝·格挡","amount":7,"editorId":"sts2-50048-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"气泡嗝·强化","status":200001,"stacks":1,"editorId":"sts2-50048-6","editorX":670,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50048-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50048-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G53">
         <v>170049</v>
@@ -3666,8 +3856,10 @@
       <c r="I53" t="s">
         <v>30</v>
       </c>
-      <c r="J53" t="s">
-        <v>270</v>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"潮汐回旋","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"潮汐回旋","amount":11,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"潮汐回旋·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"潮汐回旋·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"海朋克·追击","amount":8,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -3686,8 +3878,10 @@
       <c r="E54">
         <v>62</v>
       </c>
-      <c r="F54" t="s">
-        <v>273</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"头槌","amount":15,"hits":1,"editorId":"sts2-50049-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"WAIT","moveName":"眩晕","editorId":"sts2-50049-3","editorX":370,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50049-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G54">
         <v>170050</v>
@@ -3698,8 +3892,10 @@
       <c r="I54" t="s">
         <v>30</v>
       </c>
-      <c r="J54" t="s">
-        <v>275</v>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"岩壳碎裂","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"岩壳碎裂","amount":15,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"岩壳碎裂·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"岩壳碎裂·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"盛碗虫（岩）·追击","amount":11,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -3718,8 +3914,10 @@
       <c r="E55">
         <v>68</v>
       </c>
-      <c r="F55" t="s">
-        <v>278</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"脆弱孢子","amount":8,"hits":1,"editorId":"sts2-50050-3","editorX":670,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"脆弱孢子·削弱","status":200005,"stacks":2,"editorId":"sts2-50050-4","editorX":670,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50050-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"重击","amount":11,"hits":1,"editorId":"sts2-50050-5","editorX":370,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"易伤孢子·削弱","status":200004,"stacks":2,"editorId":"sts2-50050-6","editorX":370,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50050-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G55">
         <v>170051</v>
@@ -3730,8 +3928,10 @@
       <c r="I55" t="s">
         <v>30</v>
       </c>
-      <c r="J55" t="s">
-        <v>280</v>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"孢子成熟","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"孢子成熟","amount":11,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"孢子成熟·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"孢子成熟·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"飞菇·追击","amount":8,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -3750,8 +3950,10 @@
       <c r="E56">
         <v>230</v>
       </c>
-      <c r="F56" t="s">
-        <v>283</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"蓄势护体","amount":8,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"蓄势增压","status":200001,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"跺击","amount":15,"hits":1,"editorId":"sts2-50051-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"跺击·削弱","status":200003,"stacks":1,"editorId":"sts2-50051-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50051-3","editorX":370,"editorY":400,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"猛撞","amount":10,"hits":1,"editorId":"sts2-50051-6","editorX":370,"editorY":865,"children":[],"weight":1},{"type":"ACTION","action":"HEAL","moveName":"虹吸·治疗","amount":12,"editorId":"sts2-50051-7","editorX":370,"editorY":1020,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"高压水枪","amount":20,"hits":1,"editorId":"sts2-50051-8","editorX":370,"editorY":1175,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"增压","amount":13,"hits":1,"editorId":"sts2-50051-9","editorX":370,"editorY":1330,"children":[],"weight":1}],"editorId":"sts2-50051-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G56">
         <v>170052</v>
@@ -3762,8 +3964,10 @@
       <c r="I56" t="s">
         <v>30</v>
       </c>
-      <c r="J56" t="s">
-        <v>285</v>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"洪流增压","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":12,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"洪流增压","amount":20,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"洪流增压·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"洪流增压·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"瀑布巨人·追击","amount":15,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"洪流增压·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"洪流增压·终局","amount":12,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"洪流增压·终局·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"洪流增压·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"瀑布巨人·追击","amount":9,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -3782,8 +3986,10 @@
       <c r="E57">
         <v>72</v>
       </c>
-      <c r="F57" t="s">
-        <v>288</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"交出来","amount":7,"hits":2,"editorId":"sts2-50052-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"双重猛击","amount":6,"hits":2,"editorId":"sts2-50052-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"双重猛击·削弱","status":200003,"stacks":2,"editorId":"sts2-50052-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50052-3","editorX":370,"editorY":400,"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"嘿嘿","amount":8,"hits":1,"editorId":"sts2-50052-7","editorX":670,"editorY":1020,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"嘿嘿·强化","status":200001,"stacks":1,"editorId":"sts2-50052-8","editorX":670,"editorY":1175,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50052-6","editorX":370,"editorY":865,"weight":1}],"editorId":"sts2-50052-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G57">
         <v>170053</v>
@@ -3794,8 +4000,10 @@
       <c r="I57" t="s">
         <v>30</v>
       </c>
-      <c r="J57" t="s">
-        <v>290</v>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"佣兵死斗","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"佣兵死斗","amount":7,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"佣兵死斗·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"佣兵死斗·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"地精佣兵·追击","amount":5,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -3814,8 +4022,10 @@
       <c r="E58">
         <v>70</v>
       </c>
-      <c r="F58" t="s">
-        <v>293</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"BUFF","moveName":"吟唱·仪式","status":200001,"stacks":1,"editorId":"sts2-50053-3","editorX":670,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50053-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"暗影打击","amount":6,"hits":1,"editorId":"sts2-50053-4","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50053-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G58">
         <v>170054</v>
@@ -3826,8 +4036,10 @@
       <c r="I58" t="s">
         <v>30</v>
       </c>
-      <c r="J58" t="s">
-        <v>295</v>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200018,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"潮湿祈祷","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200005,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"潮湿祈祷","amount":6,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"潮湿祈祷·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"潮湿祈祷·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"潮湿教徒·追击","amount":4,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_POWER_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}],"filter":{}}]}</t>
+        </is>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -3846,8 +4058,10 @@
       <c r="E59">
         <v>72</v>
       </c>
-      <c r="F59" t="s">
-        <v>298</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"咬住","amount":12,"hits":1,"editorId":"sts2-50054-3","editorX":670,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50054-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"咬住","amount":12,"hits":1,"editorId":"sts2-50054-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":9,"hits":1,"editorId":"sts2-50054-7","editorX":970,"editorY":1020,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"冲撞·削弱","status":200005,"stacks":1,"editorId":"sts2-50054-8","editorX":970,"editorY":1175,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50054-6","editorX":670,"editorY":865,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"鞭击","amount":3,"hits":2,"editorId":"sts2-50054-9","editorX":670,"editorY":1330,"children":[],"weight":1}],"editorId":"sts2-50054-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50054-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G59">
         <v>170055</v>
@@ -3858,8 +4072,10 @@
       <c r="I59" t="s">
         <v>30</v>
       </c>
-      <c r="J59" t="s">
-        <v>300</v>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"化石开裂","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"化石开裂","amount":12,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"化石开裂·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"化石开裂·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"化石潜猎者·追击","amount":9,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -3878,8 +4094,10 @@
       <c r="E60">
         <v>70</v>
       </c>
-      <c r="F60" t="s">
-        <v>303</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"紧缚·虚弱","status":200003,"stacks":1,"editorId":"sts2-50055-2","editorX":370,"editorY":245,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"抽打","amount":7,"hits":1,"editorId":"sts2-50055-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"抽打·格挡","amount":5,"editorId":"sts2-50055-5","editorX":670,"editorY":710,"children":[],"weight":1}],"editorId":"sts2-50055-3","editorX":370,"editorY":400,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"鞭击","amount":12,"hits":1,"editorId":"sts2-50055-6","editorX":370,"editorY":865,"children":[],"weight":1}],"editorId":"sts2-50055-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G60">
         <v>170056</v>
@@ -3890,8 +4108,10 @@
       <c r="I60" t="s">
         <v>30</v>
       </c>
-      <c r="J60" t="s">
-        <v>305</v>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"绞杀收紧","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200020,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"绞杀收紧","amount":12,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"绞杀收紧·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"绞杀收紧·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"游蛇绞杀者·追击","amount":9,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -3910,8 +4130,10 @@
       <c r="E61">
         <v>74</v>
       </c>
-      <c r="F61" t="s">
-        <v>308</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"酸液黏浆","amount":4,"hits":1,"editorId":"sts2-50056-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"吸气·强化","status":200001,"stacks":1,"editorId":"sts2-50056-3","editorX":370,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50056-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G61">
         <v>170057</v>
@@ -3922,8 +4144,10 @@
       <c r="I61" t="s">
         <v>30</v>
       </c>
-      <c r="J61" t="s">
-        <v>310</v>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"鼓胀吐酸","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"鼓胀吐酸","amount":4,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"鼓胀吐酸·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"鼓胀吐酸·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"绒毛蠕虫·追击","amount":3,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -3942,8 +4166,10 @@
       <c r="E62">
         <v>76</v>
       </c>
-      <c r="F62" t="s">
-        <v>313</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"盾击","amount":6,"hits":1,"editorId":"sts2-50057-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"重击","amount":16,"hits":1,"editorId":"sts2-50057-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"重击·强化","status":200001,"stacks":1,"editorId":"sts2-50057-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50057-3","editorX":370,"editorY":400,"weight":1}],"editorId":"sts2-50057-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G62">
         <v>170058</v>
@@ -3954,8 +4180,10 @@
       <c r="I62" t="s">
         <v>30</v>
       </c>
-      <c r="J62" t="s">
-        <v>315</v>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"盾面反击","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"盾面反击","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"盾面反击·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"盾面反击·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"活体盾牌·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_SKILL_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":210002,"target":"SELF","params":{"amount":2,"scale":true},"children":[],"elseEffects":[]}],"filter":{}}]}</t>
+        </is>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -3974,8 +4202,10 @@
       <c r="E63">
         <v>180</v>
       </c>
-      <c r="F63" t="s">
-        <v>318</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"迅捷斩击","amount":6,"hits":1,"editorId":"sts2-50058-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"回旋斩","amount":3,"hits":2,"editorId":"sts2-50058-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"力量之舞","status":200001,"stacks":2,"editorId":"sts2-50058-4","editorX":370,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50058-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G63">
         <v>170059</v>
@@ -3986,8 +4216,10 @@
       <c r="I63" t="s">
         <v>30</v>
       </c>
-      <c r="J63" t="s">
-        <v>320</v>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"眷族觉醒","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"眷族觉醒","amount":6,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"眷族觉醒·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"眷族觉醒·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"眷族追随者·追击","amount":4,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"眷族觉醒·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"眷族觉醒·终局","amount":6,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"眷族觉醒·终局·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"眷族觉醒·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"眷族追随者·追击","amount":4,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -4006,8 +4238,10 @@
       <c r="E64">
         <v>78</v>
       </c>
-      <c r="F64" t="s">
-        <v>323</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"钳击","amount":8,"hits":2,"editorId":"sts2-50059-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"尖啸","status":200003,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50059-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G64">
         <v>170060</v>
@@ -4018,8 +4252,10 @@
       <c r="I64" t="s">
         <v>30</v>
       </c>
-      <c r="J64" t="s">
-        <v>325</v>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200017,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"巨口撕扯","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"巨口撕扯","amount":8,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"巨口撕扯·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"巨口撕扯·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"巨口兽·追击","amount":6,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -4038,8 +4274,10 @@
       <c r="E65">
         <v>74</v>
       </c>
-      <c r="F65" t="s">
-        <v>328</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"毒液","status":200006,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"啃咬","amount":13,"hits":1,"editorId":"sts2-50060-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"吸吮","amount":4,"hits":1,"editorId":"sts2-50060-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"吸吮·强化","status":200001,"stacks":1,"editorId":"sts2-50060-6","editorX":670,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50060-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50060-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G65">
         <v>170061</v>
@@ -4050,8 +4288,10 @@
       <c r="I65" t="s">
         <v>30</v>
       </c>
-      <c r="J65" t="s">
-        <v>330</v>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"螨毒扩散","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"螨毒扩散","amount":13,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"螨毒扩散·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"螨毒扩散·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"螨虫·追击","amount":9,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_DAMAGE_DEALT","listenSide":"ENEMY","limit":6,"filter":{"damageKind":"ATTACK"},"effects":[{"type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]}]}</t>
+        </is>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -4070,8 +4310,10 @@
       <c r="E66">
         <v>240</v>
       </c>
-      <c r="F66" t="s">
-        <v>333</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"践踏","amount":12,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"震地虚弱","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1}],"editorId":"sts2-50061-2","editorX":370,"editorY":245,"weight":1},{"type":"CONDITION","field":"SELF_HP_PERCENT","operator":"&lt;=","value":60,"children":[{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"巨兽咆哮·虚弱","status":200003,"stacks":1,"editorId":"sts2-50061-6","editorX":970,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"跺击","amount":15,"hits":1,"editorId":"sts2-50061-7","editorX":970,"editorY":1020,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"碾压","amount":17,"hits":1,"editorId":"sts2-50061-9","editorX":1270,"editorY":1330,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"碾压·强化","status":200001,"stacks":2,"editorId":"sts2-50061-10","editorX":1270,"editorY":1485,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50061-8","editorX":970,"editorY":1175,"weight":1}],"editorId":"sts2-50061-5","editorX":670,"editorY":710,"weight":1}],"editorId":"sts2-50061-4","editorX":370,"editorY":555,"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"犁地","amount":18,"hits":1,"editorId":"sts2-50061-12","editorX":670,"editorY":1795,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"犁地·强化","status":200001,"stacks":2,"editorId":"sts2-50061-13","editorX":670,"editorY":1950,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50061-11","editorX":370,"editorY":1640,"weight":1}],"editorId":"sts2-50061-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G66">
         <v>170062</v>
@@ -4082,8 +4324,10 @@
       <c r="I66" t="s">
         <v>30</v>
       </c>
-      <c r="J66" t="s">
-        <v>335</v>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200018,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"仪式狂热","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200005,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"仪式狂热","amount":18,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"仪式狂热·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"仪式狂热·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"仪式巨兽·追击","amount":13,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"仪式狂热·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"仪式狂热·终局","amount":12,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"仪式狂热·终局·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"仪式狂热·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"仪式巨兽·追击","amount":9,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -4102,8 +4346,10 @@
       <c r="E67">
         <v>115</v>
       </c>
-      <c r="F67" t="s">
-        <v>338</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"感染","status":200006,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"鞭击","amount":4,"hits":3,"editorId":"sts2-50062-3","editorX":370,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50062-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G67">
         <v>170063</v>
@@ -4114,8 +4360,10 @@
       <c r="I67" t="s">
         <v>53</v>
       </c>
-      <c r="J67" t="s">
-        <v>340</v>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"寄生蔓延","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"寄生蔓延","amount":4,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"寄生蔓延·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"寄生蔓延·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"蛙寄生虫·追击","amount":3,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_DAMAGE_DEALT","listenSide":"ENEMY","limit":6,"filter":{"damageKind":"ATTACK"},"effects":[{"type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]}]}</t>
+        </is>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -4134,8 +4382,10 @@
       <c r="E68">
         <v>80</v>
       </c>
-      <c r="F68" t="s">
-        <v>343</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"缠绕藤蔓","amount":8,"hits":1,"editorId":"sts2-50063-3","editorX":670,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"缠绕藤蔓·脆弱","status":200005,"stacks":1,"editorId":"sts2-50063-4","editorX":670,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50063-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"横扫","amount":6,"hits":2,"editorId":"sts2-50063-5","editorX":370,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"猛咬","amount":16,"hits":1,"editorId":"sts2-50063-6","editorX":370,"editorY":865,"children":[],"weight":1}],"editorId":"sts2-50063-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G68">
         <v>170064</v>
@@ -4146,8 +4396,10 @@
       <c r="I68" t="s">
         <v>30</v>
       </c>
-      <c r="J68" t="s">
-        <v>345</v>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"藤蔓收束","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"藤蔓收束","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"藤蔓收束·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"藤蔓收束·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"藤蔓蹒跚者·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -4166,8 +4418,10 @@
       <c r="E69">
         <v>78</v>
       </c>
-      <c r="F69" t="s">
-        <v>348</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"全速冲撞","amount":10,"hits":1,"editorId":"sts2-50064-3","editorX":670,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50064-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"全速冲撞","amount":10,"hits":1,"editorId":"sts2-50064-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"缠魂·削弱","status":200003,"stacks":2,"editorId":"sts2-50064-7","editorX":970,"editorY":1020,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEBUFF","moveName":"缠魂·削弱","status":200005,"stacks":2,"editorId":"sts2-50064-8","editorX":970,"editorY":1175,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEBUFF","moveName":"缠魂·削弱","status":200004,"stacks":2,"editorId":"sts2-50064-9","editorX":970,"editorY":1330,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50064-6","editorX":670,"editorY":865,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"横扫","amount":13,"hits":1,"editorId":"sts2-50064-10","editorX":670,"editorY":1485,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"跺击","amount":4,"hits":3,"editorId":"sts2-50064-11","editorX":670,"editorY":1640,"children":[],"weight":1}],"editorId":"sts2-50064-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50064-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G69">
         <v>170065</v>
@@ -4178,8 +4432,10 @@
       <c r="I69" t="s">
         <v>30</v>
       </c>
-      <c r="J69" t="s">
-        <v>350</v>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"亡魂缠绕","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"亡魂缠绕","amount":13,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"亡魂缠绕·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"亡魂缠绕·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"幽灵船·追击","amount":9,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -4198,8 +4454,10 @@
       <c r="E70">
         <v>82</v>
       </c>
-      <c r="F70" t="s">
-        <v>353</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"BUFF","moveName":"蓄能·强化","status":200001,"stacks":1,"editorId":"sts2-50065-2","editorX":370,"editorY":245,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"连发冲击","amount":7,"hits":1,"editorId":"sts2-50065-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"连发冲击·强化","status":200001,"stacks":1,"editorId":"sts2-50065-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50065-3","editorX":370,"editorY":400,"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"连发冲击","amount":7,"hits":1,"editorId":"sts2-50065-7","editorX":670,"editorY":1020,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"连发冲击·强化","status":200001,"stacks":1,"editorId":"sts2-50065-8","editorX":670,"editorY":1175,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50065-6","editorX":370,"editorY":865,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"喷射冲击","amount":5,"hits":2,"editorId":"sts2-50065-9","editorX":370,"editorY":1330,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"下潜·格挡","amount":8,"editorId":"sts2-50065-10","editorX":370,"editorY":1485,"children":[],"weight":1}],"editorId":"sts2-50065-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G70">
         <v>170066</v>
@@ -4210,8 +4468,10 @@
       <c r="I70" t="s">
         <v>30</v>
       </c>
-      <c r="J70" t="s">
-        <v>355</v>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":4,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"核心暴露","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"核心暴露","amount":5,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"核心暴露·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"核心暴露·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"立方构装体·追击","amount":3,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -4230,8 +4490,10 @@
       <c r="E71">
         <v>84</v>
       </c>
-      <c r="F71" t="s">
-        <v>358</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"爪击","amount":4,"hits":2,"editorId":"sts2-50066-3","editorX":670,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50066-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"爪击","amount":4,"hits":2,"editorId":"sts2-50066-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"咆哮·削弱","status":200004,"stacks":2,"editorId":"sts2-50066-6","editorX":670,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"撕扯","amount":14,"hits":1,"editorId":"sts2-50066-7","editorX":670,"editorY":1020,"children":[],"weight":1}],"editorId":"sts2-50066-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50066-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G71">
         <v>170067</v>
@@ -4242,8 +4504,10 @@
       <c r="I71" t="s">
         <v>30</v>
       </c>
-      <c r="J71" t="s">
-        <v>360</v>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200017,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"巨颚咬合","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"巨颚咬合","amount":14,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"巨颚咬合·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"巨颚咬合·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"巨颚兽·追击","amount":10,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -4262,8 +4526,10 @@
       <c r="E72">
         <v>80</v>
       </c>
-      <c r="F72" t="s">
-        <v>363</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":200014,"stacks":1,"duration":"COMBAT","children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"横扫","amount":8,"hits":1,"editorId":"sts2-50067-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"横扫·强化","status":200001,"stacks":1,"editorId":"sts2-50067-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50067-3","editorX":370,"editorY":400,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"头槌","amount":14,"hits":1,"editorId":"sts2-50067-6","editorX":370,"editorY":865,"children":[],"weight":1}],"editorId":"sts2-50067-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G72">
         <v>170068</v>
@@ -4274,8 +4540,10 @@
       <c r="I72" t="s">
         <v>30</v>
       </c>
-      <c r="J72" t="s">
-        <v>365</v>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"迷雾凝聚","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"迷雾凝聚","amount":14,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"迷雾凝聚·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"迷雾凝聚·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"雾魔·追击","amount":10,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -4294,8 +4562,10 @@
       <c r="E73">
         <v>125</v>
       </c>
-      <c r="F73" t="s">
-        <v>368</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"重击","amount":9,"hits":1,"editorId":"sts2-50068-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"疾速冲击","amount":16,"hits":1,"editorId":"sts2-50068-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"惯性·格挡","amount":10,"editorId":"sts2-50068-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"惯性·强化","status":200001,"stacks":1,"editorId":"sts2-50068-6","editorX":670,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50068-4","editorX":370,"editorY":555,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"巨蟹冲击","amount":6,"hits":2,"editorId":"sts2-50068-7","editorX":370,"editorY":1020,"children":[],"weight":1}],"editorId":"sts2-50068-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G73">
         <v>170069</v>
@@ -4306,8 +4576,10 @@
       <c r="I73" t="s">
         <v>53</v>
       </c>
-      <c r="J73" t="s">
-        <v>370</v>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"群落集中","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"群落集中","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"群落集中·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"群落集中·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"潜伏群落·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -4326,8 +4598,10 @@
       <c r="E74">
         <v>78</v>
       </c>
-      <c r="F74" t="s">
-        <v>373</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"偷窃","amount":17,"hits":1,"editorId":"sts2-50069-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":200014,"stacks":1,"duration":"COMBAT","children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"帽子戏法","amount":18,"hits":1,"editorId":"sts2-50069-4","editorX":370,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"夺取","amount":14,"hits":1,"editorId":"sts2-50069-5","editorX":370,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":200014,"stacks":1,"duration":"COMBAT","children":[],"weight":1}],"editorId":"sts2-50069-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G74">
         <v>170070</v>
@@ -4338,8 +4612,10 @@
       <c r="I74" t="s">
         <v>30</v>
       </c>
-      <c r="J74" t="s">
-        <v>375</v>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200015,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"折翼夺取","condition":"HITS_AT_LEAST","value":2,"effects":[{"type":210011,"target":"SELF","params":{"status":200015,"stacks":"ALL","amount":"ALL"},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200005,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"折翼夺取","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"折翼夺取·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"折翼夺取·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"窃贼跳虫·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -4358,8 +4634,10 @@
       <c r="E75">
         <v>82</v>
       </c>
-      <c r="F75" t="s">
-        <v>378</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"强化毒雾","amount":8,"hits":1,"editorId":"sts2-50070-3","editorX":670,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"强化毒雾·虚弱","status":200003,"stacks":1,"editorId":"sts2-50070-4","editorX":670,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50070-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"膨胀","status":200006,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"超级毒雾爆发","amount":8,"hits":1,"editorId":"sts2-50070-6","editorX":370,"editorY":865,"children":[],"weight":1}],"editorId":"sts2-50070-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G75">
         <v>170071</v>
@@ -4370,8 +4648,10 @@
       <c r="I75" t="s">
         <v>30</v>
       </c>
-      <c r="J75" t="s">
-        <v>380</v>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"毒雾实体","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"毒雾实体","amount":8,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"毒雾实体·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"毒雾实体·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"活体迷雾·追击","amount":6,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -4390,8 +4670,10 @@
       <c r="E76">
         <v>260</v>
       </c>
-      <c r="F76" t="s">
-        <v>383</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"液化地面","status":200020,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":8,"hits":2,"editorId":"sts2-50071-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"突进啃咬","amount":26,"hits":1,"editorId":"sts2-50071-4","editorX":370,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"垂涎·强化","status":200001,"stacks":2,"editorId":"sts2-50071-5","editorX":370,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":8,"hits":2,"editorId":"sts2-50071-6","editorX":370,"editorY":865,"children":[],"weight":1}],"editorId":"sts2-50071-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G76">
         <v>170072</v>
@@ -4402,8 +4684,10 @@
       <c r="I76" t="s">
         <v>30</v>
       </c>
-      <c r="J76" t="s">
-        <v>385</v>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200017,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"吞噬渴求","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200020,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"吞噬渴求","amount":24,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"吞噬渴求·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"吞噬渴求·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"贪得无厌者·追击","amount":18,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"吞噬渴求·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"吞噬渴求·终局","amount":12,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"吞噬渴求·终局·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"吞噬渴求·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"贪得无厌者·追击","amount":9,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -4422,8 +4706,10 @@
       <c r="E77">
         <v>125</v>
       </c>
-      <c r="F77" t="s">
-        <v>388</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"能量盾","amount":6,"hits":1,"editorId":"sts2-50072-3","editorX":670,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"能量盾·格挡","amount":5,"editorId":"sts2-50072-4","editorX":670,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50072-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"压制·脆弱","status":200005,"stacks":1,"editorId":"sts2-50072-5","editorX":370,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"长枪突刺","amount":10,"hits":1,"editorId":"sts2-50072-6","editorX":370,"editorY":865,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"准备·格挡","amount":5,"editorId":"sts2-50072-7","editorX":370,"editorY":1020,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"魔法炸弹","amount":22,"hits":1,"editorId":"sts2-50072-8","editorX":370,"editorY":1175,"children":[],"weight":1}],"editorId":"sts2-50072-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G77">
         <v>170073</v>
@@ -4434,8 +4720,10 @@
       <c r="I77" t="s">
         <v>53</v>
       </c>
-      <c r="J77" t="s">
-        <v>390</v>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"魔盾超载","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"魔盾超载","amount":20,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"魔盾超载·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"魔盾超载·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"魔法骑士·追击","amount":15,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_SKILL_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":210002,"target":"SELF","params":{"amount":2,"scale":true},"children":[],"elseEffects":[]}],"filter":{}}]}</t>
+        </is>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -4454,8 +4742,10 @@
       <c r="E78">
         <v>84</v>
       </c>
-      <c r="F78" t="s">
-        <v>393</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"WAIT","moveName":"沉睡","editorId":"sts2-50073-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"滚动突击","amount":16,"hits":1,"editorId":"sts2-50073-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"滚动突击·强化","status":200001,"stacks":1,"editorId":"sts2-50073-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50073-3","editorX":370,"editorY":400,"weight":1}],"editorId":"sts2-50073-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G78">
         <v>170074</v>
@@ -4466,8 +4756,10 @@
       <c r="I78" t="s">
         <v>30</v>
       </c>
-      <c r="J78" t="s">
-        <v>395</v>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"甲虫惊醒","condition":"TURN_AT_LEAST","value":3,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210011,"target":"SELF","params":{"status":200013,"stacks":"ALL","amount":"ALL"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"甲虫惊醒","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"甲虫惊醒·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"甲虫惊醒·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"沉睡甲虫·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -4486,8 +4778,10 @@
       <c r="E79">
         <v>88</v>
       </c>
-      <c r="F79" t="s">
-        <v>398</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"啃咬","amount":13,"hits":1,"editorId":"sts2-50074-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"潜地·格挡","amount":8,"editorId":"sts2-50074-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"地底突袭","amount":18,"hits":1,"editorId":"sts2-50074-4","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50074-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G79">
         <v>170075</v>
@@ -4498,8 +4792,10 @@
       <c r="I79" t="s">
         <v>30</v>
       </c>
-      <c r="J79" t="s">
-        <v>400</v>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"破土强攻","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"破土强攻","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"破土强攻·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"破土强攻·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"掘地兽·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -4518,8 +4814,10 @@
       <c r="E80">
         <v>130</v>
       </c>
-      <c r="F80" t="s">
-        <v>403</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"DEBUFF","moveName":"诅咒·虚弱","status":200003,"stacks":1,"editorId":"sts2-50075-3","editorX":670,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50075-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"DEBUFF","moveName":"诅咒·虚弱","status":200003,"stacks":1,"editorId":"sts2-50075-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"灵魂斩击","amount":15,"hits":1,"editorId":"sts2-50075-6","editorX":670,"editorY":865,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"灵魂烈焰","amount":3,"hits":3,"editorId":"sts2-50075-7","editorX":670,"editorY":1020,"children":[],"weight":1}],"editorId":"sts2-50075-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50075-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G80">
         <v>170076</v>
@@ -4530,8 +4828,10 @@
       <c r="I80" t="s">
         <v>53</v>
       </c>
-      <c r="J80" t="s">
-        <v>405</v>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"幽魂显形","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200019,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"幽魂显形","amount":15,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"幽魂显形·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"幽魂显形·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"幽魂骑士·追击","amount":11,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -4550,8 +4850,10 @@
       <c r="E81">
         <v>86</v>
       </c>
-      <c r="F81" t="s">
-        <v>408</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"虚弱迷雾·易伤","status":200004,"stacks":1,"editorId":"sts2-50076-3","editorX":670,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"BUFF","moveName":"虚弱迷雾·强化","status":200001,"stacks":1,"editorId":"sts2-50076-4","editorX":670,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50076-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"眼部激光","amount":4,"hits":2,"editorId":"sts2-50076-5","editorX":370,"editorY":710,"children":[],"weight":1}],"editorId":"sts2-50076-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G81">
         <v>170077</v>
@@ -4562,8 +4864,10 @@
       <c r="I81" t="s">
         <v>30</v>
       </c>
-      <c r="J81" t="s">
-        <v>410</v>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"迷失狂乱","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"迷失狂乱","amount":4,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"迷失狂乱·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"迷失狂乱·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"迷失者·追击","amount":3,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -4582,8 +4886,10 @@
       <c r="E82">
         <v>135</v>
       </c>
-      <c r="F82" t="s">
-        <v>413</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"猛撞","amount":15,"hits":1,"editorId":"sts2-50077-3","editorX":670,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50077-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"BUFF","moveName":"战歌·强化","status":200001,"stacks":1,"editorId":"sts2-50077-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"链锤乱击","amount":9,"hits":2,"editorId":"sts2-50077-6","editorX":670,"editorY":865,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"猛撞","amount":15,"hits":1,"editorId":"sts2-50077-7","editorX":670,"editorY":1020,"children":[],"weight":1}],"editorId":"sts2-50077-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50077-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G82">
         <v>170078</v>
@@ -4594,8 +4900,10 @@
       <c r="I82" t="s">
         <v>53</v>
       </c>
-      <c r="J82" t="s">
-        <v>415</v>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"链锤旋舞","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"链锤旋舞","amount":9,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"链锤旋舞·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"链锤旋舞·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"链锤骑士·追击","amount":6,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -4614,8 +4922,10 @@
       <c r="E83">
         <v>88</v>
       </c>
-      <c r="F83" t="s">
-        <v>418</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"瘴气·脆弱","status":200005,"stacks":1,"editorId":"sts2-50078-3","editorX":670,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEFEND","moveName":"瘴气·格挡","amount":8,"editorId":"sts2-50078-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"瘴气·强化","status":200002,"stacks":2,"editorId":"sts2-50078-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50078-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"恐惧","amount":15,"hits":1,"editorId":"sts2-50078-6","editorX":370,"editorY":865,"children":[],"weight":1}],"editorId":"sts2-50078-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G83">
         <v>170079</v>
@@ -4626,8 +4936,10 @@
       <c r="I83" t="s">
         <v>30</v>
       </c>
-      <c r="J83" t="s">
-        <v>420</v>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"记忆侵蚀","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"记忆侵蚀","amount":15,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"记忆侵蚀·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"记忆侵蚀·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"遗忘者·追击","amount":11,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -4646,8 +4958,10 @@
       <c r="E84">
         <v>90</v>
       </c>
-      <c r="F84" t="s">
-        <v>423</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"BUFF","moveName":"凸出尖刺·强化","status":200009,"stacks":1,"editorId":"sts2-50079-2","editorX":370,"editorY":245,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"尖刺爆发","amount":18,"hits":1,"editorId":"sts2-50079-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"舌鞭","amount":17,"hits":1,"editorId":"sts2-50079-4","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50079-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G84">
         <v>170080</v>
@@ -4658,8 +4972,10 @@
       <c r="I84" t="s">
         <v>30</v>
       </c>
-      <c r="J84" t="s">
-        <v>425</v>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200009,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"尖刺绽放","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"尖刺绽放","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"尖刺绽放·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"尖刺绽放·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"棘刺蟾蜍·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -4678,8 +4994,10 @@
       <c r="E85">
         <v>94</v>
       </c>
-      <c r="F85" t="s">
-        <v>428</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"DEBUFF","moveName":"软化黏液·易伤","status":200004,"stacks":1,"editorId":"sts2-50080-3","editorX":670,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50080-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"DEBUFF","moveName":"软化黏液·易伤","status":200004,"stacks":1,"editorId":"sts2-50080-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"啃咬","amount":17,"hits":1,"editorId":"sts2-50080-6","editorX":670,"editorY":865,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"穿刺","amount":6,"hits":3,"editorId":"sts2-50080-7","editorX":670,"editorY":1020,"children":[],"weight":1}],"editorId":"sts2-50080-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50080-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G85">
         <v>170081</v>
@@ -4690,8 +5008,10 @@
       <c r="I85" t="s">
         <v>30</v>
       </c>
-      <c r="J85" t="s">
-        <v>430</v>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200017,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"猎杀追击","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"猎杀追击","amount":5,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"猎杀追击·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"猎杀追击·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"猎杀者·追击","amount":3,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -4710,8 +5030,10 @@
       <c r="E86">
         <v>270</v>
       </c>
-      <c r="F86" t="s">
-        <v>433</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"知识诅咒·虚弱","status":200003,"stacks":2,"editorId":"sts2-50081-3","editorX":670,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEBUFF","moveName":"知识诅咒·脆弱","status":200005,"stacks":2,"editorId":"sts2-50081-4","editorX":670,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50081-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"拍击","amount":17,"hits":1,"editorId":"sts2-50081-5","editorX":370,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"知识洪流","amount":8,"hits":3,"editorId":"sts2-50081-6","editorX":370,"editorY":865,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"沉思","amount":11,"hits":1,"editorId":"sts2-50081-8","editorX":670,"editorY":1175,"children":[],"weight":1},{"type":"ACTION","action":"HEAL","moveName":"沉思·治疗","amount":12,"editorId":"sts2-50081-9","editorX":670,"editorY":1330,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"沉思·强化","status":200001,"stacks":2,"editorId":"sts2-50081-10","editorX":670,"editorY":1485,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50081-7","editorX":370,"editorY":1020,"weight":1}],"editorId":"sts2-50081-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G86">
         <v>170082</v>
@@ -4722,8 +5044,10 @@
       <c r="I86" t="s">
         <v>30</v>
       </c>
-      <c r="J86" t="s">
-        <v>435</v>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"禁忌知识","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"禁忌知识","amount":8,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"禁忌知识·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"禁忌知识·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"知识恶魔·追击","amount":6,"hits":3,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"禁忌知识·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"禁忌知识·终局","amount":8,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"禁忌知识·终局·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"禁忌知识·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"知识恶魔·追击","amount":6,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_POWER_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}],"filter":{}}]}</t>
+        </is>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -4742,8 +5066,10 @@
       <c r="E87">
         <v>90</v>
       </c>
-      <c r="F87" t="s">
-        <v>438</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":200014,"stacks":1,"duration":"COMBAT","children":[],"weight":1}],"editorId":"sts2-50082-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"BUFF","moveName":"闪身戒备","status":200014,"stacks":1,"duration":"COMBAT","children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"穿透凝视","amount":10,"hits":1,"editorId":"sts2-50082-6","editorX":670,"editorY":865,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"哀嚎","status":200003,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"硬化打击","amount":6,"hits":1,"editorId":"sts2-50082-9","editorX":970,"editorY":1330,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"硬化打击·格挡","amount":6,"editorId":"sts2-50082-10","editorX":970,"editorY":1485,"children":[],"weight":1}],"editorId":"sts2-50082-8","editorX":670,"editorY":1175,"weight":1}],"editorId":"sts2-50082-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50082-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G87">
         <v>170083</v>
@@ -4754,8 +5080,10 @@
       <c r="I87" t="s">
         <v>30</v>
       </c>
-      <c r="J87" t="s">
-        <v>440</v>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"晦影具象","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200005,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"晦影具象","amount":10,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"晦影具象·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"晦影具象·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"晦影者·追击","amount":7,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -4774,8 +5102,10 @@
       <c r="E88">
         <v>92</v>
       </c>
-      <c r="F88" t="s">
-        <v>443</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"集中自身力量","status":200001,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEFEND","moveName":"强化自身护甲","amount":6,"children":[],"weight":1}],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"重击","amount":16,"hits":1,"editorId":"sts2-50083-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"软化打击","amount":7,"hits":1,"editorId":"sts2-50083-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"软化打击·削弱","status":200004,"stacks":2,"editorId":"sts2-50083-6","editorX":670,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50083-4","editorX":370,"editorY":555,"weight":1},{"type":"ACTION","action":"BUFF","moveName":"营养糊·强化","status":200001,"stacks":1,"editorId":"sts2-50083-7","editorX":370,"editorY":1020,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50083-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G88">
         <v>170084</v>
@@ -4786,8 +5116,10 @@
       <c r="I88" t="s">
         <v>30</v>
       </c>
-      <c r="J88" t="s">
-        <v>445</v>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200015,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"虫卵吸收","condition":"HITS_AT_LEAST","value":3,"effects":[{"type":210011,"target":"SELF","params":{"status":200015,"stacks":"ALL","amount":"ALL"},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"虫卵吸收","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"虫卵吸收·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"虫卵吸收·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"产卵飞虫·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -4806,8 +5138,10 @@
       <c r="E89">
         <v>96</v>
       </c>
-      <c r="F89" t="s">
-        <v>448</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蛛网炮","amount":9,"hits":1,"editorId":"sts2-50084-3","editorX":670,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"蛛网炮·削弱","status":200005,"stacks":2,"editorId":"sts2-50084-4","editorX":670,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50084-2","editorX":370,"editorY":245,"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"蜷缩成长·格挡","amount":8,"editorId":"sts2-50084-6","editorX":670,"editorY":865,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"蜷缩成长·强化","status":200001,"stacks":1,"editorId":"sts2-50084-7","editorX":670,"editorY":1020,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50084-5","editorX":370,"editorY":710,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"扑击","amount":14,"hits":1,"editorId":"sts2-50084-8","editorX":370,"editorY":1175,"children":[],"weight":1}],"editorId":"sts2-50084-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G89">
         <v>170085</v>
@@ -4818,8 +5152,10 @@
       <c r="I89" t="s">
         <v>30</v>
       </c>
-      <c r="J89" t="s">
-        <v>450</v>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"始祖蜕壳","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"始祖蜕壳","amount":14,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"始祖蜕壳·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"始祖蜕壳·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"虱虫始祖·追击","amount":10,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_DAMAGE_DEALT","listenSide":"ENEMY","limit":6,"filter":{"damageKind":"ATTACK"},"effects":[{"type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]}]}</t>
+        </is>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -4838,8 +5174,10 @@
       <c r="E90">
         <v>140</v>
       </c>
-      <c r="F90" t="s">
-        <v>453</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"撞击","amount":17,"hits":1,"editorId":"sts2-50085-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"乱击","amount":3,"hits":3,"editorId":"sts2-50085-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"恐吓·削弱","status":200004,"stacks":2,"editorId":"sts2-50085-4","editorX":370,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50085-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G90">
         <v>170086</v>
@@ -4850,8 +5188,10 @@
       <c r="I90" t="s">
         <v>53</v>
       </c>
-      <c r="J90" t="s">
-        <v>455</v>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200014,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"恐惧电流","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200019,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"恐惧电流","amount":17,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"恐惧电流·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"恐惧电流·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"恐惧鳗鱼·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -4870,8 +5210,10 @@
       <c r="E91">
         <v>145</v>
       </c>
-      <c r="F91" t="s">
-        <v>458</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"蜂群","amount":3,"hits":3,"editorId":"sts2-50086-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"长枪突刺","amount":18,"hits":1,"editorId":"sts2-50086-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"集中自身力量","status":200001,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEFEND","moveName":"强化自身护甲","amount":6,"children":[],"weight":1}],"weight":1}],"editorId":"sts2-50086-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G91">
         <v>170087</v>
@@ -4882,8 +5224,10 @@
       <c r="I91" t="s">
         <v>53</v>
       </c>
-      <c r="J91" t="s">
-        <v>460</v>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"信息素狂热","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"信息素狂热","amount":18,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"信息素狂热·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"信息素狂热·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"御虫师·追击","amount":13,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -4902,8 +5246,10 @@
       <c r="E92">
         <v>100</v>
       </c>
-      <c r="F92" t="s">
-        <v>463</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"电击掌","amount":13,"hits":1,"editorId":"sts2-50087-3","editorX":670,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"电击掌·削弱","status":200005,"stacks":2,"editorId":"sts2-50087-4","editorX":670,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50087-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"雷霆打击","amount":6,"hits":3,"editorId":"sts2-50087-5","editorX":370,"editorY":710,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"电流爆发","amount":16,"hits":1,"editorId":"sts2-50087-7","editorX":670,"editorY":1020,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"电流爆发·强化","status":200001,"stacks":1,"editorId":"sts2-50087-8","editorX":670,"editorY":1175,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50087-6","editorX":370,"editorY":865,"weight":1}],"editorId":"sts2-50087-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G92">
         <v>170088</v>
@@ -4914,8 +5260,10 @@
       <c r="I92" t="s">
         <v>30</v>
       </c>
-      <c r="J92" t="s">
-        <v>465</v>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"电流回路","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"电流回路","amount":5,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"电流回路·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"电流回路·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"球头怪·追击","amount":3,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -4934,8 +5282,10 @@
       <c r="E93">
         <v>100</v>
       </c>
-      <c r="F93" t="s">
-        <v>468</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>{"type":"RANDOM","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"BUFF","moveName":"集中自身力量","status":200001,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEFEND","moveName":"强化自身护甲","amount":6,"children":[],"weight":1}],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"制造打击","amount":18,"hits":1,"editorId":"sts2-50088-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"瓦解","amount":11,"hits":1,"editorId":"sts2-50088-4","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50088-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G93">
         <v>170089</v>
@@ -4946,8 +5296,10 @@
       <c r="I93" t="s">
         <v>30</v>
       </c>
-      <c r="J93" t="s">
-        <v>470</v>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"工具改装","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"工具改装","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"工具改装·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"工具改装·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"制造者·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -4966,8 +5318,10 @@
       <c r="E94">
         <v>102</v>
       </c>
-      <c r="F94" t="s">
-        <v>473</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"BUFF","moveName":"禁忌咒语·仪式","status":200001,"stacks":1,"editorId":"sts2-50089-3","editorX":670,"editorY":400,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50089-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"狂野打击","amount":12,"hits":1,"editorId":"sts2-50089-4","editorX":370,"editorY":555,"children":[],"weight":1}],"editorId":"sts2-50089-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G94">
         <v>170090</v>
@@ -4978,8 +5332,10 @@
       <c r="I94" t="s">
         <v>30</v>
       </c>
-      <c r="J94" t="s">
-        <v>475</v>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200018,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"禁忌雕像","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"禁忌雕像","amount":12,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"禁忌雕像·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"禁忌雕像·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"虔诚雕塑师·追击","amount":9,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_POWER_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}],"filter":{}}]}</t>
+        </is>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -4998,8 +5354,10 @@
       <c r="E95">
         <v>104</v>
       </c>
-      <c r="F95" t="s">
-        <v>478</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"横扫","amount":13,"hits":1,"editorId":"sts2-50090-3","editorX":670,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50090-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"横扫","amount":13,"hits":1,"editorId":"sts2-50090-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"喷射硬币","amount":2,"hits":3,"editorId":"sts2-50090-6","editorX":670,"editorY":865,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"投掷遗物","amount":9,"hits":1,"editorId":"sts2-50090-8","editorX":970,"editorY":1175,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"投掷遗物·削弱","status":200005,"stacks":1,"editorId":"sts2-50090-9","editorX":970,"editorY":1330,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50090-7","editorX":670,"editorY":1020,"weight":1},{"type":"ACTION","action":"BUFF","moveName":"狂怒·强化","status":200001,"stacks":1,"editorId":"sts2-50090-10","editorX":670,"editorY":1485,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50090-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50090-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G95">
         <v>170091</v>
@@ -5010,8 +5368,10 @@
       <c r="I95" t="s">
         <v>30</v>
       </c>
-      <c r="J95" t="s">
-        <v>480</v>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200017,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"贪欲揭面","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200005,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"贪欲揭面","amount":13,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"贪欲揭面·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"贪欲揭面·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"伪装商人·追击","amount":9,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -5030,8 +5390,10 @@
       <c r="E96">
         <v>280</v>
       </c>
-      <c r="F96" t="s">
-        <v>483</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"傀儡丝线","status":200020,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"你属于我·削弱","status":200005,"stacks":3,"editorId":"sts2-50091-4","editorX":670,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEBUFF","moveName":"你属于我·削弱","status":200003,"stacks":3,"editorId":"sts2-50091-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEBUFF","moveName":"你属于我·削弱","status":200004,"stacks":3,"editorId":"sts2-50091-6","editorX":670,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50091-3","editorX":370,"editorY":400,"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"为我燃烧·格挡","amount":16,"editorId":"sts2-50091-7","editorX":370,"editorY":1020,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"斩下你的头","amount":3,"hits":4,"editorId":"sts2-50091-8","editorX":370,"editorY":1175,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"处决","amount":15,"hits":1,"editorId":"sts2-50091-9","editorX":370,"editorY":1330,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"狂怒·强化","status":200001,"stacks":2,"editorId":"sts2-50091-10","editorX":370,"editorY":1485,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50091-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G96">
         <v>170092</v>
@@ -5042,8 +5404,10 @@
       <c r="I96" t="s">
         <v>30</v>
       </c>
-      <c r="J96" t="s">
-        <v>485</v>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"女王亲征","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"女王亲征","amount":15,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"女王亲征·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"女王亲征·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"女王·追击","amount":11,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"女王亲征·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"女王亲征·终局","amount":12,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"女王亲征·终局·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"女王亲征·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"女王·追击","amount":9,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -5062,8 +5426,10 @@
       <c r="E97">
         <v>250</v>
       </c>
-      <c r="F97" t="s">
-        <v>488</v>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"锁定准星","amount":3,"hits":1,"editorId":"sts2-50092-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"精准光束","amount":18,"hits":1,"editorId":"sts2-50092-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"蓄能·强化","status":200001,"stacks":2,"editorId":"sts2-50092-4","editorX":370,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"激光","amount":26,"hits":1,"editorId":"sts2-50092-5","editorX":370,"editorY":710,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"蓄势护体","amount":8,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"蓄势增压","status":200001,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1}],"editorId":"sts2-50092-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G97">
         <v>170093</v>
@@ -5074,8 +5440,10 @@
       <c r="I97" t="s">
         <v>30</v>
       </c>
-      <c r="J97" t="s">
-        <v>490</v>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"火箭超载","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":12,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"火箭超载","amount":24,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"火箭超载·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"火箭超载·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"火箭·追击","amount":18,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"火箭超载·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"火箭超载·终局","amount":12,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"火箭超载·终局·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"火箭超载·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"火箭·追击","amount":9,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -5094,8 +5462,10 @@
       <c r="E98">
         <v>230</v>
       </c>
-      <c r="F98" t="s">
-        <v>493</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"脆弱法球","amount":8,"hits":1,"editorId":"sts2-50093-3","editorX":670,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"脆弱法球·削弱","status":200005,"stacks":1,"editorId":"sts2-50093-4","editorX":670,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50093-2","editorX":370,"editorY":245,"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"虚弱法球","amount":8,"hits":1,"editorId":"sts2-50093-6","editorX":670,"editorY":865,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"虚弱法球·削弱","status":200003,"stacks":1,"editorId":"sts2-50093-7","editorX":670,"editorY":1020,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50093-5","editorX":370,"editorY":710,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"光束","amount":3,"hits":3,"editorId":"sts2-50093-8","editorX":370,"editorY":1175,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"仪式·强化","status":200001,"stacks":2,"editorId":"sts2-50093-9","editorX":370,"editorY":1330,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50093-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G98">
         <v>170094</v>
@@ -5106,8 +5476,10 @@
       <c r="I98" t="s">
         <v>30</v>
       </c>
-      <c r="J98" t="s">
-        <v>495</v>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200018,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"祭司法阵","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"祭司法阵","amount":3,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"祭司法阵·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"祭司法阵·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"眷族祭司·追击","amount":3,"hits":3,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"祭司法阵·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"祭司法阵·终局","amount":3,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"祭司法阵·终局·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"祭司法阵·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"眷族祭司·追击","amount":3,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_POWER_PLAYED","listenSide":"PLAYER","limit":6,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}],"filter":{}}]}</t>
+        </is>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -5126,8 +5498,10 @@
       <c r="E99">
         <v>108</v>
       </c>
-      <c r="F99" t="s">
-        <v>498</v>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"舌鞭","amount":13,"hits":1,"editorId":"sts2-50094-3","editorX":670,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"舌鞭·削弱","status":200005,"stacks":2,"editorId":"sts2-50094-4","editorX":670,"editorY":555,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50094-2","editorX":370,"editorY":245,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"讨伐邪恶","amount":18,"hits":1,"editorId":"sts2-50094-5","editorX":370,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"为了女王·强化","status":200001,"stacks":1,"editorId":"sts2-50094-6","editorX":370,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"甲虫冲锋","amount":18,"hits":1,"editorId":"sts2-50094-7","editorX":370,"editorY":1020,"children":[],"weight":1}],"editorId":"sts2-50094-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G99">
         <v>170095</v>
@@ -5138,8 +5512,10 @@
       <c r="I99" t="s">
         <v>30</v>
       </c>
-      <c r="J99" t="s">
-        <v>500</v>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"骑士誓言","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"骑士誓言","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"骑士誓言·压制","status":200005,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"骑士誓言·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"青蛙骑士·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -5158,8 +5534,10 @@
       <c r="E100">
         <v>260</v>
       </c>
-      <c r="F100" t="s">
-        <v>503</v>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":18,"hits":1,"editorId":"sts2-50095-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"冲撞","amount":18,"hits":1,"editorId":"sts2-50095-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"灵魂光束","amount":8,"hits":3,"editorId":"sts2-50095-4","editorX":370,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"虚弱冲撞","amount":14,"hits":1,"editorId":"sts2-50095-5","editorX":370,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"虚弱冲撞","amount":14,"hits":1,"editorId":"sts2-50095-6","editorX":370,"editorY":865,"children":[],"weight":1}],"editorId":"sts2-50095-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G100">
         <v>170096</v>
@@ -5170,8 +5548,10 @@
       <c r="I100" t="s">
         <v>30</v>
       </c>
-      <c r="J100" t="s">
-        <v>505</v>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200013,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"融合燃烧","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":12,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"融合燃烧","amount":8,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"融合燃烧·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"融合燃烧·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"火炬头融合体·追击","amount":6,"hits":3,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"融合燃烧·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"融合燃烧·终局","amount":8,"hits":3,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"融合燃烧·终局·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"融合燃烧·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"火炬头融合体·追击","amount":6,"hits":3,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -5190,8 +5570,10 @@
       <c r="E101">
         <v>155</v>
       </c>
-      <c r="F101" t="s">
-        <v>508</v>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"刺拳","amount":22,"hits":1,"editorId":"sts2-50096-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"辐射","amount":16,"hits":1,"editorId":"sts2-50096-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"辐射·格挡","amount":12,"editorId":"sts2-50096-5","editorX":670,"editorY":710,"children":[],"weight":1}],"editorId":"sts2-50096-3","editorX":370,"editorY":400,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"旋风连击","amount":7,"hits":3,"editorId":"sts2-50096-6","editorX":370,"editorY":865,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"脉动·格挡","amount":12,"editorId":"sts2-50096-8","editorX":670,"editorY":1175,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"脉动·强化","status":200001,"stacks":1,"editorId":"sts2-50096-9","editorX":670,"editorY":1330,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50096-7","editorX":370,"editorY":1020,"weight":1}],"editorId":"sts2-50096-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G101">
         <v>170097</v>
@@ -5202,8 +5584,10 @@
       <c r="I101" t="s">
         <v>53</v>
       </c>
-      <c r="J101" t="s">
-        <v>510</v>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"棱晶裂解","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"棱晶裂解","amount":20,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"棱晶裂解·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"棱晶裂解·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"寄生棱晶·追击","amount":15,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[{"event":"ON_DAMAGE_DEALT","listenSide":"ENEMY","limit":6,"filter":{"damageKind":"ATTACK"},"effects":[{"type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]}]}</t>
+        </is>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -5222,8 +5606,10 @@
       <c r="E102">
         <v>110</v>
       </c>
-      <c r="F102" t="s">
-        <v>513</v>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"裁判审视","amount":16,"hits":1,"editorId":"sts2-50097-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"连环啄击","amount":4,"hits":3,"editorId":"sts2-50097-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"审判之翼","status":200003,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"判决","amount":18,"hits":1,"editorId":"sts2-50097-6","editorX":670,"editorY":865,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"判决·削弱","status":200004,"stacks":2,"editorId":"sts2-50097-7","editorX":670,"editorY":1020,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50097-5","editorX":370,"editorY":710,"weight":1}],"editorId":"sts2-50097-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G102">
         <v>170098</v>
@@ -5234,8 +5620,10 @@
       <c r="I102" t="s">
         <v>30</v>
       </c>
-      <c r="J102" t="s">
-        <v>515</v>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200015,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"落地审判","condition":"HITS_AT_LEAST","value":3,"effects":[{"type":210011,"target":"SELF","params":{"status":200015,"stacks":"ALL","amount":"ALL"},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"落地审判","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"落地审判·压制","status":200004,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"落地审判·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"猫头鹰裁判官·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -5254,8 +5642,10 @@
       <c r="E103">
         <v>155</v>
       </c>
-      <c r="F103" t="s">
-        <v>518</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>{"type":"SELECTOR","children":[{"type":"CONDITION","field":"TURN","operator":"==","value":1,"children":[{"type":"ACTION","action":"ATTACK","moveName":"灵魂灼烧","amount":22,"hits":1,"editorId":"sts2-50098-3","editorX":670,"editorY":400,"children":[],"weight":1}],"editorId":"sts2-50098-2","editorX":370,"editorY":245,"weight":1},{"type":"RANDOM","children":[{"type":"ACTION","action":"ATTACK","moveName":"灵魂灼烧","amount":22,"hits":1,"editorId":"sts2-50098-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"漩涡","amount":6,"hits":3,"editorId":"sts2-50098-6","editorX":670,"editorY":865,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"汲取生命","amount":18,"hits":1,"editorId":"sts2-50098-8","editorX":970,"editorY":1175,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"汲取生命·削弱","status":200004,"stacks":2,"editorId":"sts2-50098-9","editorX":970,"editorY":1330,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"DEBUFF","moveName":"汲取生命·削弱","status":200003,"stacks":2,"editorId":"sts2-50098-10","editorX":970,"editorY":1485,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50098-7","editorX":670,"editorY":1020,"weight":1}],"editorId":"sts2-50098-4","editorX":370,"editorY":555,"weight":1}],"editorId":"sts2-50098-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G103">
         <v>170099</v>
@@ -5266,8 +5656,10 @@
       <c r="I103" t="s">
         <v>53</v>
       </c>
-      <c r="J103" t="s">
-        <v>520</v>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200010,"stacks":3,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"魂核暴露","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210003,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"魂核暴露","amount":20,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"魂核暴露·压制","status":200003,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"魂核暴露·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"灵魂枢纽·追击","amount":15,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -5286,8 +5678,10 @@
       <c r="E104">
         <v>115</v>
       </c>
-      <c r="F104" t="s">
-        <v>523</v>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"喷吐脓液","status":200006,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"ATTACK","moveName":"狂怒连打","amount":4,"hits":3,"editorId":"sts2-50099-3","editorX":370,"editorY":400,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEBUFF","moveName":"吸血拥抱·削弱","status":200003,"stacks":2,"editorId":"sts2-50099-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"},{"type":"ACTION","action":"BUFF","moveName":"吸血拥抱·强化","status":200001,"stacks":1,"editorId":"sts2-50099-6","editorX":670,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50099-4","editorX":370,"editorY":555,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"窒息","amount":18,"hits":1,"editorId":"sts2-50099-7","editorX":370,"editorY":1020,"children":[],"weight":1}],"editorId":"sts2-50099-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G104">
         <v>170100</v>
@@ -5298,8 +5692,10 @@
       <c r="I104" t="s">
         <v>30</v>
       </c>
-      <c r="J104" t="s">
-        <v>525</v>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200017,"stacks":1,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"黏液沸腾","condition":"HP_BELOW","value":40,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"黏液沸腾","amount":16,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"黏液沸腾·压制","status":200006,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"黏液沸腾·重整","amount":3,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"黏液狂战士·追击","amount":12,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -5318,8 +5714,10 @@
       <c r="E105">
         <v>165</v>
       </c>
-      <c r="F105" t="s">
-        <v>528</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"冲锋","amount":22,"hits":1,"editorId":"sts2-50100-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"火焰喷射","amount":8,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"持续燃烧","status":200019,"stacks":2,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"DEFEND","moveName":"蓄力·格挡","amount":12,"editorId":"sts2-50100-5","editorX":670,"editorY":710,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"蓄力·强化","status":200001,"stacks":1,"editorId":"sts2-50100-6","editorX":670,"editorY":865,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50100-4","editorX":370,"editorY":555,"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"沉重劈砍","amount":22,"hits":1,"editorId":"sts2-50100-7","editorX":370,"editorY":1020,"children":[],"weight":1}],"editorId":"sts2-50100-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G105">
         <v>170101</v>
@@ -5330,8 +5728,10 @@
       <c r="I105" t="s">
         <v>53</v>
       </c>
-      <c r="J105" t="s">
-        <v>530</v>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200016,"stacks":4,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"机甲破损","condition":"HP_BELOW","value":50,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"机甲破损","amount":20,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"机甲破损·压制","status":200019,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"机甲破损·重整","amount":6,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"机甲骑士·追击","amount":15,"hits":1,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -5350,8 +5750,10 @@
       <c r="E106">
         <v>300</v>
       </c>
-      <c r="F106" t="s">
-        <v>533</v>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>{"type":"CYCLE","children":[{"type":"ACTION","action":"ATTACK","moveName":"光束","amount":26,"hits":1,"editorId":"sts2-50101-2","editorX":370,"editorY":245,"children":[],"weight":1},{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"退回门内","amount":26,"hits":1,"editorId":"sts2-50101-4","editorX":670,"editorY":555,"children":[],"weight":1},{"type":"ACTION","action":"BUFF","moveName":"退回门内·强化","status":200001,"stacks":2,"editorId":"sts2-50101-5","editorX":670,"editorY":710,"children":[],"weight":1,"duration":"DEFAULT"}],"editorId":"sts2-50101-3","editorX":370,"editorY":400,"weight":1}],"editorId":"sts2-50101-1","editorX":70,"editorY":90,"weight":1}</t>
+        </is>
       </c>
       <c r="G106">
         <v>170102</v>
@@ -5362,8 +5764,10 @@
       <c r="I106" t="s">
         <v>30</v>
       </c>
-      <c r="J106" t="s">
-        <v>535</v>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>{"initialStatuses":[{"status":200007,"stacks":2,"duration":"COMBAT"}],"phases":[{"id":"phase1","name":"门扉破裂","condition":"HP_BELOW","value":65,"effects":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"门扉破裂","amount":24,"hits":1,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"门扉破裂·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"门扉破裂·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"造门者·追击","amount":18,"hits":1,"children":[],"weight":1}],"weight":1}},{"id":"phase2","name":"门扉破裂·终局","condition":"HP_BELOW","value":30,"effects":[{"type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"behavior":{"type":"CYCLE","children":[{"type":"SEQUENCE","children":[{"type":"ACTION","action":"ATTACK","moveName":"门扉破裂·终局","amount":12,"hits":2,"children":[],"weight":1},{"type":"ACTION","action":"DEBUFF","moveName":"门扉破裂·终局·压制","status":200020,"stacks":1,"children":[],"weight":1,"duration":"DEFAULT"}],"weight":1},{"type":"ACTION","action":"DEFEND","moveName":"门扉破裂·终局·重整","amount":9,"children":[],"weight":1},{"type":"ACTION","action":"ATTACK","moveName":"造门者·追击","amount":9,"hits":2,"children":[],"weight":1}],"weight":1}}],"triggers":[]}</t>
+        </is>
       </c>
     </row>
   </sheetData>
